--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C41777C7-E39A-437B-AC39-446B05335F10}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6BC92766-32FF-46AF-8726-247CB9A1662D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5170" uniqueCount="1430">
   <si>
     <t>Operador</t>
   </si>
@@ -4057,6 +4057,264 @@
   </si>
   <si>
     <t>Rodrigo Alejandro Calix Cardenas</t>
+  </si>
+  <si>
+    <t>christian.velasquez@clarosv</t>
+  </si>
+  <si>
+    <t>Christian Alexander Velásquez Castro</t>
+  </si>
+  <si>
+    <t>Alexandra Bolaños</t>
+  </si>
+  <si>
+    <t>mariare.escobar@clarosv</t>
+  </si>
+  <si>
+    <t>María Renee Escobar Castro</t>
+  </si>
+  <si>
+    <t>kevin.chavez@clarosv</t>
+  </si>
+  <si>
+    <t>Kevin Guillermo Chavez Alvarez</t>
+  </si>
+  <si>
+    <t>raquel.montoya@clarosv</t>
+  </si>
+  <si>
+    <t>Raquel Abigail Montoya Gonzalez</t>
+  </si>
+  <si>
+    <t>Byron Marin</t>
+  </si>
+  <si>
+    <t>ashleys.martinez@clarosv</t>
+  </si>
+  <si>
+    <t>Ashley Stacey Martinez Ramos</t>
+  </si>
+  <si>
+    <t>alexis.medina@clarosv</t>
+  </si>
+  <si>
+    <t>Christopher Alexis Marroquin Medina</t>
+  </si>
+  <si>
+    <t>edwin.arivas@clarosv</t>
+  </si>
+  <si>
+    <t>Edwin Alexis Rivas Alfaro</t>
+  </si>
+  <si>
+    <t>elizabeth.moran@clarosv</t>
+  </si>
+  <si>
+    <t>Elizabeth Jeannette Moran Paniagua</t>
+  </si>
+  <si>
+    <t>gladys.perez@clarosv</t>
+  </si>
+  <si>
+    <t>Gladys Vanessa Perez Carrillo</t>
+  </si>
+  <si>
+    <t>karenm.floresm@clarosv</t>
+  </si>
+  <si>
+    <t>Karen Melissa Flores Mejia</t>
+  </si>
+  <si>
+    <t>kathya.aguilar@clarosv</t>
+  </si>
+  <si>
+    <t>Kathya Ivette Aguilar Vasquez</t>
+  </si>
+  <si>
+    <t>maria.moranc@clarosv</t>
+  </si>
+  <si>
+    <t>Maria Jose Moran Castro</t>
+  </si>
+  <si>
+    <t>maritza.salazar@clarosv</t>
+  </si>
+  <si>
+    <t>Maritza Lissette Salazar Gomez</t>
+  </si>
+  <si>
+    <t>melissa.rivas@clarosv</t>
+  </si>
+  <si>
+    <t>Melissa Jazmin Rivas Aguirre</t>
+  </si>
+  <si>
+    <t>milton.zaldana@clarosv</t>
+  </si>
+  <si>
+    <t>Milton Alberto Zaldana Miranda</t>
+  </si>
+  <si>
+    <t>sara.canizales@clarosv</t>
+  </si>
+  <si>
+    <t>Sara Ester Canizalles Villanueva</t>
+  </si>
+  <si>
+    <t>dianan.montano@clarosv</t>
+  </si>
+  <si>
+    <t>Diana Natalia Montano Portillo</t>
+  </si>
+  <si>
+    <t>Rudy Centeno</t>
+  </si>
+  <si>
+    <t>nataliap1.munoz@clarosv</t>
+  </si>
+  <si>
+    <t>Natalia Patricia Munoz de Juarez</t>
+  </si>
+  <si>
+    <t>bryan.represa@clarosv</t>
+  </si>
+  <si>
+    <t>Bryan Ismael Represa Barrera</t>
+  </si>
+  <si>
+    <t>Aracely Rodriguez</t>
+  </si>
+  <si>
+    <t>miriamj.garcia@clarosv</t>
+  </si>
+  <si>
+    <t>Miriam Julissa Garcia Barrientos</t>
+  </si>
+  <si>
+    <t>josselyn.garcia@clarosv</t>
+  </si>
+  <si>
+    <t>Josselyn Elizabeth Martinez Garcia</t>
+  </si>
+  <si>
+    <t>alejandra.cardona@clarosv</t>
+  </si>
+  <si>
+    <t>Alejandra Noemi Cardona Gonzalez</t>
+  </si>
+  <si>
+    <t>axel1.torres@clarosv</t>
+  </si>
+  <si>
+    <t>gisela.rodas@clarosv</t>
+  </si>
+  <si>
+    <t>Gisela Margarita Rodas Torres</t>
+  </si>
+  <si>
+    <t>javier.ruize@clarosv</t>
+  </si>
+  <si>
+    <t>Cesar Elias</t>
+  </si>
+  <si>
+    <t>fernandoa1.magana@clarosv</t>
+  </si>
+  <si>
+    <t>Fernando Alberto Magana Argumedo</t>
+  </si>
+  <si>
+    <t>tatiana.aragon@clarosv</t>
+  </si>
+  <si>
+    <t>Tatiana Rosibel Aragon Pineda</t>
+  </si>
+  <si>
+    <t>priscila.escobar@clarosv</t>
+  </si>
+  <si>
+    <t>Priscila Alejandra Escobar Hernandez</t>
+  </si>
+  <si>
+    <t>Emerson Hernandez</t>
+  </si>
+  <si>
+    <t>mariana.osorio@clarosv</t>
+  </si>
+  <si>
+    <t>Mariana Alejandra Osorio Hernandez</t>
+  </si>
+  <si>
+    <t>kathya.jimenez@clarosv</t>
+  </si>
+  <si>
+    <t>Kathya Marisela Jimenez Martinez</t>
+  </si>
+  <si>
+    <t>sandrav.aquino@clarosv</t>
+  </si>
+  <si>
+    <t>Gerson Raymundo</t>
+  </si>
+  <si>
+    <t>rolando.floresg@clarosv</t>
+  </si>
+  <si>
+    <t>Rolando Eduardo Flores Garcia</t>
+  </si>
+  <si>
+    <t>jose.medranov@clarosv</t>
+  </si>
+  <si>
+    <t>Jose Alexander Medrano Valdes</t>
+  </si>
+  <si>
+    <t>carmen.calito@clarosv</t>
+  </si>
+  <si>
+    <t>Carmen Rachel Calito Diaz</t>
+  </si>
+  <si>
+    <t>elisandra.garcia@clarosv</t>
+  </si>
+  <si>
+    <t>Elisandra Anahi Garcia Portillo</t>
+  </si>
+  <si>
+    <t>jeremy.guevara@clarosv</t>
+  </si>
+  <si>
+    <t>Jeremy Hernan Guevara Genovez</t>
+  </si>
+  <si>
+    <t>douglas.figueroa@clarosv</t>
+  </si>
+  <si>
+    <t>Douglas Alberto Figueroa Garcia</t>
+  </si>
+  <si>
+    <t>marcelac.cruz@clarosv</t>
+  </si>
+  <si>
+    <t>MARCELA SILENE CRUZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>daniel.amartinezg@clarosv</t>
+  </si>
+  <si>
+    <t>Daniel Alexander Martinez Guerrero</t>
+  </si>
+  <si>
+    <t>pamela.ramosd@clarosv</t>
+  </si>
+  <si>
+    <t>Fernando Giron</t>
+  </si>
+  <si>
+    <t>garcia.abraham@clarosv</t>
+  </si>
+  <si>
+    <t>Abraham Alexander García Sánchez</t>
   </si>
 </sst>
 </file>
@@ -4189,7 +4447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4277,12 +4535,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4403,6 +4670,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4572,8 +4848,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:I636" totalsRowShown="0">
-  <autoFilter ref="A1:I636" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:I677" totalsRowShown="0">
+  <autoFilter ref="A1:I677" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7BD220EC-FC0A-4480-8D39-25DB09CE0C75}" name="Usuario nuevo"/>
     <tableColumn id="2" xr3:uid="{CA71B84D-567B-4CB2-ADA9-AE9685B5C54E}" name="Area"/>
@@ -4886,7 +5162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E5DA33-968B-4101-A9B9-D29317846CB4}">
-  <dimension ref="A1:I636"/>
+  <dimension ref="A1:I677"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="1" customWidth="1"/>
@@ -6443,7 +6719,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30">
+    <row r="59" spans="1:9">
       <c r="A59" s="9" t="s">
         <v>206</v>
       </c>
@@ -6499,7 +6775,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30">
+    <row r="61" spans="1:9">
       <c r="A61" s="9" t="s">
         <v>211</v>
       </c>
@@ -6580,7 +6856,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30">
+    <row r="64" spans="1:9">
       <c r="A64" s="5" t="s">
         <v>217</v>
       </c>
@@ -6636,7 +6912,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="30">
+    <row r="66" spans="1:9">
       <c r="A66" s="5" t="s">
         <v>221</v>
       </c>
@@ -6690,7 +6966,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30">
+    <row r="68" spans="1:9">
       <c r="A68" s="5" t="s">
         <v>225</v>
       </c>
@@ -6744,7 +7020,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30">
+    <row r="70" spans="1:9">
       <c r="A70" s="5" t="s">
         <v>229</v>
       </c>
@@ -6771,7 +7047,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="30">
+    <row r="71" spans="1:9">
       <c r="A71" s="9" t="s">
         <v>231</v>
       </c>
@@ -6825,7 +7101,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30">
+    <row r="73" spans="1:9">
       <c r="A73" s="9" t="s">
         <v>235</v>
       </c>
@@ -6879,7 +7155,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30">
+    <row r="75" spans="1:9">
       <c r="A75" s="9" t="s">
         <v>239</v>
       </c>
@@ -6933,7 +7209,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30">
+    <row r="77" spans="1:9">
       <c r="A77" s="9" t="s">
         <v>243</v>
       </c>
@@ -6987,7 +7263,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="30">
+    <row r="79" spans="1:9">
       <c r="A79" s="9" t="s">
         <v>247</v>
       </c>
@@ -7041,7 +7317,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="30">
+    <row r="81" spans="1:9">
       <c r="A81" s="9" t="s">
         <v>251</v>
       </c>
@@ -7095,7 +7371,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30">
+    <row r="83" spans="1:9">
       <c r="A83" s="9" t="s">
         <v>255</v>
       </c>
@@ -7122,7 +7398,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="30">
+    <row r="84" spans="1:9">
       <c r="A84" s="5" t="s">
         <v>257</v>
       </c>
@@ -7149,7 +7425,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="30">
+    <row r="85" spans="1:9">
       <c r="A85" s="9" t="s">
         <v>259</v>
       </c>
@@ -7176,7 +7452,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="30">
+    <row r="86" spans="1:9">
       <c r="A86" s="5" t="s">
         <v>261</v>
       </c>
@@ -7261,7 +7537,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="30">
+    <row r="89" spans="1:9">
       <c r="A89" s="9" t="s">
         <v>267</v>
       </c>
@@ -7369,7 +7645,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="30">
+    <row r="93" spans="1:9">
       <c r="A93" s="9" t="s">
         <v>275</v>
       </c>
@@ -7425,7 +7701,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30">
+    <row r="95" spans="1:9">
       <c r="A95" s="9" t="s">
         <v>279</v>
       </c>
@@ -9180,7 +9456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="30">
+    <row r="160" spans="1:9">
       <c r="A160" s="5" t="s">
         <v>423</v>
       </c>
@@ -14254,7 +14530,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="29.25">
+    <row r="350" spans="1:9">
       <c r="A350" s="5" t="s">
         <v>763</v>
       </c>
@@ -14308,7 +14584,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="29.25">
+    <row r="352" spans="1:9">
       <c r="A352" s="5" t="s">
         <v>767</v>
       </c>
@@ -14416,7 +14692,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="29.25">
+    <row r="356" spans="1:9">
       <c r="A356" s="5" t="s">
         <v>775</v>
       </c>
@@ -14632,7 +14908,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="29.25">
+    <row r="364" spans="1:9">
       <c r="A364" s="5" t="s">
         <v>791</v>
       </c>
@@ -14740,7 +15016,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="29.25">
+    <row r="368" spans="1:9">
       <c r="A368" s="5" t="s">
         <v>799</v>
       </c>
@@ -14767,7 +15043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="29.25">
+    <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
         <v>801</v>
       </c>
@@ -14956,7 +15232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="29.25">
+    <row r="376" spans="1:9">
       <c r="A376" s="16" t="s">
         <v>815</v>
       </c>
@@ -14983,7 +15259,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="29.25">
+    <row r="377" spans="1:9">
       <c r="A377" s="15" t="s">
         <v>817</v>
       </c>
@@ -15037,7 +15313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="29.25">
+    <row r="379" spans="1:9">
       <c r="A379" s="15" t="s">
         <v>821</v>
       </c>
@@ -15091,7 +15367,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="29.25">
+    <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
         <v>825</v>
       </c>
@@ -15118,7 +15394,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="43.5">
+    <row r="382" spans="1:9">
       <c r="A382" s="5" t="s">
         <v>827</v>
       </c>
@@ -15280,7 +15556,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="29.25">
+    <row r="388" spans="1:9">
       <c r="A388" s="5" t="s">
         <v>839</v>
       </c>
@@ -15307,7 +15583,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="43.5">
+    <row r="389" spans="1:9" ht="29.25">
       <c r="A389" s="9" t="s">
         <v>841</v>
       </c>
@@ -15496,7 +15772,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="29.25">
+    <row r="396" spans="1:9">
       <c r="A396" s="5" t="s">
         <v>855</v>
       </c>
@@ -15631,7 +15907,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="29.25">
+    <row r="401" spans="1:9">
       <c r="A401" s="9" t="s">
         <v>865</v>
       </c>
@@ -15685,7 +15961,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="29.25">
+    <row r="403" spans="1:9">
       <c r="A403" s="9" t="s">
         <v>869</v>
       </c>
@@ -15712,7 +15988,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="29.25">
+    <row r="404" spans="1:9">
       <c r="A404" s="5" t="s">
         <v>871</v>
       </c>
@@ -15739,7 +16015,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="29.25">
+    <row r="405" spans="1:9">
       <c r="A405" s="9" t="s">
         <v>873</v>
       </c>
@@ -18567,7 +18843,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="30">
+    <row r="517" spans="1:9">
       <c r="A517" s="9" t="s">
         <v>1106</v>
       </c>
@@ -18867,7 +19143,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="30">
+    <row r="529" spans="1:9">
       <c r="A529" s="9" t="s">
         <v>1130</v>
       </c>
@@ -18917,7 +19193,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="30">
+    <row r="531" spans="1:9">
       <c r="A531" s="9" t="s">
         <v>1133</v>
       </c>
@@ -18942,7 +19218,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="30">
+    <row r="532" spans="1:9">
       <c r="A532" s="5" t="s">
         <v>1135</v>
       </c>
@@ -19550,7 +19826,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="30">
+    <row r="556" spans="1:9">
       <c r="A556" s="5" t="s">
         <v>1182</v>
       </c>
@@ -19675,7 +19951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="45">
+    <row r="561" spans="1:9" ht="30">
       <c r="A561" s="9" t="s">
         <v>1192</v>
       </c>
@@ -19825,7 +20101,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="30">
+    <row r="567" spans="1:9">
       <c r="A567" s="9" t="s">
         <v>1204</v>
       </c>
@@ -20029,7 +20305,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="30">
+    <row r="575" spans="1:9">
       <c r="A575" s="9" t="s">
         <v>1220</v>
       </c>
@@ -20079,7 +20355,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="30">
+    <row r="577" spans="1:9">
       <c r="A577" s="9" t="s">
         <v>1224</v>
       </c>
@@ -20129,7 +20405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="30">
+    <row r="579" spans="1:9">
       <c r="A579" s="9" t="s">
         <v>1228</v>
       </c>
@@ -20206,7 +20482,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="30">
+    <row r="582" spans="1:9">
       <c r="A582" s="5" t="s">
         <v>1233</v>
       </c>
@@ -20308,7 +20584,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="30">
+    <row r="586" spans="1:9">
       <c r="A586" s="5" t="s">
         <v>1241</v>
       </c>
@@ -20408,7 +20684,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="30">
+    <row r="590" spans="1:9">
       <c r="A590" s="5" t="s">
         <v>1249</v>
       </c>
@@ -20737,7 +21013,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="30">
+    <row r="603" spans="1:9">
       <c r="A603" s="9" t="s">
         <v>1275</v>
       </c>
@@ -20762,7 +21038,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="30">
+    <row r="604" spans="1:9">
       <c r="A604" s="5" t="s">
         <v>1277</v>
       </c>
@@ -20862,7 +21138,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="30">
+    <row r="608" spans="1:9">
       <c r="A608" s="5" t="s">
         <v>1286</v>
       </c>
@@ -21602,10 +21878,10 @@
       <c r="A636" s="5" t="s">
         <v>1342</v>
       </c>
-      <c r="B636" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C636" s="53" t="s">
+      <c r="B636" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C636" s="50" t="s">
         <v>1343</v>
       </c>
       <c r="D636" s="7" t="s">
@@ -21622,6 +21898,1113 @@
       </c>
       <c r="H636" s="7"/>
       <c r="I636" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9">
+      <c r="A637" s="68" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B637" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C637" s="50" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D637" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="E637" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F637" s="69" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G637" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H637" s="69"/>
+      <c r="I637" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9">
+      <c r="A638" s="68" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B638" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C638" s="50" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D638" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="E638" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F638" s="69" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G638" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H638" s="69"/>
+      <c r="I638" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9">
+      <c r="A639" s="68" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B639" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C639" s="50" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D639" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="E639" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F639" s="69" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G639" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H639" s="69"/>
+      <c r="I639" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9">
+      <c r="A640" s="70" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B640" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C640" s="50" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D640" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E640" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F640" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G640" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H640" s="69"/>
+      <c r="I640" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9">
+      <c r="A641" s="70" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B641" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C641" s="50" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D641" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E641" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F641" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G641" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H641" s="69"/>
+      <c r="I641" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9">
+      <c r="A642" s="70" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B642" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C642" s="50" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D642" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E642" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F642" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G642" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H642" s="69"/>
+      <c r="I642" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9">
+      <c r="A643" s="70" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B643" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C643" s="50" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D643" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E643" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F643" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G643" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H643" s="69"/>
+      <c r="I643" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9">
+      <c r="A644" s="70" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B644" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C644" s="50" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D644" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E644" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F644" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G644" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H644" s="69"/>
+      <c r="I644" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9">
+      <c r="A645" s="70" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B645" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C645" s="50" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D645" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E645" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F645" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G645" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H645" s="69"/>
+      <c r="I645" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9">
+      <c r="A646" s="70" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B646" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C646" s="50" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D646" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E646" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F646" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G646" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H646" s="69"/>
+      <c r="I646" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9">
+      <c r="A647" s="70" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B647" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C647" s="50" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D647" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E647" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F647" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G647" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H647" s="69"/>
+      <c r="I647" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9">
+      <c r="A648" s="70" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B648" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C648" s="50" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D648" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E648" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F648" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G648" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H648" s="69"/>
+      <c r="I648" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9">
+      <c r="A649" s="68" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B649" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C649" s="50" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D649" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E649" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F649" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G649" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H649" s="69"/>
+      <c r="I649" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9">
+      <c r="A650" s="68" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B650" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C650" s="50" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D650" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E650" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F650" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G650" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H650" s="69"/>
+      <c r="I650" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9">
+      <c r="A651" s="68" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B651" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C651" s="50" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D651" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E651" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F651" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G651" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H651" s="69"/>
+      <c r="I651" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9">
+      <c r="A652" s="68" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B652" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C652" s="50" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D652" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E652" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F652" s="69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G652" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H652" s="69"/>
+      <c r="I652" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9">
+      <c r="A653" s="68" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B653" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C653" s="50" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D653" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E653" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F653" s="69" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G653" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H653" s="69"/>
+      <c r="I653" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9">
+      <c r="A654" s="68" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B654" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C654" s="50" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D654" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E654" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F654" s="69" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G654" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H654" s="69"/>
+      <c r="I654" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9">
+      <c r="A655" s="68" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B655" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C655" s="50" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D655" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E655" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F655" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G655" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H655" s="69"/>
+      <c r="I655" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9">
+      <c r="A656" s="68" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B656" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C656" s="50" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D656" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E656" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F656" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G656" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H656" s="69"/>
+      <c r="I656" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9">
+      <c r="A657" s="68" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B657" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C657" s="50" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D657" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E657" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F657" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G657" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H657" s="69"/>
+      <c r="I657" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9">
+      <c r="A658" s="68" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B658" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C658" s="50" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D658" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E658" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F658" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G658" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H658" s="69"/>
+      <c r="I658" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9">
+      <c r="A659" s="68" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B659" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C659" s="50" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D659" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E659" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F659" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G659" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H659" s="69"/>
+      <c r="I659" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9">
+      <c r="A660" s="68" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B660" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C660" s="50" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D660" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E660" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F660" s="69" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G660" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H660" s="69"/>
+      <c r="I660" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9">
+      <c r="A661" s="68" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B661" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C661" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="D661" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E661" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F661" s="69" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G661" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H661" s="69"/>
+      <c r="I661" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9">
+      <c r="A662" s="68" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B662" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C662" s="50" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D662" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E662" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F662" s="69" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G662" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H662" s="69"/>
+      <c r="I662" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9">
+      <c r="A663" s="68" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B663" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C663" s="50" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D663" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E663" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F663" s="69" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G663" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H663" s="69"/>
+      <c r="I663" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9">
+      <c r="A664" s="68" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B664" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C664" s="50" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D664" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E664" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F664" s="69" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G664" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H664" s="69"/>
+      <c r="I664" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9">
+      <c r="A665" s="68" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B665" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C665" s="50" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D665" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E665" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F665" s="69" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G665" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H665" s="69"/>
+      <c r="I665" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9">
+      <c r="A666" s="68" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B666" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C666" s="50" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D666" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E666" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F666" s="69" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G666" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H666" s="69"/>
+      <c r="I666" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9">
+      <c r="A667" s="68" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B667" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C667" s="50" t="s">
+        <v>918</v>
+      </c>
+      <c r="D667" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E667" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F667" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G667" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H667" s="69"/>
+      <c r="I667" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9">
+      <c r="A668" s="68" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B668" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C668" s="50" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D668" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E668" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F668" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G668" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H668" s="69"/>
+      <c r="I668" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9">
+      <c r="A669" s="68" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B669" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C669" s="50" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D669" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E669" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F669" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G669" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H669" s="69"/>
+      <c r="I669" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9">
+      <c r="A670" s="68" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B670" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C670" s="50" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D670" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E670" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F670" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G670" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H670" s="69"/>
+      <c r="I670" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9">
+      <c r="A671" s="68" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B671" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C671" s="50" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D671" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E671" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F671" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G671" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H671" s="69"/>
+      <c r="I671" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9">
+      <c r="A672" s="68" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B672" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C672" s="50" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D672" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E672" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F672" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G672" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H672" s="69"/>
+      <c r="I672" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9">
+      <c r="A673" s="68" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B673" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C673" s="50" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D673" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E673" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F673" s="69" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G673" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H673" s="69"/>
+      <c r="I673" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9">
+      <c r="A674" s="68" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B674" s="72" t="s">
+        <v>292</v>
+      </c>
+      <c r="C674" s="50" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D674" s="69" t="s">
+        <v>294</v>
+      </c>
+      <c r="E674" s="69" t="s">
+        <v>425</v>
+      </c>
+      <c r="F674" s="69" t="s">
+        <v>880</v>
+      </c>
+      <c r="G674" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H674" s="69"/>
+      <c r="I674" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9">
+      <c r="A675" s="70" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B675" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="C675" s="50" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D675" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="E675" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="F675" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G675" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H675" s="69"/>
+      <c r="I675" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9">
+      <c r="A676" s="68" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B676" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="C676" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D676" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="E676" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="F676" s="69" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G676" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H676" s="69"/>
+      <c r="I676" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="1:9">
+      <c r="A677" s="68" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B677" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="C677" s="50" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D677" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E677" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="F677" s="71" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G677" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H677" s="69"/>
+      <c r="I677" s="72" t="s">
         <v>0</v>
       </c>
     </row>
@@ -21777,31 +23160,26 @@
     <hyperlink ref="A611" r:id="rId148" display="mailto:angel.reyesh@clarosv" xr:uid="{E6853CBA-D83E-4647-9058-374EB04F575D}"/>
     <hyperlink ref="A616" r:id="rId149" display="mailto:alejandram.flores@clarosv" xr:uid="{F1A197E0-917E-46EA-87D9-842D5CD919D8}"/>
     <hyperlink ref="A617" r:id="rId150" display="mailto:adriana.raudag@clarosv" xr:uid="{B766A802-1A3B-4F64-90F3-208C2FFA2085}"/>
+    <hyperlink ref="A640" r:id="rId151" display="mailto:raquel.montoya@clarosv" xr:uid="{C07B9160-B733-4FA6-A5A0-D31637362B1E}"/>
+    <hyperlink ref="A641" r:id="rId152" display="mailto:ashleys.martinez@clarosv" xr:uid="{391CA61D-0262-4845-B378-92864880A10A}"/>
+    <hyperlink ref="A642" r:id="rId153" display="mailto:alexis.medina@clarosv" xr:uid="{3E395814-9EA4-4EE7-A4AE-33E5F4C313A1}"/>
+    <hyperlink ref="A643" r:id="rId154" display="mailto:edwin.arivas@clarosv" xr:uid="{86C4FF5D-F3AA-4BCB-B8BF-FC3613DFA0C9}"/>
+    <hyperlink ref="A644" r:id="rId155" display="mailto:elizabeth.moran@clarosv" xr:uid="{BFF41FBB-82DF-4EAF-8E36-97439F76B32A}"/>
+    <hyperlink ref="A645" r:id="rId156" display="mailto:gladys.perez@clarosv" xr:uid="{DFD9A412-355E-415A-BA9C-387FB0BEF0CC}"/>
+    <hyperlink ref="A646" r:id="rId157" display="mailto:karenm.floresm@clarosv" xr:uid="{D1E34B77-3A68-4D0D-A6A1-187F948D1143}"/>
+    <hyperlink ref="A647" r:id="rId158" display="mailto:kathya.aguilar@clarosv" xr:uid="{7763D5D3-EC14-45B7-A524-ED910A171443}"/>
+    <hyperlink ref="A648" r:id="rId159" display="mailto:maria.moranc@clarosv" xr:uid="{E66F9E59-ECFD-4433-AAF7-5AAC5BD64433}"/>
+    <hyperlink ref="A675" r:id="rId160" display="mailto:daniel.amartinezg@clarosv" xr:uid="{75819FCF-E904-4344-A254-B7606BFE1ADB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId151"/>
+  <pageSetup orientation="portrait" r:id="rId161"/>
   <tableParts count="1">
-    <tablePart r:id="rId152"/>
+    <tablePart r:id="rId162"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -21939,31 +23317,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21979,4 +23348,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6BC92766-32FF-46AF-8726-247CB9A1662D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C0102305-AE15-4CA2-80BC-8700904DA3EE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5170" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5740" uniqueCount="1620">
   <si>
     <t>Operador</t>
   </si>
@@ -4315,6 +4315,576 @@
   </si>
   <si>
     <t>Abraham Alexander García Sánchez</t>
+  </si>
+  <si>
+    <t>alexander.hurtado@clarosv</t>
+  </si>
+  <si>
+    <t>Erick Alexander Hurtado Henríquez</t>
+  </si>
+  <si>
+    <t>priscila.cardona@clarosv</t>
+  </si>
+  <si>
+    <t>Priscila Guadalupe Cardona Ramirez</t>
+  </si>
+  <si>
+    <t>fatima.cea@clarosv</t>
+  </si>
+  <si>
+    <t>Fatima Yosabeth Cea Lemus</t>
+  </si>
+  <si>
+    <t>estefany.ramirez@clarosv</t>
+  </si>
+  <si>
+    <t>Estefany Lizbeth Ramirez Castillo</t>
+  </si>
+  <si>
+    <t>claudia.castillom@clarosv</t>
+  </si>
+  <si>
+    <t>Claudia Marisela Castillo de Mejia</t>
+  </si>
+  <si>
+    <t>cristian.portillo@clarosv</t>
+  </si>
+  <si>
+    <t>Cristian Ernesto Portillo Zepeda</t>
+  </si>
+  <si>
+    <t>fatima.mayorga@clarosv</t>
+  </si>
+  <si>
+    <t>Fatima Elena Mayorga Rosales</t>
+  </si>
+  <si>
+    <t>karla.mendozam@clarosv</t>
+  </si>
+  <si>
+    <t>Karla Vanessa Mendoza Mendoza</t>
+  </si>
+  <si>
+    <t>katherine.menac@clarosv</t>
+  </si>
+  <si>
+    <t>Katherine Eunice Mena Castro</t>
+  </si>
+  <si>
+    <t>marcela.deras@clarosv</t>
+  </si>
+  <si>
+    <t>Marcela Elizabeth Deras Torres</t>
+  </si>
+  <si>
+    <t>mariela.martinezh@clarosv</t>
+  </si>
+  <si>
+    <t>Mariela Alejandra Martinez Hernandez</t>
+  </si>
+  <si>
+    <t>yanira.perez@clarosv</t>
+  </si>
+  <si>
+    <t>Yanira Elizabeth Perez Lopez</t>
+  </si>
+  <si>
+    <t>alexander.ruedas@clarosv</t>
+  </si>
+  <si>
+    <t>Alexander Humberto Ruedas Martinez 1</t>
+  </si>
+  <si>
+    <t>edwin.riverae@clarosv</t>
+  </si>
+  <si>
+    <t>Edwin Alexander Rivera Estevez</t>
+  </si>
+  <si>
+    <t>jenniffer.calderon@clarosv</t>
+  </si>
+  <si>
+    <t>Jenniffer Tatiana Calderon Moran</t>
+  </si>
+  <si>
+    <t>rodrigoa.monroyg@clarosv</t>
+  </si>
+  <si>
+    <t>Rodrigo Alejandro Monroy Garcia</t>
+  </si>
+  <si>
+    <t>raniay.alvarezl@clarosv</t>
+  </si>
+  <si>
+    <t>Rania Yasin Alvarez Linares</t>
+  </si>
+  <si>
+    <t>ernestoa.ramireze@clarosv</t>
+  </si>
+  <si>
+    <t>Ernesto Aaron Ramirez Estevez</t>
+  </si>
+  <si>
+    <t>gracia.colindres@clarosv</t>
+  </si>
+  <si>
+    <t>Gracia Alejandra Colindres Contreras</t>
+  </si>
+  <si>
+    <t>jacquelinne.lopez@clarosv</t>
+  </si>
+  <si>
+    <t>Jacquelinne Melisa Lopez Castro</t>
+  </si>
+  <si>
+    <t>cristian.floresr@clarosv</t>
+  </si>
+  <si>
+    <t>Cristian Everardo Flores Ramirez</t>
+  </si>
+  <si>
+    <t>alejandro.huezo@clarosv</t>
+  </si>
+  <si>
+    <t>Emerson Alejandro Castellanos Huezo</t>
+  </si>
+  <si>
+    <t>erick.amorales@clarosv</t>
+  </si>
+  <si>
+    <t>Erick Alexander Morales Castaneda</t>
+  </si>
+  <si>
+    <t>erikaj.ramirez@clarosv</t>
+  </si>
+  <si>
+    <t>Erika Jazmin Ramirez Bachez</t>
+  </si>
+  <si>
+    <t>fatima.galero@clarosv</t>
+  </si>
+  <si>
+    <t>Fatima Abigail Galero Cristales</t>
+  </si>
+  <si>
+    <t>gloria.pineda@clarosv</t>
+  </si>
+  <si>
+    <t>Gloria Lineth Pineda Beltran</t>
+  </si>
+  <si>
+    <t>hubert.mata@clarosv</t>
+  </si>
+  <si>
+    <t>Hubert Josederick Mata Martinez</t>
+  </si>
+  <si>
+    <t>jenniffer.escobar@clarosv</t>
+  </si>
+  <si>
+    <t>Jenniffer Johanna Escobar Zarceno</t>
+  </si>
+  <si>
+    <t>leticia.qrodriguez@clarosv</t>
+  </si>
+  <si>
+    <t>Laura Leticia Quintanilla Rodriguez</t>
+  </si>
+  <si>
+    <t>melanie.alvarenga@clarosv</t>
+  </si>
+  <si>
+    <t>Melanie Jazmin Alvarenga Tobar</t>
+  </si>
+  <si>
+    <t>reinaldo.aguilar@clarosv</t>
+  </si>
+  <si>
+    <t>Reinaldo Jose Aguilar Bermudes</t>
+  </si>
+  <si>
+    <t>alejandrar.rivera@clarosv</t>
+  </si>
+  <si>
+    <t>Alejandra Rosalia Rivera Osegueda</t>
+  </si>
+  <si>
+    <t>alejandra.mancia@clarosv</t>
+  </si>
+  <si>
+    <t>Alejandra Margarita Mancia Paniagua</t>
+  </si>
+  <si>
+    <t>alma.alvarezb@clarosv</t>
+  </si>
+  <si>
+    <t>Alma Cristina Alvarez Blanco</t>
+  </si>
+  <si>
+    <t>jenniffer.hernandez@clarosv</t>
+  </si>
+  <si>
+    <t>Jeniffer Tatiana Hernandez Aranas</t>
+  </si>
+  <si>
+    <t>jorge.catalana@clarosv</t>
+  </si>
+  <si>
+    <t>Jorge Roberto Catalan Ayala</t>
+  </si>
+  <si>
+    <t>leslie.raimundo@clarosv</t>
+  </si>
+  <si>
+    <t>Leslie Marcela Raimundo Morales</t>
+  </si>
+  <si>
+    <t>lizeth.aguilar@clarosv</t>
+  </si>
+  <si>
+    <t>Lizeth Aziel Aguilar Vega</t>
+  </si>
+  <si>
+    <t>mario.alarconj@clarosv</t>
+  </si>
+  <si>
+    <t>Mario Ernesto Alarcon Jimenez</t>
+  </si>
+  <si>
+    <t>sandra.marenco@clarosv</t>
+  </si>
+  <si>
+    <t>Sandra Liseth Marenco Gonzalez</t>
+  </si>
+  <si>
+    <t>mariad.lopezd@clarosv</t>
+  </si>
+  <si>
+    <t>Maria de los Angeles Lopez Bolanos</t>
+  </si>
+  <si>
+    <t>gabriel.villegas@clarosv</t>
+  </si>
+  <si>
+    <t>Gabriel Alexander Villegas Hernandez</t>
+  </si>
+  <si>
+    <t>axel.rendon@clarosv</t>
+  </si>
+  <si>
+    <t>Axel Alejandro Rendon Vigil</t>
+  </si>
+  <si>
+    <t>anac.escobar@clarosv</t>
+  </si>
+  <si>
+    <t>Ana Carmen Escobar Amaya</t>
+  </si>
+  <si>
+    <t>axela.moreira@clarosv</t>
+  </si>
+  <si>
+    <t>Axel Adonis Moreira Chicas</t>
+  </si>
+  <si>
+    <t>christophera.leiva@clarosv</t>
+  </si>
+  <si>
+    <t>Christopher Alejandro Leiva Cestoni</t>
+  </si>
+  <si>
+    <t>jennifer.sanchezf@clarosv</t>
+  </si>
+  <si>
+    <t>Jennifer de los Angeles Sanchez Flores</t>
+  </si>
+  <si>
+    <t>astrid.flores@clarosv</t>
+  </si>
+  <si>
+    <t>Astrid Ivonne Flores Toledo</t>
+  </si>
+  <si>
+    <t>jonathana.figueroa@clarosv</t>
+  </si>
+  <si>
+    <t>Jonathan Alberto Figueroa Aguirre</t>
+  </si>
+  <si>
+    <t>jose.marcilla@clarosv</t>
+  </si>
+  <si>
+    <t>Jose Carlos Marcilla Hernandez</t>
+  </si>
+  <si>
+    <t>paolag.hernandez@clarosv</t>
+  </si>
+  <si>
+    <t>Paola Guadalupe Hernandez Lopez</t>
+  </si>
+  <si>
+    <t>rodrigo.nieto@clarosv</t>
+  </si>
+  <si>
+    <t>Rodrigo Ernesto Nieto Gomez</t>
+  </si>
+  <si>
+    <t>carlosa.osorio@clarosv</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Osorio Arana</t>
+  </si>
+  <si>
+    <t>gabrielae.gomez@clarosv</t>
+  </si>
+  <si>
+    <t>Gabriela Elizabeth gomez Lara</t>
+  </si>
+  <si>
+    <t>gabrielaa.moran@clarosv</t>
+  </si>
+  <si>
+    <t>Gabriela Alejandra Moran Hernandez</t>
+  </si>
+  <si>
+    <t>irene.preza@clarosv</t>
+  </si>
+  <si>
+    <t>Irene Verenice Preza Perez</t>
+  </si>
+  <si>
+    <t>marilynb.pena@clarosv</t>
+  </si>
+  <si>
+    <t>Marilyn Beatriz Pena Zapata</t>
+  </si>
+  <si>
+    <t>rafael.ebarrera@clarosv</t>
+  </si>
+  <si>
+    <t>Rafael Ernesto Barrera Anaya</t>
+  </si>
+  <si>
+    <t>ricardor.lopez@clarosv</t>
+  </si>
+  <si>
+    <t>Ricardo Rixiery Lopez Calderon</t>
+  </si>
+  <si>
+    <t>vanessab.mendoza@clarosv</t>
+  </si>
+  <si>
+    <t>Vanessa Beatriz Mendoza Cruz</t>
+  </si>
+  <si>
+    <t>josuej.ramirez@clarosv</t>
+  </si>
+  <si>
+    <t>Josue Jeremias Ramirez Vasquez</t>
+  </si>
+  <si>
+    <t>karinae.tobar@clarosv</t>
+  </si>
+  <si>
+    <t>Karina Estefany Tobar Portillo</t>
+  </si>
+  <si>
+    <t>marioa.castro@clarosv</t>
+  </si>
+  <si>
+    <t>Mario Alejandro Castro Iglesias</t>
+  </si>
+  <si>
+    <t>oscar.cordova@clarosv</t>
+  </si>
+  <si>
+    <t>Oscar Roberto Cordova Burgos</t>
+  </si>
+  <si>
+    <t>rebeca.argumedo@clarosv</t>
+  </si>
+  <si>
+    <t>Rebeca Priscila Argumedo Rivera</t>
+  </si>
+  <si>
+    <t>walteri.marroquin@clarosv</t>
+  </si>
+  <si>
+    <t>Walter Isaac Marroquin Anzora</t>
+  </si>
+  <si>
+    <t>william.campose@clarosv</t>
+  </si>
+  <si>
+    <t>William Alexander Campos Echeverria</t>
+  </si>
+  <si>
+    <t>adonis.ponce@clarosv</t>
+  </si>
+  <si>
+    <t>Adonis Emmanuel Ponce Ulloa</t>
+  </si>
+  <si>
+    <t>angela.mendozac@clarosv</t>
+  </si>
+  <si>
+    <t>Angela Guadalupe Mendoza Cruz</t>
+  </si>
+  <si>
+    <t>daniela.gomezr@clarosv</t>
+  </si>
+  <si>
+    <t>Daniela Ivette Gomez Romero</t>
+  </si>
+  <si>
+    <t>elias.genovez@clarosv</t>
+  </si>
+  <si>
+    <t>Elias Javier Genovez Lopez</t>
+  </si>
+  <si>
+    <t>fernando.guillen@clarosv</t>
+  </si>
+  <si>
+    <t>Fernando Jose Guillen Garcia</t>
+  </si>
+  <si>
+    <t>erika.pmartinez2@clarosv</t>
+  </si>
+  <si>
+    <t>adriana.garciac@clarosv</t>
+  </si>
+  <si>
+    <t>ADRIANA LISSETTE GARCIA CAMPOS</t>
+  </si>
+  <si>
+    <t>Nesting</t>
+  </si>
+  <si>
+    <t>brenda.ramosc@clarosv</t>
+  </si>
+  <si>
+    <t>BRENDA ABIGAIL RAMOS CASTILLO</t>
+  </si>
+  <si>
+    <t>dayana.campos@clarosv</t>
+  </si>
+  <si>
+    <t>DAYANA JEANNETTE CAMPOS FUENTES</t>
+  </si>
+  <si>
+    <t>diana.martinezm@clarosv</t>
+  </si>
+  <si>
+    <t>DIANA ARACELI MARTINEZ MERINO</t>
+  </si>
+  <si>
+    <t>diego.contreras@clarosv</t>
+  </si>
+  <si>
+    <t>DIEGO ALEJANDRO CONTRERAS VANEGAS</t>
+  </si>
+  <si>
+    <t>fernando.agreda@clarosv</t>
+  </si>
+  <si>
+    <t>FERNANDO ALBERTO AGREDA PENATE</t>
+  </si>
+  <si>
+    <t>gabriela.garciaf@clarosv</t>
+  </si>
+  <si>
+    <t>GABRIELA GUADALUPE GARCIA FLORES</t>
+  </si>
+  <si>
+    <t>gerson.villaltar@clarosv</t>
+  </si>
+  <si>
+    <t>GERSON SALVADOR VILLALTA RIVERA</t>
+  </si>
+  <si>
+    <t>javier.fuentesv@clarosv</t>
+  </si>
+  <si>
+    <t>JAVIER ALEJANDRO FUENTES VARGAS</t>
+  </si>
+  <si>
+    <t>julio.floresc@clarosv</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO FLORES CHAVEZ</t>
+  </si>
+  <si>
+    <t>karen.deceron@clarosv</t>
+  </si>
+  <si>
+    <t>KAREN EDITH MORALES DE CERON</t>
+  </si>
+  <si>
+    <t>karla.garciav@clarosv</t>
+  </si>
+  <si>
+    <t>KARLA ABIGAIL GARCIA VASQUEZ</t>
+  </si>
+  <si>
+    <t>katherinne.murillo@clarosv</t>
+  </si>
+  <si>
+    <t>KATHERINNE LIZBETH MURILLO VALDEZ</t>
+  </si>
+  <si>
+    <t>marelin.pineda@clarosv</t>
+  </si>
+  <si>
+    <t>MARELIN JULISSA PINEDA MORALES</t>
+  </si>
+  <si>
+    <t>mariac.romeror@clarosv</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN ROMERO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>maria.mejiaa@clarosv</t>
+  </si>
+  <si>
+    <t>MARIA ESTELA MEJIA AYALA</t>
+  </si>
+  <si>
+    <t>mario.godoy@clarosv</t>
+  </si>
+  <si>
+    <t>MARIO EDGARDO GODOY BARRERA</t>
+  </si>
+  <si>
+    <t>nathalie.hernandez@clarosv</t>
+  </si>
+  <si>
+    <t>NATHALIE ALEJANDRA HERNANDEZ MONTANO</t>
+  </si>
+  <si>
+    <t>paola.alfaro@clarosv</t>
+  </si>
+  <si>
+    <t>PAOLA CAROLINA ALFARO MENDOZA</t>
+  </si>
+  <si>
+    <t>sonia.hidalgo@clarosv</t>
+  </si>
+  <si>
+    <t>SONIA CAMILA HIDALGO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>vilma.flores@clarosv</t>
+  </si>
+  <si>
+    <t>VILMA NOEMI FLORES HERNANDEZ</t>
+  </si>
+  <si>
+    <t>yaritza.garciab@clarosv</t>
+  </si>
+  <si>
+    <t>YARITZA FERNANDA GARCIA BARRIENTOS</t>
   </si>
 </sst>
 </file>
@@ -4549,7 +5119,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4679,6 +5249,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4848,8 +5419,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:I677" totalsRowShown="0">
-  <autoFilter ref="A1:I677" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:I772" totalsRowShown="0">
+  <autoFilter ref="A1:I772" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7BD220EC-FC0A-4480-8D39-25DB09CE0C75}" name="Usuario nuevo"/>
     <tableColumn id="2" xr3:uid="{CA71B84D-567B-4CB2-ADA9-AE9685B5C54E}" name="Area"/>
@@ -5162,7 +5733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E5DA33-968B-4101-A9B9-D29317846CB4}">
-  <dimension ref="A1:I677"/>
+  <dimension ref="A1:I772"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="1" customWidth="1"/>
@@ -23007,6 +23578,2191 @@
       <c r="I677" s="72" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="678" spans="1:9">
+      <c r="A678" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D678" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E678" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F678" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="G678" s="7"/>
+      <c r="H678" s="7"/>
+      <c r="I678" s="73"/>
+    </row>
+    <row r="679" spans="1:9">
+      <c r="A679" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D679" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E679" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F679" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G679" s="7"/>
+      <c r="H679" s="7"/>
+      <c r="I679" s="73"/>
+    </row>
+    <row r="680" spans="1:9">
+      <c r="A680" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D680" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E680" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F680" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G680" s="7"/>
+      <c r="H680" s="7"/>
+      <c r="I680" s="73"/>
+    </row>
+    <row r="681" spans="1:9">
+      <c r="A681" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D681" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E681" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F681" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G681" s="7"/>
+      <c r="H681" s="7"/>
+      <c r="I681" s="73"/>
+    </row>
+    <row r="682" spans="1:9">
+      <c r="A682" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E682" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F682" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G682" s="7"/>
+      <c r="H682" s="7"/>
+      <c r="I682" s="73"/>
+    </row>
+    <row r="683" spans="1:9">
+      <c r="A683" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D683" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E683" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F683" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G683" s="7"/>
+      <c r="H683" s="7"/>
+      <c r="I683" s="73"/>
+    </row>
+    <row r="684" spans="1:9">
+      <c r="A684" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D684" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E684" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F684" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G684" s="7"/>
+      <c r="H684" s="7"/>
+      <c r="I684" s="73"/>
+    </row>
+    <row r="685" spans="1:9">
+      <c r="A685" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D685" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E685" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F685" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G685" s="7"/>
+      <c r="H685" s="7"/>
+      <c r="I685" s="73"/>
+    </row>
+    <row r="686" spans="1:9">
+      <c r="A686" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D686" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E686" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F686" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G686" s="7"/>
+      <c r="H686" s="7"/>
+      <c r="I686" s="73"/>
+    </row>
+    <row r="687" spans="1:9">
+      <c r="A687" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D687" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E687" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F687" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G687" s="7"/>
+      <c r="H687" s="7"/>
+      <c r="I687" s="73"/>
+    </row>
+    <row r="688" spans="1:9">
+      <c r="A688" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D688" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E688" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F688" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G688" s="7"/>
+      <c r="H688" s="7"/>
+      <c r="I688" s="73"/>
+    </row>
+    <row r="689" spans="1:9">
+      <c r="A689" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D689" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E689" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F689" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G689" s="7"/>
+      <c r="H689" s="7"/>
+      <c r="I689" s="73"/>
+    </row>
+    <row r="690" spans="1:9">
+      <c r="A690" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D690" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E690" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F690" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G690" s="7"/>
+      <c r="H690" s="7"/>
+      <c r="I690" s="73"/>
+    </row>
+    <row r="691" spans="1:9">
+      <c r="A691" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D691" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E691" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F691" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G691" s="7"/>
+      <c r="H691" s="7"/>
+      <c r="I691" s="73"/>
+    </row>
+    <row r="692" spans="1:9">
+      <c r="A692" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D692" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E692" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F692" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G692" s="7"/>
+      <c r="H692" s="7"/>
+      <c r="I692" s="73"/>
+    </row>
+    <row r="693" spans="1:9">
+      <c r="A693" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D693" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E693" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F693" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G693" s="7"/>
+      <c r="H693" s="7"/>
+      <c r="I693" s="73"/>
+    </row>
+    <row r="694" spans="1:9">
+      <c r="A694" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D694" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E694" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F694" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G694" s="7"/>
+      <c r="H694" s="7"/>
+      <c r="I694" s="73"/>
+    </row>
+    <row r="695" spans="1:9">
+      <c r="A695" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D695" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E695" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F695" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G695" s="7"/>
+      <c r="H695" s="7"/>
+      <c r="I695" s="73"/>
+    </row>
+    <row r="696" spans="1:9">
+      <c r="A696" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D696" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E696" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F696" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G696" s="7"/>
+      <c r="H696" s="7"/>
+      <c r="I696" s="73"/>
+    </row>
+    <row r="697" spans="1:9">
+      <c r="A697" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D697" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E697" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F697" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G697" s="7"/>
+      <c r="H697" s="7"/>
+      <c r="I697" s="73"/>
+    </row>
+    <row r="698" spans="1:9">
+      <c r="A698" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D698" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E698" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F698" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G698" s="7"/>
+      <c r="H698" s="7"/>
+      <c r="I698" s="73"/>
+    </row>
+    <row r="699" spans="1:9">
+      <c r="A699" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D699" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E699" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F699" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G699" s="7"/>
+      <c r="H699" s="7"/>
+      <c r="I699" s="73"/>
+    </row>
+    <row r="700" spans="1:9">
+      <c r="A700" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D700" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E700" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F700" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G700" s="7"/>
+      <c r="H700" s="7"/>
+      <c r="I700" s="73"/>
+    </row>
+    <row r="701" spans="1:9">
+      <c r="A701" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D701" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E701" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F701" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G701" s="7"/>
+      <c r="H701" s="7"/>
+      <c r="I701" s="73"/>
+    </row>
+    <row r="702" spans="1:9">
+      <c r="A702" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D702" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E702" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F702" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G702" s="7"/>
+      <c r="H702" s="7"/>
+      <c r="I702" s="73"/>
+    </row>
+    <row r="703" spans="1:9">
+      <c r="A703" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D703" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E703" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F703" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G703" s="7"/>
+      <c r="H703" s="7"/>
+      <c r="I703" s="73"/>
+    </row>
+    <row r="704" spans="1:9">
+      <c r="A704" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D704" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E704" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F704" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G704" s="7"/>
+      <c r="H704" s="7"/>
+      <c r="I704" s="73"/>
+    </row>
+    <row r="705" spans="1:9">
+      <c r="A705" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D705" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E705" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F705" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G705" s="7"/>
+      <c r="H705" s="7"/>
+      <c r="I705" s="73"/>
+    </row>
+    <row r="706" spans="1:9">
+      <c r="A706" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C706" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D706" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E706" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F706" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G706" s="7"/>
+      <c r="H706" s="7"/>
+      <c r="I706" s="73"/>
+    </row>
+    <row r="707" spans="1:9">
+      <c r="A707" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D707" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E707" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F707" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G707" s="7"/>
+      <c r="H707" s="7"/>
+      <c r="I707" s="73"/>
+    </row>
+    <row r="708" spans="1:9">
+      <c r="A708" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D708" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E708" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F708" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G708" s="7"/>
+      <c r="H708" s="7"/>
+      <c r="I708" s="73"/>
+    </row>
+    <row r="709" spans="1:9">
+      <c r="A709" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C709" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D709" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E709" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F709" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G709" s="7"/>
+      <c r="H709" s="7"/>
+      <c r="I709" s="73"/>
+    </row>
+    <row r="710" spans="1:9">
+      <c r="A710" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C710" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D710" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E710" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F710" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G710" s="7"/>
+      <c r="H710" s="7"/>
+      <c r="I710" s="73"/>
+    </row>
+    <row r="711" spans="1:9">
+      <c r="A711" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D711" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E711" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F711" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G711" s="7"/>
+      <c r="H711" s="7"/>
+      <c r="I711" s="73"/>
+    </row>
+    <row r="712" spans="1:9">
+      <c r="A712" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D712" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E712" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F712" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G712" s="7"/>
+      <c r="H712" s="7"/>
+      <c r="I712" s="73"/>
+    </row>
+    <row r="713" spans="1:9">
+      <c r="A713" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D713" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E713" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F713" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G713" s="7"/>
+      <c r="H713" s="7"/>
+      <c r="I713" s="73"/>
+    </row>
+    <row r="714" spans="1:9">
+      <c r="A714" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D714" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E714" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F714" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G714" s="7"/>
+      <c r="H714" s="7"/>
+      <c r="I714" s="73"/>
+    </row>
+    <row r="715" spans="1:9">
+      <c r="A715" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D715" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E715" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F715" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G715" s="7"/>
+      <c r="H715" s="7"/>
+      <c r="I715" s="73"/>
+    </row>
+    <row r="716" spans="1:9">
+      <c r="A716" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C716" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D716" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E716" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F716" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G716" s="7"/>
+      <c r="H716" s="7"/>
+      <c r="I716" s="73"/>
+    </row>
+    <row r="717" spans="1:9">
+      <c r="A717" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D717" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E717" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F717" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G717" s="7"/>
+      <c r="H717" s="7"/>
+      <c r="I717" s="73"/>
+    </row>
+    <row r="718" spans="1:9">
+      <c r="A718" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D718" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E718" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F718" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G718" s="7"/>
+      <c r="H718" s="7"/>
+      <c r="I718" s="73"/>
+    </row>
+    <row r="719" spans="1:9">
+      <c r="A719" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C719" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D719" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E719" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F719" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G719" s="7"/>
+      <c r="H719" s="7"/>
+      <c r="I719" s="73"/>
+    </row>
+    <row r="720" spans="1:9">
+      <c r="A720" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C720" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D720" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E720" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F720" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G720" s="7"/>
+      <c r="H720" s="7"/>
+      <c r="I720" s="73"/>
+    </row>
+    <row r="721" spans="1:9">
+      <c r="A721" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D721" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E721" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F721" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G721" s="7"/>
+      <c r="H721" s="7"/>
+      <c r="I721" s="73"/>
+    </row>
+    <row r="722" spans="1:9">
+      <c r="A722" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C722" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D722" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E722" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F722" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G722" s="7"/>
+      <c r="H722" s="7"/>
+      <c r="I722" s="73"/>
+    </row>
+    <row r="723" spans="1:9">
+      <c r="A723" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D723" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E723" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F723" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G723" s="7"/>
+      <c r="H723" s="7"/>
+      <c r="I723" s="73"/>
+    </row>
+    <row r="724" spans="1:9">
+      <c r="A724" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C724" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D724" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E724" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F724" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G724" s="7"/>
+      <c r="H724" s="7"/>
+      <c r="I724" s="73"/>
+    </row>
+    <row r="725" spans="1:9">
+      <c r="A725" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C725" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D725" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E725" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F725" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G725" s="7"/>
+      <c r="H725" s="7"/>
+      <c r="I725" s="73"/>
+    </row>
+    <row r="726" spans="1:9">
+      <c r="A726" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C726" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D726" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E726" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F726" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G726" s="7"/>
+      <c r="H726" s="7"/>
+      <c r="I726" s="73"/>
+    </row>
+    <row r="727" spans="1:9">
+      <c r="A727" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C727" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D727" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E727" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F727" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G727" s="7"/>
+      <c r="H727" s="7"/>
+      <c r="I727" s="73"/>
+    </row>
+    <row r="728" spans="1:9">
+      <c r="A728" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C728" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D728" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E728" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F728" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G728" s="7"/>
+      <c r="H728" s="7"/>
+      <c r="I728" s="73"/>
+    </row>
+    <row r="729" spans="1:9">
+      <c r="A729" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D729" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E729" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F729" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G729" s="7"/>
+      <c r="H729" s="7"/>
+      <c r="I729" s="73"/>
+    </row>
+    <row r="730" spans="1:9">
+      <c r="A730" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C730" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D730" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E730" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F730" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G730" s="7"/>
+      <c r="H730" s="7"/>
+      <c r="I730" s="73"/>
+    </row>
+    <row r="731" spans="1:9">
+      <c r="A731" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D731" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E731" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F731" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G731" s="7"/>
+      <c r="H731" s="7"/>
+      <c r="I731" s="73"/>
+    </row>
+    <row r="732" spans="1:9">
+      <c r="A732" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D732" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E732" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F732" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G732" s="7"/>
+      <c r="H732" s="7"/>
+      <c r="I732" s="73"/>
+    </row>
+    <row r="733" spans="1:9">
+      <c r="A733" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C733" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D733" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E733" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F733" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G733" s="7"/>
+      <c r="H733" s="7"/>
+      <c r="I733" s="73"/>
+    </row>
+    <row r="734" spans="1:9">
+      <c r="A734" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C734" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D734" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E734" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F734" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G734" s="7"/>
+      <c r="H734" s="7"/>
+      <c r="I734" s="73"/>
+    </row>
+    <row r="735" spans="1:9">
+      <c r="A735" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D735" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E735" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F735" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G735" s="7"/>
+      <c r="H735" s="7"/>
+      <c r="I735" s="73"/>
+    </row>
+    <row r="736" spans="1:9">
+      <c r="A736" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C736" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D736" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E736" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F736" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G736" s="7"/>
+      <c r="H736" s="7"/>
+      <c r="I736" s="73"/>
+    </row>
+    <row r="737" spans="1:9">
+      <c r="A737" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C737" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D737" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E737" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F737" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G737" s="7"/>
+      <c r="H737" s="7"/>
+      <c r="I737" s="73"/>
+    </row>
+    <row r="738" spans="1:9">
+      <c r="A738" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C738" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D738" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E738" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F738" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G738" s="7"/>
+      <c r="H738" s="7"/>
+      <c r="I738" s="73"/>
+    </row>
+    <row r="739" spans="1:9">
+      <c r="A739" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C739" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D739" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E739" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F739" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G739" s="7"/>
+      <c r="H739" s="7"/>
+      <c r="I739" s="73"/>
+    </row>
+    <row r="740" spans="1:9">
+      <c r="A740" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C740" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D740" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E740" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F740" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G740" s="7"/>
+      <c r="H740" s="7"/>
+      <c r="I740" s="73"/>
+    </row>
+    <row r="741" spans="1:9">
+      <c r="A741" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C741" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D741" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E741" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F741" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G741" s="7"/>
+      <c r="H741" s="7"/>
+      <c r="I741" s="73"/>
+    </row>
+    <row r="742" spans="1:9">
+      <c r="A742" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D742" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E742" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F742" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G742" s="7"/>
+      <c r="H742" s="7"/>
+      <c r="I742" s="73"/>
+    </row>
+    <row r="743" spans="1:9">
+      <c r="A743" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D743" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E743" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F743" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G743" s="7"/>
+      <c r="H743" s="7"/>
+      <c r="I743" s="73"/>
+    </row>
+    <row r="744" spans="1:9">
+      <c r="A744" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C744" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D744" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E744" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F744" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G744" s="7"/>
+      <c r="H744" s="7"/>
+      <c r="I744" s="73"/>
+    </row>
+    <row r="745" spans="1:9">
+      <c r="A745" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C745" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D745" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E745" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F745" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G745" s="7"/>
+      <c r="H745" s="7"/>
+      <c r="I745" s="73"/>
+    </row>
+    <row r="746" spans="1:9">
+      <c r="A746" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D746" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E746" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F746" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G746" s="7"/>
+      <c r="H746" s="7"/>
+      <c r="I746" s="73"/>
+    </row>
+    <row r="747" spans="1:9">
+      <c r="A747" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C747" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D747" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E747" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F747" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G747" s="7"/>
+      <c r="H747" s="7"/>
+      <c r="I747" s="73"/>
+    </row>
+    <row r="748" spans="1:9">
+      <c r="A748" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C748" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D748" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E748" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F748" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G748" s="7"/>
+      <c r="H748" s="7"/>
+      <c r="I748" s="73"/>
+    </row>
+    <row r="749" spans="1:9">
+      <c r="A749" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C749" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D749" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E749" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F749" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G749" s="7"/>
+      <c r="H749" s="7"/>
+      <c r="I749" s="73"/>
+    </row>
+    <row r="750" spans="1:9">
+      <c r="A750" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D750" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E750" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F750" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="G750" s="7"/>
+      <c r="H750" s="7"/>
+      <c r="I750" s="73"/>
+    </row>
+    <row r="751" spans="1:9">
+      <c r="A751" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D751" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E751" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F751" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G751" s="7"/>
+      <c r="H751" s="7"/>
+      <c r="I751" s="73"/>
+    </row>
+    <row r="752" spans="1:9">
+      <c r="A752" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C752" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D752" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E752" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F752" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G752" s="7"/>
+      <c r="H752" s="7"/>
+      <c r="I752" s="73"/>
+    </row>
+    <row r="753" spans="1:9">
+      <c r="A753" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C753" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D753" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E753" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F753" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G753" s="7"/>
+      <c r="H753" s="7"/>
+      <c r="I753" s="73"/>
+    </row>
+    <row r="754" spans="1:9">
+      <c r="A754" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C754" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D754" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E754" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F754" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G754" s="7"/>
+      <c r="H754" s="7"/>
+      <c r="I754" s="73"/>
+    </row>
+    <row r="755" spans="1:9">
+      <c r="A755" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C755" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D755" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E755" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F755" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G755" s="7"/>
+      <c r="H755" s="7"/>
+      <c r="I755" s="73"/>
+    </row>
+    <row r="756" spans="1:9">
+      <c r="A756" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C756" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D756" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E756" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F756" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G756" s="7"/>
+      <c r="H756" s="7"/>
+      <c r="I756" s="73"/>
+    </row>
+    <row r="757" spans="1:9">
+      <c r="A757" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D757" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E757" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F757" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G757" s="7"/>
+      <c r="H757" s="7"/>
+      <c r="I757" s="73"/>
+    </row>
+    <row r="758" spans="1:9">
+      <c r="A758" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D758" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E758" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F758" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G758" s="7"/>
+      <c r="H758" s="7"/>
+      <c r="I758" s="73"/>
+    </row>
+    <row r="759" spans="1:9">
+      <c r="A759" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C759" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D759" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E759" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F759" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G759" s="7"/>
+      <c r="H759" s="7"/>
+      <c r="I759" s="73"/>
+    </row>
+    <row r="760" spans="1:9">
+      <c r="A760" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C760" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D760" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E760" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F760" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G760" s="7"/>
+      <c r="H760" s="7"/>
+      <c r="I760" s="73"/>
+    </row>
+    <row r="761" spans="1:9">
+      <c r="A761" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D761" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E761" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F761" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G761" s="7"/>
+      <c r="H761" s="7"/>
+      <c r="I761" s="73"/>
+    </row>
+    <row r="762" spans="1:9">
+      <c r="A762" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D762" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E762" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F762" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G762" s="7"/>
+      <c r="H762" s="7"/>
+      <c r="I762" s="73"/>
+    </row>
+    <row r="763" spans="1:9">
+      <c r="A763" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C763" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D763" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E763" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F763" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G763" s="7"/>
+      <c r="H763" s="7"/>
+      <c r="I763" s="73"/>
+    </row>
+    <row r="764" spans="1:9">
+      <c r="A764" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D764" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E764" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F764" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G764" s="7"/>
+      <c r="H764" s="7"/>
+      <c r="I764" s="73"/>
+    </row>
+    <row r="765" spans="1:9">
+      <c r="A765" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C765" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D765" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E765" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F765" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G765" s="7"/>
+      <c r="H765" s="7"/>
+      <c r="I765" s="73"/>
+    </row>
+    <row r="766" spans="1:9">
+      <c r="A766" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D766" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E766" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F766" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G766" s="7"/>
+      <c r="H766" s="7"/>
+      <c r="I766" s="73"/>
+    </row>
+    <row r="767" spans="1:9">
+      <c r="A767" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C767" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D767" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E767" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F767" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G767" s="7"/>
+      <c r="H767" s="7"/>
+      <c r="I767" s="73"/>
+    </row>
+    <row r="768" spans="1:9">
+      <c r="A768" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D768" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E768" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F768" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G768" s="7"/>
+      <c r="H768" s="7"/>
+      <c r="I768" s="73"/>
+    </row>
+    <row r="769" spans="1:9">
+      <c r="A769" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D769" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E769" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F769" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G769" s="7"/>
+      <c r="H769" s="7"/>
+      <c r="I769" s="73"/>
+    </row>
+    <row r="770" spans="1:9">
+      <c r="A770" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D770" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E770" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F770" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G770" s="7"/>
+      <c r="H770" s="7"/>
+      <c r="I770" s="73"/>
+    </row>
+    <row r="771" spans="1:9">
+      <c r="A771" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D771" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E771" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F771" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G771" s="7"/>
+      <c r="H771" s="7"/>
+      <c r="I771" s="73"/>
+    </row>
+    <row r="772" spans="1:9">
+      <c r="A772" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D772" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E772" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F772" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G772" s="7"/>
+      <c r="H772" s="7"/>
+      <c r="I772" s="73"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23180,6 +25936,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -23317,22 +26088,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23348,28 +26128,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5C85900D-F5CA-411B-9840-AE683A547477}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="113_{A252CA1F-02C3-4D0A-A766-005CCFA67AAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B8CD039C-0877-4D9A-8A1E-972680D02156}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -4908,9 +4908,6 @@
     <t>Erika Martinez Perez1</t>
   </si>
   <si>
-    <t>Rodirgo Gomez</t>
-  </si>
-  <si>
     <t>mario.rodriguezm@clarosv</t>
   </si>
   <si>
@@ -4924,6 +4921,9 @@
   </si>
   <si>
     <t>Guillermo Cortez</t>
+  </si>
+  <si>
+    <t>Rodrigo Gomez</t>
   </si>
 </sst>
 </file>
@@ -14704,7 +14704,7 @@
         <v>4</v>
       </c>
       <c r="F340" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G340" s="6" t="s">
         <v>97</v>
@@ -14730,8 +14730,8 @@
       <c r="E341" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F341" s="53" t="s">
-        <v>1627</v>
+      <c r="F341" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G341" s="11" t="s">
         <v>97</v>
@@ -14758,7 +14758,7 @@
         <v>4</v>
       </c>
       <c r="F342" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G342" s="6" t="s">
         <v>97</v>
@@ -14784,8 +14784,8 @@
       <c r="E343" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F343" s="53" t="s">
-        <v>1627</v>
+      <c r="F343" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G343" s="11" t="s">
         <v>97</v>
@@ -14812,7 +14812,7 @@
         <v>4</v>
       </c>
       <c r="F344" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G344" s="6" t="s">
         <v>97</v>
@@ -14838,8 +14838,8 @@
       <c r="E345" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F345" s="53" t="s">
-        <v>1627</v>
+      <c r="F345" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G345" s="11" t="s">
         <v>97</v>
@@ -14866,7 +14866,7 @@
         <v>4</v>
       </c>
       <c r="F346" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G346" s="6" t="s">
         <v>97</v>
@@ -14892,8 +14892,8 @@
       <c r="E347" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F347" s="53" t="s">
-        <v>1627</v>
+      <c r="F347" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G347" s="11" t="s">
         <v>97</v>
@@ -14920,7 +14920,7 @@
         <v>4</v>
       </c>
       <c r="F348" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G348" s="6" t="s">
         <v>97</v>
@@ -14946,8 +14946,8 @@
       <c r="E349" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F349" s="53" t="s">
-        <v>1627</v>
+      <c r="F349" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G349" s="11" t="s">
         <v>97</v>
@@ -14974,7 +14974,7 @@
         <v>4</v>
       </c>
       <c r="F350" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G350" s="6" t="s">
         <v>97</v>
@@ -15000,8 +15000,8 @@
       <c r="E351" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F351" s="53" t="s">
-        <v>1627</v>
+      <c r="F351" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G351" s="11" t="s">
         <v>97</v>
@@ -15028,7 +15028,7 @@
         <v>4</v>
       </c>
       <c r="F352" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G352" s="6" t="s">
         <v>97</v>
@@ -15054,8 +15054,8 @@
       <c r="E353" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F353" s="53" t="s">
-        <v>1627</v>
+      <c r="F353" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G353" s="11" t="s">
         <v>97</v>
@@ -15082,7 +15082,7 @@
         <v>4</v>
       </c>
       <c r="F354" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G354" s="6" t="s">
         <v>97</v>
@@ -15094,7 +15094,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="51" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B355" s="20" t="s">
         <v>94</v>
@@ -15108,8 +15108,8 @@
       <c r="E355" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F355" s="53" t="s">
-        <v>1627</v>
+      <c r="F355" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G355" s="11" t="s">
         <v>97</v>
@@ -15136,7 +15136,7 @@
         <v>4</v>
       </c>
       <c r="F356" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G356" s="6" t="s">
         <v>97</v>
@@ -15162,8 +15162,8 @@
       <c r="E357" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F357" s="53" t="s">
-        <v>1627</v>
+      <c r="F357" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G357" s="11" t="s">
         <v>97</v>
@@ -15190,7 +15190,7 @@
         <v>4</v>
       </c>
       <c r="F358" s="54" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G358" s="6" t="s">
         <v>97</v>
@@ -15216,8 +15216,8 @@
       <c r="E359" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F359" s="53" t="s">
-        <v>1627</v>
+      <c r="F359" s="54" t="s">
+        <v>1632</v>
       </c>
       <c r="G359" s="11" t="s">
         <v>97</v>
@@ -16247,7 +16247,7 @@
         <v>1558</v>
       </c>
       <c r="D397" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E397" s="57" t="s">
         <v>36</v>
@@ -16274,7 +16274,7 @@
         <v>1488</v>
       </c>
       <c r="D398" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E398" s="57" t="s">
         <v>4</v>
@@ -16301,7 +16301,7 @@
         <v>1486</v>
       </c>
       <c r="D399" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E399" s="57" t="s">
         <v>4</v>
@@ -16328,7 +16328,7 @@
         <v>1466</v>
       </c>
       <c r="D400" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E400" s="57" t="s">
         <v>4</v>
@@ -16355,7 +16355,7 @@
         <v>1293</v>
       </c>
       <c r="D401" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E401" s="57" t="s">
         <v>4</v>
@@ -16411,7 +16411,7 @@
         <v>1490</v>
       </c>
       <c r="D403" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E403" s="57" t="s">
         <v>4</v>
@@ -16438,7 +16438,7 @@
         <v>1510</v>
       </c>
       <c r="D404" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E404" s="57" t="s">
         <v>36</v>
@@ -16465,7 +16465,7 @@
         <v>103</v>
       </c>
       <c r="D405" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E405" s="57" t="s">
         <v>4</v>
@@ -16550,7 +16550,7 @@
         <v>1560</v>
       </c>
       <c r="D408" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E408" s="57" t="s">
         <v>36</v>
@@ -16606,7 +16606,7 @@
         <v>1518</v>
       </c>
       <c r="D410" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E410" s="57" t="s">
         <v>36</v>
@@ -16633,7 +16633,7 @@
         <v>1508</v>
       </c>
       <c r="D411" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E411" s="57" t="s">
         <v>36</v>
@@ -16660,7 +16660,7 @@
         <v>1512</v>
       </c>
       <c r="D412" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E412" s="57" t="s">
         <v>36</v>
@@ -16745,7 +16745,7 @@
         <v>1528</v>
       </c>
       <c r="D415" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E415" s="57" t="s">
         <v>36</v>
@@ -16830,7 +16830,7 @@
         <v>1514</v>
       </c>
       <c r="D418" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E418" s="57" t="s">
         <v>36</v>
@@ -16886,7 +16886,7 @@
         <v>1433</v>
       </c>
       <c r="D420" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E420" s="57" t="s">
         <v>4</v>
@@ -16913,7 +16913,7 @@
         <v>1464</v>
       </c>
       <c r="D421" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E421" s="57" t="s">
         <v>4</v>
@@ -16940,7 +16940,7 @@
         <v>1435</v>
       </c>
       <c r="D422" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E422" s="57" t="s">
         <v>4</v>
@@ -17054,7 +17054,7 @@
         <v>1562</v>
       </c>
       <c r="D426" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E426" s="57" t="s">
         <v>36</v>
@@ -17168,7 +17168,7 @@
         <v>543</v>
       </c>
       <c r="D430" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E430" s="57" t="s">
         <v>36</v>
@@ -17224,7 +17224,7 @@
         <v>1450</v>
       </c>
       <c r="D432" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E432" s="57" t="s">
         <v>4</v>
@@ -17251,7 +17251,7 @@
         <v>1564</v>
       </c>
       <c r="D433" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E433" s="57" t="s">
         <v>36</v>
@@ -17307,7 +17307,7 @@
         <v>1468</v>
       </c>
       <c r="D435" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E435" s="57" t="s">
         <v>4</v>
@@ -17363,7 +17363,7 @@
         <v>1470</v>
       </c>
       <c r="D437" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E437" s="57" t="s">
         <v>4</v>
@@ -17419,7 +17419,7 @@
         <v>1458</v>
       </c>
       <c r="D439" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E439" s="57" t="s">
         <v>4</v>
@@ -17446,7 +17446,7 @@
         <v>1431</v>
       </c>
       <c r="D440" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E440" s="57" t="s">
         <v>4</v>
@@ -17473,7 +17473,7 @@
         <v>1429</v>
       </c>
       <c r="D441" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E441" s="57" t="s">
         <v>4</v>
@@ -17500,7 +17500,7 @@
         <v>1472</v>
       </c>
       <c r="D442" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E442" s="57" t="s">
         <v>4</v>
@@ -17527,7 +17527,7 @@
         <v>1437</v>
       </c>
       <c r="D443" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E443" s="57" t="s">
         <v>4</v>
@@ -17554,7 +17554,7 @@
         <v>1566</v>
       </c>
       <c r="D444" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E444" s="57" t="s">
         <v>36</v>
@@ -17581,7 +17581,7 @@
         <v>1506</v>
       </c>
       <c r="D445" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E445" s="57" t="s">
         <v>36</v>
@@ -17608,7 +17608,7 @@
         <v>1532</v>
       </c>
       <c r="D446" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E446" s="57" t="s">
         <v>36</v>
@@ -17635,7 +17635,7 @@
         <v>1530</v>
       </c>
       <c r="D447" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E447" s="57" t="s">
         <v>36</v>
@@ -17691,7 +17691,7 @@
         <v>1474</v>
       </c>
       <c r="D449" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E449" s="57" t="s">
         <v>4</v>
@@ -17747,7 +17747,7 @@
         <v>1460</v>
       </c>
       <c r="D451" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E451" s="57" t="s">
         <v>4</v>
@@ -17774,7 +17774,7 @@
         <v>826</v>
       </c>
       <c r="D452" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E452" s="57" t="s">
         <v>4</v>
@@ -17801,7 +17801,7 @@
         <v>135</v>
       </c>
       <c r="D453" s="52" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E453" s="52" t="s">
         <v>36</v>
@@ -17828,7 +17828,7 @@
         <v>133</v>
       </c>
       <c r="D454" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E454" s="57" t="s">
         <v>36</v>
@@ -17855,7 +17855,7 @@
         <v>101</v>
       </c>
       <c r="D455" s="52" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E455" s="52" t="s">
         <v>36</v>
@@ -17940,7 +17940,7 @@
         <v>1476</v>
       </c>
       <c r="D458" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E458" s="57" t="s">
         <v>4</v>
@@ -17967,7 +17967,7 @@
         <v>1534</v>
       </c>
       <c r="D459" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E459" s="57" t="s">
         <v>36</v>
@@ -18052,7 +18052,7 @@
         <v>1462</v>
       </c>
       <c r="D462" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E462" s="57" t="s">
         <v>4</v>
@@ -18079,7 +18079,7 @@
         <v>1516</v>
       </c>
       <c r="D463" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E463" s="57" t="s">
         <v>36</v>
@@ -18106,7 +18106,7 @@
         <v>1452</v>
       </c>
       <c r="D464" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E464" s="57" t="s">
         <v>4</v>
@@ -18133,7 +18133,7 @@
         <v>1478</v>
       </c>
       <c r="D465" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E465" s="57" t="s">
         <v>4</v>
@@ -18160,7 +18160,7 @@
         <v>1492</v>
       </c>
       <c r="D466" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E466" s="57" t="s">
         <v>4</v>
@@ -18216,7 +18216,7 @@
         <v>1520</v>
       </c>
       <c r="D468" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E468" s="57" t="s">
         <v>36</v>
@@ -18243,7 +18243,7 @@
         <v>1494</v>
       </c>
       <c r="D469" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E469" s="57" t="s">
         <v>4</v>
@@ -18270,7 +18270,7 @@
         <v>1522</v>
       </c>
       <c r="D470" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E470" s="57" t="s">
         <v>36</v>
@@ -18326,7 +18326,7 @@
         <v>1544</v>
       </c>
       <c r="D472" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E472" s="57" t="s">
         <v>36</v>
@@ -18469,7 +18469,7 @@
         <v>1546</v>
       </c>
       <c r="D477" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E477" s="57" t="s">
         <v>36</v>
@@ -18496,7 +18496,7 @@
         <v>1439</v>
       </c>
       <c r="D478" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E478" s="57" t="s">
         <v>4</v>
@@ -18552,7 +18552,7 @@
         <v>1441</v>
       </c>
       <c r="D480" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E480" s="57" t="s">
         <v>4</v>
@@ -18693,7 +18693,7 @@
         <v>1496</v>
       </c>
       <c r="D485" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E485" s="57" t="s">
         <v>4</v>
@@ -18749,7 +18749,7 @@
         <v>1480</v>
       </c>
       <c r="D487" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E487" s="57" t="s">
         <v>4</v>
@@ -18805,7 +18805,7 @@
         <v>1498</v>
       </c>
       <c r="D489" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E489" s="57" t="s">
         <v>4</v>
@@ -18832,7 +18832,7 @@
         <v>100</v>
       </c>
       <c r="D490" s="52" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E490" s="52" t="s">
         <v>36</v>
@@ -18888,7 +18888,7 @@
         <v>1443</v>
       </c>
       <c r="D492" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E492" s="57" t="s">
         <v>4</v>
@@ -18944,7 +18944,7 @@
         <v>1504</v>
       </c>
       <c r="D494" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E494" s="57" t="s">
         <v>36</v>
@@ -18971,7 +18971,7 @@
         <v>1445</v>
       </c>
       <c r="D495" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E495" s="57" t="s">
         <v>4</v>
@@ -18998,7 +18998,7 @@
         <v>1536</v>
       </c>
       <c r="D496" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E496" s="57" t="s">
         <v>36</v>
@@ -19025,7 +19025,7 @@
         <v>1500</v>
       </c>
       <c r="D497" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E497" s="57" t="s">
         <v>4</v>
@@ -19052,7 +19052,7 @@
         <v>1548</v>
       </c>
       <c r="D498" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E498" s="57" t="s">
         <v>36</v>
@@ -19166,7 +19166,7 @@
         <v>1482</v>
       </c>
       <c r="D502" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E502" s="57" t="s">
         <v>4</v>
@@ -19309,7 +19309,7 @@
         <v>1132</v>
       </c>
       <c r="D507" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E507" s="57" t="s">
         <v>4</v>
@@ -19394,7 +19394,7 @@
         <v>1550</v>
       </c>
       <c r="D510" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E510" s="57" t="s">
         <v>36</v>
@@ -19421,7 +19421,7 @@
         <v>1524</v>
       </c>
       <c r="D511" s="52" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E511" s="57" t="s">
         <v>36</v>
@@ -19477,7 +19477,7 @@
         <v>1427</v>
       </c>
       <c r="D513" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E513" s="65" t="s">
         <v>4</v>
@@ -19504,7 +19504,7 @@
         <v>1538</v>
       </c>
       <c r="D514" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E514" s="65" t="s">
         <v>36</v>
@@ -19531,7 +19531,7 @@
         <v>1456</v>
       </c>
       <c r="D515" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E515" s="65" t="s">
         <v>4</v>
@@ -19558,7 +19558,7 @@
         <v>1552</v>
       </c>
       <c r="D516" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E516" s="57" t="s">
         <v>36</v>
@@ -19585,7 +19585,7 @@
         <v>1484</v>
       </c>
       <c r="D517" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E517" s="57" t="s">
         <v>4</v>
@@ -19612,7 +19612,7 @@
         <v>1540</v>
       </c>
       <c r="D518" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E518" s="57" t="s">
         <v>36</v>
@@ -19668,7 +19668,7 @@
         <v>1526</v>
       </c>
       <c r="D520" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E520" s="57" t="s">
         <v>36</v>
@@ -19695,7 +19695,7 @@
         <v>1454</v>
       </c>
       <c r="D521" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E521" s="57" t="s">
         <v>4</v>
@@ -19809,7 +19809,7 @@
         <v>1502</v>
       </c>
       <c r="D525" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E525" s="57" t="s">
         <v>4</v>
@@ -19894,7 +19894,7 @@
         <v>1542</v>
       </c>
       <c r="D528" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E528" s="57" t="s">
         <v>36</v>
@@ -19950,7 +19950,7 @@
         <v>1554</v>
       </c>
       <c r="D530" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E530" s="57" t="s">
         <v>36</v>
@@ -19977,7 +19977,7 @@
         <v>95</v>
       </c>
       <c r="D531" s="64" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E531" s="52" t="s">
         <v>36</v>
@@ -20033,7 +20033,7 @@
         <v>1556</v>
       </c>
       <c r="D533" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E533" s="57" t="s">
         <v>36</v>
@@ -20060,7 +20060,7 @@
         <v>1447</v>
       </c>
       <c r="D534" s="64" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E534" s="57" t="s">
         <v>4</v>
@@ -23511,7 +23511,7 @@
         <v>109</v>
       </c>
       <c r="C668" s="5" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D668" s="6" t="s">
         <v>111</v>
@@ -23682,7 +23682,7 @@
         <v>36</v>
       </c>
       <c r="F674" s="6" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G674" s="15" t="s">
         <v>97</v>
@@ -23709,7 +23709,7 @@
         <v>36</v>
       </c>
       <c r="F675" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G675" s="14" t="s">
         <v>97</v>
@@ -23736,7 +23736,7 @@
         <v>36</v>
       </c>
       <c r="F676" s="6" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G676" s="15" t="s">
         <v>97</v>
@@ -23763,7 +23763,7 @@
         <v>36</v>
       </c>
       <c r="F677" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G677" s="14" t="s">
         <v>97</v>
@@ -23790,7 +23790,7 @@
         <v>36</v>
       </c>
       <c r="F678" s="6" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G678" s="15" t="s">
         <v>97</v>
@@ -23817,7 +23817,7 @@
         <v>36</v>
       </c>
       <c r="F679" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G679" s="14" t="s">
         <v>97</v>
@@ -26555,6 +26555,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -26692,22 +26707,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26723,28 +26747,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="113_{36CFE76D-187E-4464-B363-7BD286C1C351}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{27DB1791-83B9-45AC-950F-087DD2A6A1DF}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="113_{6C874331-FAA1-4795-96B8-7F7BC6A3A28C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{68F4562D-9057-4DAD-B46F-8E9D1E53F9C7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -18241,7 +18241,7 @@
         <v>321</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C468" s="5" t="s">
         <v>1620</v>
@@ -23014,8 +23014,8 @@
       <c r="A644" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="B644" s="17" t="s">
-        <v>93</v>
+      <c r="B644" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="C644" s="17" t="s">
         <v>1652</v>
@@ -23042,7 +23042,7 @@
         <v>1561</v>
       </c>
       <c r="B645" s="16" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C645" s="16" t="s">
         <v>1653</v>
@@ -23069,7 +23069,7 @@
         <v>317</v>
       </c>
       <c r="B646" s="17" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C646" s="17" t="s">
         <v>318</v>
@@ -23095,8 +23095,8 @@
       <c r="A647" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="B647" s="16" t="s">
-        <v>93</v>
+      <c r="B647" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="C647" s="16" t="s">
         <v>1654</v>
@@ -23122,8 +23122,8 @@
       <c r="A648" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="B648" s="17" t="s">
-        <v>93</v>
+      <c r="B648" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="C648" s="17" t="s">
         <v>310</v>
@@ -26595,176 +26595,176 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1" display="mailto:angelg.mejia@clarosv" xr:uid="{9CA9E569-F6DB-4886-9BCE-7E367E156D47}"/>
-    <hyperlink ref="A17" r:id="rId2" display="mailto:camila.pena@clarosv" xr:uid="{CC8C4273-2585-430C-ADB0-67D7DC53C887}"/>
-    <hyperlink ref="A19" r:id="rId3" display="mailto:carmen.turcios@clarosv" xr:uid="{A0C4EFAA-BEDF-407E-A9D6-BCB3588F57FC}"/>
-    <hyperlink ref="A21" r:id="rId4" display="mailto:christian.garciag@clarosv" xr:uid="{36A46822-7CE8-40C9-A51B-07E7A1F44B70}"/>
-    <hyperlink ref="A22" r:id="rId5" display="mailto:cindy.albanes@clarosv" xr:uid="{E2961F69-12E2-4D39-B40B-0A3D56EC72CD}"/>
-    <hyperlink ref="A24" r:id="rId6" display="mailto:daniel.daguilar@clarosv" xr:uid="{BDD90DBC-72DD-417E-B044-B7DF511D704B}"/>
-    <hyperlink ref="A25" r:id="rId7" display="mailto:daniela.cerritos@clarosv" xr:uid="{95B127DF-E161-444F-9DE5-5863BB2B8B00}"/>
-    <hyperlink ref="A27" r:id="rId8" display="mailto:daniela.olivares@clarosv" xr:uid="{09EAE8A2-3E67-4BE1-A125-B9F9D22AB36E}"/>
-    <hyperlink ref="A28" r:id="rId9" display="mailto:debbie.castilloc@clarosv" xr:uid="{94860CCD-946A-420C-AF57-0F31FB13E127}"/>
-    <hyperlink ref="A29" r:id="rId10" display="mailto:duran.rolando@clarosv" xr:uid="{FA61CA8B-1D69-4480-A617-564293205756}"/>
-    <hyperlink ref="A30" r:id="rId11" display="mailto:edwin.grijalvah@clarosv" xr:uid="{800DEAAC-0F16-4E48-9C1F-5E9BC2B18DC1}"/>
-    <hyperlink ref="A33" r:id="rId12" display="mailto:ernesto.alopez@clarosv" xr:uid="{E4CCEC9F-B211-4ADD-A970-989259E2B827}"/>
-    <hyperlink ref="A35" r:id="rId13" display="mailto:geisel.rosales@clarosv" xr:uid="{CDD3C118-C043-4279-B38A-07A723A9DCB8}"/>
-    <hyperlink ref="A36" r:id="rId14" display="mailto:gracia.bonilla@clarosv" xr:uid="{B4CA0BE7-9542-42AE-A1C1-0B45B9578364}"/>
-    <hyperlink ref="A37" r:id="rId15" display="mailto:harold.diaz@clarosv" xr:uid="{9AF67EB1-0BA2-4F60-AE8B-C2BCDA4F4A07}"/>
-    <hyperlink ref="A40" r:id="rId16" display="mailto:irving.alvarez@clarosv" xr:uid="{2FCE2C46-EBCF-48C5-B834-C545F1808D3A}"/>
-    <hyperlink ref="A44" r:id="rId17" display="mailto:josue.diazp@clarosv" xr:uid="{B8D6708C-CCD1-43BB-A280-F0EC36B38BC8}"/>
-    <hyperlink ref="A45" r:id="rId18" display="mailto:juanm.ortiz@clarosv" xr:uid="{6728D24A-2B33-4264-9EAF-11744792798D}"/>
-    <hyperlink ref="A46" r:id="rId19" display="mailto:julissa.cardona@clarosv" xr:uid="{5ABBE0AC-6CAD-4806-9895-AE8D41E90BC8}"/>
-    <hyperlink ref="A48" r:id="rId20" display="mailto:karen.chacon@clarosv" xr:uid="{A0230BB2-7DCC-4793-B6B8-28736919D59A}"/>
-    <hyperlink ref="A49" r:id="rId21" display="mailto:katherine.calderonh@clarosv" xr:uid="{B3FFB406-0579-498D-AEA9-6B99D4EB69CB}"/>
-    <hyperlink ref="A50" r:id="rId22" display="mailto:kathya.molina@clarosv" xr:uid="{33D78EFE-BC39-4A22-8980-5530A365576A}"/>
-    <hyperlink ref="A51" r:id="rId23" display="mailto:kevin.navarro@clarosv" xr:uid="{0DC3B40C-36E9-4081-8C0F-E1634DED8116}"/>
-    <hyperlink ref="A52" r:id="rId24" display="mailto:kevin.serranob@clarosv" xr:uid="{102F7F3B-21BA-4002-BC38-1EA241806813}"/>
-    <hyperlink ref="A53" r:id="rId25" display="mailto:laura.ortizf@clarosv" xr:uid="{D15404EE-6D69-446D-89E3-D2B1B234A0FA}"/>
-    <hyperlink ref="A54" r:id="rId26" display="mailto:lesly.romerog@clarosv" xr:uid="{34CE1430-9A86-46F1-B23E-4EABC0AE8C8F}"/>
-    <hyperlink ref="A57" r:id="rId27" display="mailto:maria.quintanilla@clarosv" xr:uid="{41E8D03C-2A29-4D6C-A216-2CC7EDB17BFE}"/>
-    <hyperlink ref="A59" r:id="rId28" display="mailto:marisela.santos@clarosv" xr:uid="{62C9635F-382B-4E76-977D-1BB5AEAF1D2A}"/>
-    <hyperlink ref="A60" r:id="rId29" display="mailto:marlon.rivera@clarosv" xr:uid="{E45827BA-0F4B-4719-BD08-82FDCE9996B1}"/>
-    <hyperlink ref="A62" r:id="rId30" display="mailto:miguel.arevalo@clarosv" xr:uid="{8F35A1A5-6986-48CC-8462-47BA9B1B00B6}"/>
-    <hyperlink ref="A63" r:id="rId31" display="mailto:milenal.ceron@clarosv" xr:uid="{242B5058-1278-4F8A-BF83-B6A5B74AE22E}"/>
-    <hyperlink ref="A64" r:id="rId32" display="mailto:mireya.guirola@clarosv" xr:uid="{F124939E-3589-4217-AB0A-2F395A69C26E}"/>
-    <hyperlink ref="A65" r:id="rId33" display="mailto:mynoru.garcia@clarosv" xr:uid="{9C00075B-D3B0-49AA-A9C6-2D97CB19AB99}"/>
-    <hyperlink ref="A66" r:id="rId34" display="mailto:nestor.maldonador@clarosv" xr:uid="{37AE6771-13FD-4365-A83B-2A7F3D0A76D0}"/>
-    <hyperlink ref="A67" r:id="rId35" display="mailto:noe.castillo@clarosv" xr:uid="{97E712B9-E8AF-4E49-BF28-AE3D98555A27}"/>
-    <hyperlink ref="A69" r:id="rId36" display="mailto:patricia.miranda@clarosv" xr:uid="{EB79BDEC-72AD-4D3D-B294-B26E04CFC585}"/>
-    <hyperlink ref="A72" r:id="rId37" display="mailto:rolandoa.pineda@clarosv" xr:uid="{401ED7F3-4447-4583-8F9D-33C9F38CBF64}"/>
-    <hyperlink ref="A73" r:id="rId38" display="mailto:roxana.valencia@clarosv" xr:uid="{6608E67A-F30F-459E-A182-0929C09BDDAF}"/>
-    <hyperlink ref="A74" r:id="rId39" display="mailto:samuel.duran@clarosv" xr:uid="{114E83BB-DC92-4E01-B891-58E30C5D06BB}"/>
-    <hyperlink ref="A77" r:id="rId40" display="mailto:tommy.ramos@clarosv" xr:uid="{2AAFE6BC-E732-4E4C-8998-45FB0A0892D3}"/>
-    <hyperlink ref="A81" r:id="rId41" display="mailto:wilfredo.floresm@clarosv" xr:uid="{50FF491E-6492-40C6-B6B9-0B87A6A95439}"/>
-    <hyperlink ref="A86" r:id="rId42" display="mailto:alexandrap.melchor@clarosv" xr:uid="{E41D4BF9-CADF-443B-80BF-DC9BDFB83EBB}"/>
-    <hyperlink ref="A88" r:id="rId43" display="mailto:andreab.reyes@clarosv" xr:uid="{B59F0106-BEF7-439F-A2A1-AB4EE2BD4685}"/>
-    <hyperlink ref="A89" r:id="rId44" display="mailto:aquino.wilbert@clarosv" xr:uid="{42780736-FCCB-450C-9441-C9BA2C22B794}"/>
-    <hyperlink ref="A92" r:id="rId45" display="mailto:bessy.olivia@clarosv" xr:uid="{385CAA4E-6A2D-4F4D-8059-FA04590CE133}"/>
-    <hyperlink ref="A99" r:id="rId46" display="mailto:carlosa.flores@clarosv" xr:uid="{C1EE99D3-9932-46A3-98B0-55E349F684A1}"/>
-    <hyperlink ref="A101" r:id="rId47" display="mailto:carlosh.villalta@clarosv" xr:uid="{DA00D72D-4F94-4AAF-822D-820CBCD84E57}"/>
-    <hyperlink ref="A104" r:id="rId48" display="mailto:clara.vasquez@clarosv" xr:uid="{F89546A2-E5E5-4E1E-8F52-6025ABA49EAE}"/>
-    <hyperlink ref="A113" r:id="rId49" display="mailto:estefanyy.fabian@clarosv" xr:uid="{91B8B742-772F-42B3-8461-2C4958907447}"/>
-    <hyperlink ref="A135" r:id="rId50" display="mailto:josej.zelaya@clarosv" xr:uid="{A5DC8BD1-771B-43EC-B1DD-08C2ACA504DF}"/>
-    <hyperlink ref="A150" r:id="rId51" display="mailto:luiss.aguirre@clarosv" xr:uid="{0ED15368-B023-4DB4-9E76-70F9C01E9F31}"/>
-    <hyperlink ref="A158" r:id="rId52" display="mailto:michelle.perez@clarosv" xr:uid="{076B9531-F36B-4507-B6F7-A396406402F3}"/>
-    <hyperlink ref="A159" r:id="rId53" display="mailto:milton.barraza@clarosv" xr:uid="{DF719352-2851-48E8-87CD-3833F46437EB}"/>
-    <hyperlink ref="A162" r:id="rId54" display="mailto:op16@clarosv" xr:uid="{C2398008-23B3-4A4D-BC97-DB79D02518DF}"/>
-    <hyperlink ref="A163" r:id="rId55" display="mailto:op17@clarosv" xr:uid="{B46017B6-1533-490D-9952-04D29B57B388}"/>
-    <hyperlink ref="A164" r:id="rId56" display="mailto:op18@clarosv" xr:uid="{A45E6E32-A61C-4E36-8D19-2C9D001FE074}"/>
-    <hyperlink ref="A173" r:id="rId57" display="mailto:sandray.chicas@clarosv" xr:uid="{3FA812C3-C5C6-4D2B-9A85-363DE325E642}"/>
-    <hyperlink ref="A175" r:id="rId58" display="mailto:solano.vanessa@clarosv" xr:uid="{221329CC-C556-432E-99F7-83632104ECC7}"/>
-    <hyperlink ref="A182" r:id="rId59" display="mailto:camila.diaz@clarosv" xr:uid="{86E73B53-7576-47D9-95E3-4C423ED253AC}"/>
-    <hyperlink ref="A183" r:id="rId60" display="mailto:carlos.hernandezr@clarosv" xr:uid="{64F3DC06-12E3-45D3-ACE6-B6F460444165}"/>
-    <hyperlink ref="A184" r:id="rId61" display="mailto:christian.rodriguezm@clarosv" xr:uid="{66FFE42B-20D7-4FDF-8966-86AC78C6E246}"/>
-    <hyperlink ref="A185" r:id="rId62" display="mailto:cristhian.flores@clarosv" xr:uid="{4BA076C2-0DC8-44B1-ACD2-2B2A667469C7}"/>
-    <hyperlink ref="A186" r:id="rId63" display="mailto:cristian.tobarc@clarosv" xr:uid="{5E3A8191-A8A1-4F3E-91B0-B2040BACBC8D}"/>
-    <hyperlink ref="A187" r:id="rId64" display="mailto:karen.perezn@clarosv" xr:uid="{6BBAF703-2B7C-4491-878B-3E01AE727A22}"/>
-    <hyperlink ref="A194" r:id="rId65" display="mailto:alexis.medina@clarosv" xr:uid="{CBDB3472-FC8C-4FD7-966A-9021DC8C5D29}"/>
-    <hyperlink ref="A195" r:id="rId66" display="mailto:ashleys.martinez@clarosv" xr:uid="{F42825C7-C5D7-46D9-A5B2-422760E1C706}"/>
-    <hyperlink ref="A196" r:id="rId67" display="mailto:edwin.arivas@clarosv" xr:uid="{3D1C92B5-FCB8-4A1A-9CF7-D28E1E06F1E3}"/>
-    <hyperlink ref="A197" r:id="rId68" display="mailto:elizabeth.moran@clarosv" xr:uid="{817070B6-BFA6-47BD-8E33-42A55C438EF7}"/>
-    <hyperlink ref="A198" r:id="rId69" display="mailto:gladys.perez@clarosv" xr:uid="{0521ECA6-A11C-4699-A3C9-21CC8585C2A5}"/>
-    <hyperlink ref="A199" r:id="rId70" display="mailto:karenm.floresm@clarosv" xr:uid="{16D5AD46-AB5C-479A-A64E-C5165E4EAC4E}"/>
-    <hyperlink ref="A200" r:id="rId71" display="mailto:kathya.aguilar@clarosv" xr:uid="{3DBCB10D-B38E-431E-A2E7-97DDA2E716BC}"/>
-    <hyperlink ref="A201" r:id="rId72" display="mailto:maria.moranc@clarosv" xr:uid="{9232D7DE-7D2A-4B3C-BB22-9E5AD19BF7FD}"/>
-    <hyperlink ref="A205" r:id="rId73" display="mailto:raquel.montoya@clarosv" xr:uid="{C2DBFAAD-CED2-4F95-B37A-F74723CA85F4}"/>
-    <hyperlink ref="A221" r:id="rId74" display="mailto:claudiag.escobar@clarosv" xr:uid="{B3869441-1C36-40CA-A5BA-8F0AC8BA092B}"/>
-    <hyperlink ref="A253" r:id="rId75" display="mailto:benjamin.jovel@clarosv" xr:uid="{6A4E69FA-19AC-4A21-9138-9B7190F3F3CE}"/>
-    <hyperlink ref="A254" r:id="rId76" display="mailto:carlos.dmolina@clarosv" xr:uid="{E5557F58-D632-46AF-BFE0-DF89A73FD0D2}"/>
-    <hyperlink ref="A257" r:id="rId77" display="mailto:douglas.molina@clarosv" xr:uid="{2E5B381B-9D4A-4FC6-80C3-C0A5418C6174}"/>
-    <hyperlink ref="A258" r:id="rId78" display="mailto:eduardoa.moran@clarosv" xr:uid="{1FB6EEE4-011C-4E63-B478-A9875884B3B9}"/>
-    <hyperlink ref="A268" r:id="rId79" display="mailto:oscar.rgomez@clarosv" xr:uid="{70D65CA1-0EA7-4BB9-84D4-193A8C87ED7E}"/>
-    <hyperlink ref="A269" r:id="rId80" display="mailto:oscare.cruz@clarosv" xr:uid="{5D2DCF75-BC42-4F76-9A87-4719239763DE}"/>
-    <hyperlink ref="A271" r:id="rId81" display="mailto:yaneth.ramos@clarosv" xr:uid="{08DCD171-4CBA-4C04-BE3A-267D2733AA9A}"/>
-    <hyperlink ref="A283" r:id="rId82" display="mailto:danielag.pena@clarosv" xr:uid="{84862E54-85F4-49C6-843E-97380DA311BA}"/>
-    <hyperlink ref="A301" r:id="rId83" display="mailto:maira.gil@clarosv" xr:uid="{BAD684DD-7ED6-406E-9921-B5BD01E2DF44}"/>
-    <hyperlink ref="A302" r:id="rId84" display="mailto:marjorie.guardado@clarosv" xr:uid="{77A536C2-8DC5-4F9C-AEF3-DF04B9C36760}"/>
-    <hyperlink ref="A340" r:id="rId85" display="mailto:jorgem.serrano@clarosv" xr:uid="{6EBBFF46-A396-49FE-87AF-33856F1A9D19}"/>
-    <hyperlink ref="A348" r:id="rId86" display="mailto:iveth.cuadra@clarosv" xr:uid="{864E9C35-BEBD-4BDD-9C53-1DD2A5FFD545}"/>
-    <hyperlink ref="A353" r:id="rId87" display="mailto:carlosd.tobar@clarosv" xr:uid="{7F3FFA8C-8A48-431D-ABB8-9260C9C0CAC8}"/>
-    <hyperlink ref="A354" r:id="rId88" display="mailto:hazela.ramirez@clarosv" xr:uid="{61357F7E-1F7D-45E2-B596-4340EF81A36F}"/>
-    <hyperlink ref="A356" r:id="rId89" display="mailto:jonathan.ahernandez@clarosv" xr:uid="{9A71CA2C-68D0-4212-8228-BC9F271BFDF6}"/>
-    <hyperlink ref="A358" r:id="rId90" display="mailto:katherine.reynosa@clarosv" xr:uid="{D537FCEB-7FBD-47EC-BD45-82388CF4383A}"/>
-    <hyperlink ref="A399" r:id="rId91" display="mailto:marielos.hernandez@clarosv" xr:uid="{611A58F6-EE2D-4780-AC1A-624D22C18D6C}"/>
-    <hyperlink ref="A411" r:id="rId92" display="mailto:byron.marroquin@clarosv" xr:uid="{94E0571B-2751-4DC0-BDC5-6F4C7EF84D5F}"/>
-    <hyperlink ref="A412" r:id="rId93" display="mailto:cesar.elias@clarosv" xr:uid="{E324CC77-0586-4453-9C63-24FCE2DCF4A0}"/>
-    <hyperlink ref="A413" r:id="rId94" display="mailto:christian.mendoza@clarosv" xr:uid="{0D3C839C-1189-4790-85AE-39473F07B8AD}"/>
-    <hyperlink ref="A414" r:id="rId95" display="mailto:javier.ruiz@clarosv" xr:uid="{D34EFEEF-0B3A-47B8-9AAC-4329481FE775}"/>
-    <hyperlink ref="A415" r:id="rId96" display="mailto:jennifer.landaverde@clarosv" xr:uid="{D828AC2B-D3C0-4ECD-A357-6A10D797D9AF}"/>
-    <hyperlink ref="A416" r:id="rId97" display="mailto:miriam.martinez@clarosv" xr:uid="{5FBAE8E3-5207-4BC6-8DB0-4C8FBF43CFB9}"/>
-    <hyperlink ref="A417" r:id="rId98" display="mailto:rebeca.caballero@clarosv" xr:uid="{3D7CFC6A-F167-4E26-9146-6EB3D730B0EB}"/>
-    <hyperlink ref="A418" r:id="rId99" display="mailto:vladimir.estradav@clarosv" xr:uid="{DA22349F-68AC-4920-B8B6-A443DFA291CD}"/>
-    <hyperlink ref="A424" r:id="rId100" display="mailto:melendezm.juan@clarosv" xr:uid="{21A1A7A1-3467-4B55-BD11-8018F02539F2}"/>
-    <hyperlink ref="A425" r:id="rId101" display="mailto:rivera_marvin@clarosv" xr:uid="{022E653C-5AFC-4E52-8CA0-B6EF15C204BC}"/>
-    <hyperlink ref="A426" r:id="rId102" display="mailto:rafaela.figueroa@clarosv" xr:uid="{3AE671B3-6F5E-475D-B692-81002B577F82}"/>
-    <hyperlink ref="A428" r:id="rId103" display="mailto:gabriela.ocruz@clarosv" xr:uid="{53DAC44D-9FDD-46CA-8348-51267C420DED}"/>
-    <hyperlink ref="A430" r:id="rId104" display="mailto:katherine.bolainez@clarosv" xr:uid="{8FC3AA0A-4704-4E59-8C0A-7B677AC4160C}"/>
-    <hyperlink ref="A432" r:id="rId105" display="mailto:pineda.gabriela@clarosv" xr:uid="{0CB3833C-6A11-4F79-979F-E769A05F6930}"/>
-    <hyperlink ref="A433" r:id="rId106" display="mailto:veronica.campos@clarosv" xr:uid="{7F50A440-C160-4F75-9113-4A8C56DAFF31}"/>
-    <hyperlink ref="A436" r:id="rId107" display="mailto:alexander.orellanap@clarosv" xr:uid="{80350043-2748-4537-ACAD-EECC30AB4964}"/>
-    <hyperlink ref="A441" r:id="rId108" display="mailto:antonio.ponce@clarosv" xr:uid="{53042835-6C9A-4D20-B45F-E8C4B4FDB071}"/>
-    <hyperlink ref="A443" r:id="rId109" display="mailto:blanca.avelarm@clarosv" xr:uid="{36A1C43C-5570-4D8D-A553-CC99D4182098}"/>
-    <hyperlink ref="A444" r:id="rId110" display="mailto:brenda.turcios@clarosv" xr:uid="{0C10DC20-F149-43BC-87FD-22D892B75CF0}"/>
-    <hyperlink ref="A445" r:id="rId111" display="mailto:daniel.hernandezs@clarosv" xr:uid="{3573ADC5-EB03-4782-A71B-1FBE177600FB}"/>
-    <hyperlink ref="A448" r:id="rId112" display="mailto:ezequiel.lopez@clarosv" xr:uid="{9BC34C70-C07C-4CAE-97E8-FEE797732840}"/>
-    <hyperlink ref="A449" r:id="rId113" display="mailto:jessica.valencia@clarosv" xr:uid="{437AC3F0-A77C-4223-A3B9-B5B091D9172D}"/>
-    <hyperlink ref="A451" r:id="rId114" display="mailto:josem.ayala@clarosv" xr:uid="{F508AD5A-8506-49EE-9546-CD0A64B907C9}"/>
-    <hyperlink ref="A454" r:id="rId115" display="mailto:kathya.guerrero@clarosv" xr:uid="{A9650AC9-7F02-4D91-B14F-B6DF63C9D334}"/>
-    <hyperlink ref="A456" r:id="rId116" display="mailto:mario.jovel@clarosv" xr:uid="{DCE6DDA6-9121-4631-AA40-B4036111B41F}"/>
-    <hyperlink ref="A457" r:id="rId117" display="mailto:op12@clarosv" xr:uid="{6D6AB674-199B-49A7-B63C-4D9D6FCAC4B4}"/>
-    <hyperlink ref="A458" r:id="rId118" display="mailto:orellana.luism@clarosv" xr:uid="{706E0EC0-49D3-4688-B1AA-F9B4EC3DB051}"/>
-    <hyperlink ref="A459" r:id="rId119" display="mailto:orellana.olgam@clarosv" xr:uid="{F6FB2A54-995C-452F-AC5F-E64E5DF09301}"/>
-    <hyperlink ref="A460" r:id="rId120" display="mailto:oscar.sarceno@clarosv" xr:uid="{07BA6DF2-6048-406A-94C7-4A4FBB1A863D}"/>
-    <hyperlink ref="A462" r:id="rId121" display="mailto:soniae.mendez@clarosv" xr:uid="{446CA39E-4AFB-45F4-A14C-B0B4C7BB4D53}"/>
-    <hyperlink ref="A464" r:id="rId122" display="mailto:susana.valiente@clarosv" xr:uid="{CCD3B7E8-FAA7-492C-BC54-18D3DE29A72B}"/>
-    <hyperlink ref="A465" r:id="rId123" display="mailto:wendys.mejia@clarosv" xr:uid="{8EB5B300-4F4F-470E-8B23-1E5BDBBA2BFC}"/>
-    <hyperlink ref="A466" r:id="rId124" display="mailto:xiomara.mejia@clarosv" xr:uid="{75294511-DDCE-4644-9944-27FB40E4A1DD}"/>
-    <hyperlink ref="A467" r:id="rId125" display="mailto:alejandran.blancom@clarosv" xr:uid="{73A970B1-5B90-43EA-A399-D1D0A15BC56E}"/>
-    <hyperlink ref="A470" r:id="rId126" display="mailto:henry.romero@clarosv" xr:uid="{F015E06F-BA9E-4232-8D8C-F8450333DD75}"/>
-    <hyperlink ref="A472" r:id="rId127" display="mailto:ambara.maradiaga@clarosv" xr:uid="{BC28BA11-AF10-4B1A-A868-97B3D4A9BA0B}"/>
-    <hyperlink ref="A476" r:id="rId128" display="mailto:gabrielaa.amarin@clarosv" xr:uid="{C6013A5B-8496-4028-811E-D7133CBDE0CD}"/>
-    <hyperlink ref="A478" r:id="rId129" display="mailto:luis.orellana@clarosv" xr:uid="{367003E9-B8F9-4D95-9260-53E5AC8A72D4}"/>
-    <hyperlink ref="A479" r:id="rId130" display="mailto:william.murcia@clarosv" xr:uid="{3BD66E9D-1683-498C-B3A7-0D14D82E9BAD}"/>
-    <hyperlink ref="A630" r:id="rId131" display="mailto:nasser.zablash@clarosv" xr:uid="{425CBEB5-6689-4B50-B0C1-73E801FCEECA}"/>
-    <hyperlink ref="A645" r:id="rId132" display="mailto:erika.pmartinez2@clarosv" xr:uid="{54CA9408-4DFE-45EF-80E9-31C04F139154}"/>
-    <hyperlink ref="A650" r:id="rId133" display="mailto:adriana.raudag@clarosv" xr:uid="{F17EF7A3-818C-40C2-BC9E-6B7875AE108F}"/>
-    <hyperlink ref="A651" r:id="rId134" display="mailto:alejandram.flores@clarosv" xr:uid="{B4910BF3-93B3-43CC-945B-4DD0CA24C6AE}"/>
-    <hyperlink ref="A657" r:id="rId135" display="mailto:angel.monterrosag@clarosv" xr:uid="{865D4263-CBD2-49FC-80A6-4C3BB0AEC4C9}"/>
-    <hyperlink ref="A658" r:id="rId136" display="mailto:angel.reyesh@clarosv" xr:uid="{7EEB4535-F012-4EBA-ADDF-8F73497AA930}"/>
-    <hyperlink ref="A661" r:id="rId137" display="mailto:belen.avedano@clarosv" xr:uid="{8881C140-19F4-4C86-86B5-6A450464CDBB}"/>
-    <hyperlink ref="A667" r:id="rId138" display="mailto:carlos.eflores@clarosv" xr:uid="{EC39A50B-49D6-42E1-87F0-9EF356BE117E}"/>
-    <hyperlink ref="A668" r:id="rId139" display="mailto:carlos.mguzman@clarosv" xr:uid="{85EE54FD-467C-4CDA-BC6A-B1552320DA27}"/>
-    <hyperlink ref="A673" r:id="rId140" display="mailto:clara.lzavaleta@clarosv" xr:uid="{0BBF15A4-0C9F-4BF9-8E35-651E6491137C}"/>
-    <hyperlink ref="A674" r:id="rId141" display="mailto:claudia.perez@clarosv" xr:uid="{30E6DCE0-7010-4644-9C9C-F380FFE6EF8B}"/>
-    <hyperlink ref="A677" r:id="rId142" display="mailto:daniel.moran@clarosv" xr:uid="{5DFA9648-B064-44F1-9711-74B29DBAA175}"/>
-    <hyperlink ref="A680" r:id="rId143" display="mailto:davida.hernandezm@clarosv" xr:uid="{A4E112B3-526A-4603-8189-E2C99B27F39E}"/>
-    <hyperlink ref="A682" r:id="rId144" display="mailto:derek.caballero@clarosv" xr:uid="{651AFB4B-B9F0-4DA2-87E4-D633CB0C5B62}"/>
-    <hyperlink ref="A689" r:id="rId145" display="mailto:edwin.madrid@clarosv" xr:uid="{2C20781E-81E5-4691-94D8-CE3528DE2768}"/>
-    <hyperlink ref="A691" r:id="rId146" display="mailto:emilio.martineza@clarosv" xr:uid="{9C86F419-3802-4B90-83E2-659EFBB38B6E}"/>
-    <hyperlink ref="A692" r:id="rId147" display="mailto:estefany.mendezg@clarosv" xr:uid="{180DF06C-D08D-4B2C-ABDD-AB77546D451E}"/>
-    <hyperlink ref="A697" r:id="rId148" display="mailto:gilma.barillas@clarosv" xr:uid="{2B0574C5-5435-4D38-ACFF-3767C414FB0D}"/>
-    <hyperlink ref="A703" r:id="rId149" display="mailto:henry.matute@clarosv" xr:uid="{7A30597C-A4DC-44B7-8420-35B7C2007811}"/>
-    <hyperlink ref="A705" r:id="rId150" display="mailto:iris.graciasz@clarosv" xr:uid="{F7CBB5F6-06AB-4A00-ABF3-A35216AC74E9}"/>
-    <hyperlink ref="A706" r:id="rId151" display="mailto:izamar.perezm@clarosv" xr:uid="{11DB463F-DD1E-4996-9F1A-ADC30C9C09D3}"/>
-    <hyperlink ref="A707" r:id="rId152" display="mailto:jackelyn.guevarap@clarosv" xr:uid="{015C34E3-1947-462E-9658-94BE5D2F8397}"/>
-    <hyperlink ref="A710" r:id="rId153" display="mailto:jasmin.branr@clarosv" xr:uid="{3E23043B-6A9C-44C0-B161-911021BE2BDB}"/>
-    <hyperlink ref="A711" r:id="rId154" display="mailto:joaquin.lizamam@clarosv" xr:uid="{6E0CA9DB-93A6-4FFB-9583-E611799E7114}"/>
-    <hyperlink ref="A714" r:id="rId155" display="mailto:jose.ayalam@clarosv" xr:uid="{3A067F65-BF3D-46E8-984C-9C477C65755C}"/>
-    <hyperlink ref="A724" r:id="rId156" display="mailto:juan.amartinez@clarosv" xr:uid="{D0F04B73-CE60-4E83-B758-60B625B27F17}"/>
-    <hyperlink ref="A729" r:id="rId157" display="mailto:karlav.hernandez@clarosv" xr:uid="{CC7DC7D8-BCEE-42AF-ABD0-68989DB738F6}"/>
-    <hyperlink ref="A735" r:id="rId158" display="mailto:kevin.contrerass@clarosv" xr:uid="{2375866D-DF57-4857-92C0-7A2C13B9DCE8}"/>
-    <hyperlink ref="A737" r:id="rId159" display="mailto:kevin.menjivarh@clarosv" xr:uid="{6272432A-AF2C-4613-8CDD-1FF8CAF645BD}"/>
-    <hyperlink ref="A739" r:id="rId160" display="mailto:linda.rivasg@clarosv" xr:uid="{D6DE6DB1-D5EE-421D-940F-BB9185CAED6D}"/>
-    <hyperlink ref="A741" r:id="rId161" display="mailto:maria.alfaro@clarosv" xr:uid="{6D877F49-933E-4395-981D-3C3265B8DA34}"/>
-    <hyperlink ref="A750" r:id="rId162" display="mailto:marjorie.ortiza@clarosv" xr:uid="{256A109F-8D8E-4775-82F0-35EF33907311}"/>
-    <hyperlink ref="A752" r:id="rId163" display="mailto:marlong.garcia@clarosv" xr:uid="{F4CA7A1A-54CC-486B-9D37-89194A738B01}"/>
-    <hyperlink ref="A762" r:id="rId164" display="mailto:nelsonv.rivera@clarosv" xr:uid="{A124D85D-CE03-4501-A53B-BC7ED62174F0}"/>
-    <hyperlink ref="A764" r:id="rId165" display="mailto:oscars.bonilla@clarosv" xr:uid="{EC324752-70A3-44E1-86B7-8D8A1CC116D2}"/>
-    <hyperlink ref="A770" r:id="rId166" display="mailto:ricardo.pleitezh@clarosv" xr:uid="{73372756-3806-49D5-81C5-9736C3B4F505}"/>
-    <hyperlink ref="A772" r:id="rId167" display="mailto:rodrigoa.martinez@clarosv" xr:uid="{86B5C04D-495F-4063-AFA3-7C5AC18DA795}"/>
-    <hyperlink ref="A773" r:id="rId168" display="mailto:rosaura.garcia@clarosv" xr:uid="{80BE5D08-720F-4D4B-8D19-C83B4580033E}"/>
-    <hyperlink ref="A780" r:id="rId169" display="mailto:vladimiran.margueiz@clarosv" xr:uid="{319C0FEC-D9E1-4EF5-8FC3-FFCF81E876F5}"/>
-    <hyperlink ref="A783" r:id="rId170" display="mailto:zuleyma.mendozar@clarosv" xr:uid="{9E7320AC-914F-4D76-81BA-E34C0F7BF012}"/>
+    <hyperlink ref="A15" r:id="rId1" display="mailto:angelg.mejia@clarosv" xr:uid="{8927B62C-5642-4E37-8541-133F553046D7}"/>
+    <hyperlink ref="A17" r:id="rId2" display="mailto:camila.pena@clarosv" xr:uid="{427A8986-CAAE-4302-B1D6-E64545EDE782}"/>
+    <hyperlink ref="A19" r:id="rId3" display="mailto:carmen.turcios@clarosv" xr:uid="{3537DBED-0563-404F-B7A5-644D6EEE1371}"/>
+    <hyperlink ref="A21" r:id="rId4" display="mailto:christian.garciag@clarosv" xr:uid="{B83C06A9-D3D7-4432-BF6C-2BA493B90738}"/>
+    <hyperlink ref="A22" r:id="rId5" display="mailto:cindy.albanes@clarosv" xr:uid="{D17673EA-64B0-4585-AE4A-C6874EEF1742}"/>
+    <hyperlink ref="A24" r:id="rId6" display="mailto:daniel.daguilar@clarosv" xr:uid="{EE7223F1-273D-4CB1-9873-A2984B0B34C6}"/>
+    <hyperlink ref="A25" r:id="rId7" display="mailto:daniela.cerritos@clarosv" xr:uid="{7623D078-08BA-4928-8F82-306F38D4640F}"/>
+    <hyperlink ref="A27" r:id="rId8" display="mailto:daniela.olivares@clarosv" xr:uid="{15DA68CA-4615-4594-815B-35E8C54510CD}"/>
+    <hyperlink ref="A28" r:id="rId9" display="mailto:debbie.castilloc@clarosv" xr:uid="{FC5FF5B0-A22A-4995-A83C-54B499E27D17}"/>
+    <hyperlink ref="A29" r:id="rId10" display="mailto:duran.rolando@clarosv" xr:uid="{2BDC31C9-5DC3-46B9-ABDC-A1F572F1197E}"/>
+    <hyperlink ref="A30" r:id="rId11" display="mailto:edwin.grijalvah@clarosv" xr:uid="{1096786F-0FB9-4E6C-AB6E-5F9C04B13CE3}"/>
+    <hyperlink ref="A33" r:id="rId12" display="mailto:ernesto.alopez@clarosv" xr:uid="{7857A685-A41D-4B3C-977F-58D66FD6C31E}"/>
+    <hyperlink ref="A35" r:id="rId13" display="mailto:geisel.rosales@clarosv" xr:uid="{87B51C6F-DBF5-46D7-AEB3-F2B046AF7057}"/>
+    <hyperlink ref="A36" r:id="rId14" display="mailto:gracia.bonilla@clarosv" xr:uid="{24848229-B1FA-404D-B061-4654859E913F}"/>
+    <hyperlink ref="A37" r:id="rId15" display="mailto:harold.diaz@clarosv" xr:uid="{CE9F5B01-4E89-471C-9E91-8515FD149E48}"/>
+    <hyperlink ref="A40" r:id="rId16" display="mailto:irving.alvarez@clarosv" xr:uid="{8F8993B7-0615-4784-9D91-76E0C5AFD13F}"/>
+    <hyperlink ref="A44" r:id="rId17" display="mailto:josue.diazp@clarosv" xr:uid="{DFC691B2-1A85-45AB-B184-78E92B354B06}"/>
+    <hyperlink ref="A45" r:id="rId18" display="mailto:juanm.ortiz@clarosv" xr:uid="{43A4CB1D-1DC3-4D15-A5A0-F2DEF41BAFE6}"/>
+    <hyperlink ref="A46" r:id="rId19" display="mailto:julissa.cardona@clarosv" xr:uid="{0565D657-6F7F-440F-8B8D-3621607437E6}"/>
+    <hyperlink ref="A48" r:id="rId20" display="mailto:karen.chacon@clarosv" xr:uid="{69BFAC36-D7C8-4F10-8650-D58CD495E39A}"/>
+    <hyperlink ref="A49" r:id="rId21" display="mailto:katherine.calderonh@clarosv" xr:uid="{04027D98-2FD1-422D-B3AC-50596EED6FEF}"/>
+    <hyperlink ref="A50" r:id="rId22" display="mailto:kathya.molina@clarosv" xr:uid="{4BDF195F-8781-40D6-AC0D-1D86994F309E}"/>
+    <hyperlink ref="A51" r:id="rId23" display="mailto:kevin.navarro@clarosv" xr:uid="{33358D5D-FBF1-4DD1-9CDE-5B6F520FF37C}"/>
+    <hyperlink ref="A52" r:id="rId24" display="mailto:kevin.serranob@clarosv" xr:uid="{EAAE655C-F54B-4A17-AE82-9B29EC2BBB61}"/>
+    <hyperlink ref="A53" r:id="rId25" display="mailto:laura.ortizf@clarosv" xr:uid="{D1CF79E3-492D-49F7-A9E9-B9C4601211AC}"/>
+    <hyperlink ref="A54" r:id="rId26" display="mailto:lesly.romerog@clarosv" xr:uid="{43967FF8-4C3F-4C06-A283-1BB03F84E4CF}"/>
+    <hyperlink ref="A57" r:id="rId27" display="mailto:maria.quintanilla@clarosv" xr:uid="{0FC18BB8-1B5B-4F4D-9187-AAC1023298F9}"/>
+    <hyperlink ref="A59" r:id="rId28" display="mailto:marisela.santos@clarosv" xr:uid="{884C24A2-C749-4C32-AFF1-6DA87960B086}"/>
+    <hyperlink ref="A60" r:id="rId29" display="mailto:marlon.rivera@clarosv" xr:uid="{7455E035-8386-47A6-8246-CB06B0898DF5}"/>
+    <hyperlink ref="A62" r:id="rId30" display="mailto:miguel.arevalo@clarosv" xr:uid="{3C3DFE2B-EC71-48ED-925B-6507A6977741}"/>
+    <hyperlink ref="A63" r:id="rId31" display="mailto:milenal.ceron@clarosv" xr:uid="{11062A1E-4A84-48E5-9559-06B0BBD62B1D}"/>
+    <hyperlink ref="A64" r:id="rId32" display="mailto:mireya.guirola@clarosv" xr:uid="{E7FAD5E8-74AD-41B9-81BC-CA2FD3BB13CE}"/>
+    <hyperlink ref="A65" r:id="rId33" display="mailto:mynoru.garcia@clarosv" xr:uid="{06200DEE-9C92-4E77-B13A-979494C41307}"/>
+    <hyperlink ref="A66" r:id="rId34" display="mailto:nestor.maldonador@clarosv" xr:uid="{3CDC70A9-2FD4-4E53-8F77-14951E24FC5C}"/>
+    <hyperlink ref="A67" r:id="rId35" display="mailto:noe.castillo@clarosv" xr:uid="{E6B60FBF-447C-43A7-948A-3E74E7C2CE04}"/>
+    <hyperlink ref="A69" r:id="rId36" display="mailto:patricia.miranda@clarosv" xr:uid="{896737ED-9E38-46AB-803C-D80480C45260}"/>
+    <hyperlink ref="A72" r:id="rId37" display="mailto:rolandoa.pineda@clarosv" xr:uid="{B9C295A8-2F5A-4538-87F3-F305F8202346}"/>
+    <hyperlink ref="A73" r:id="rId38" display="mailto:roxana.valencia@clarosv" xr:uid="{05F8240B-4059-47D9-A8EA-4920C31C2CFE}"/>
+    <hyperlink ref="A74" r:id="rId39" display="mailto:samuel.duran@clarosv" xr:uid="{A2D04108-7D1E-4B77-A522-5421F461754E}"/>
+    <hyperlink ref="A77" r:id="rId40" display="mailto:tommy.ramos@clarosv" xr:uid="{51D78540-5A04-41E6-9E28-0A6CCFE81291}"/>
+    <hyperlink ref="A81" r:id="rId41" display="mailto:wilfredo.floresm@clarosv" xr:uid="{6A17F062-DDAC-4872-AA43-E63A61FD6F3C}"/>
+    <hyperlink ref="A86" r:id="rId42" display="mailto:alexandrap.melchor@clarosv" xr:uid="{B501769D-2E45-4257-84B3-561E70A3AB4D}"/>
+    <hyperlink ref="A88" r:id="rId43" display="mailto:andreab.reyes@clarosv" xr:uid="{8B00CFB4-5547-4695-8C39-248E6D75A778}"/>
+    <hyperlink ref="A89" r:id="rId44" display="mailto:aquino.wilbert@clarosv" xr:uid="{AB22CDDA-5206-4AFF-9CC4-5CBED734770C}"/>
+    <hyperlink ref="A92" r:id="rId45" display="mailto:bessy.olivia@clarosv" xr:uid="{E6E725B9-BD7A-4288-B667-82177A893DBF}"/>
+    <hyperlink ref="A99" r:id="rId46" display="mailto:carlosa.flores@clarosv" xr:uid="{3DA6DB91-27EF-4FD7-848A-029A740D501B}"/>
+    <hyperlink ref="A101" r:id="rId47" display="mailto:carlosh.villalta@clarosv" xr:uid="{0724D293-639B-4C21-896D-E04208B0C1DA}"/>
+    <hyperlink ref="A104" r:id="rId48" display="mailto:clara.vasquez@clarosv" xr:uid="{34AB3787-4850-4DE4-86A6-E1E1CD0161FC}"/>
+    <hyperlink ref="A113" r:id="rId49" display="mailto:estefanyy.fabian@clarosv" xr:uid="{58AA704E-C9AF-4B19-B209-94A8B1216E9C}"/>
+    <hyperlink ref="A135" r:id="rId50" display="mailto:josej.zelaya@clarosv" xr:uid="{9B680BD9-E0D3-4AF0-B0A9-8345D66252BD}"/>
+    <hyperlink ref="A150" r:id="rId51" display="mailto:luiss.aguirre@clarosv" xr:uid="{9FDCF2C4-54A6-4D09-B41E-E92E2B333092}"/>
+    <hyperlink ref="A158" r:id="rId52" display="mailto:michelle.perez@clarosv" xr:uid="{E42B43B8-5B4A-41EB-BEFC-5356A3348809}"/>
+    <hyperlink ref="A159" r:id="rId53" display="mailto:milton.barraza@clarosv" xr:uid="{C2B36D1D-B054-45C1-95DE-1DAD93F2C8A1}"/>
+    <hyperlink ref="A162" r:id="rId54" display="mailto:op16@clarosv" xr:uid="{AA1BE4FF-3B0D-4704-BF10-BB8F7551CF94}"/>
+    <hyperlink ref="A163" r:id="rId55" display="mailto:op17@clarosv" xr:uid="{DDC86C26-F7CD-4F20-A4EA-567BFFDE1290}"/>
+    <hyperlink ref="A164" r:id="rId56" display="mailto:op18@clarosv" xr:uid="{7C92FFC1-8B67-4A58-83BD-ED6ACE94A11D}"/>
+    <hyperlink ref="A173" r:id="rId57" display="mailto:sandray.chicas@clarosv" xr:uid="{814B7622-C9AE-4933-9F66-A0D182DA9A6D}"/>
+    <hyperlink ref="A175" r:id="rId58" display="mailto:solano.vanessa@clarosv" xr:uid="{12BAE7B6-292C-4B01-9AE5-D6758D9D740F}"/>
+    <hyperlink ref="A182" r:id="rId59" display="mailto:camila.diaz@clarosv" xr:uid="{7F89BB7B-AB24-45C2-82E2-1DF2E2183CF9}"/>
+    <hyperlink ref="A183" r:id="rId60" display="mailto:carlos.hernandezr@clarosv" xr:uid="{902F2DC5-250F-4FB9-9F64-21268FF524BF}"/>
+    <hyperlink ref="A184" r:id="rId61" display="mailto:christian.rodriguezm@clarosv" xr:uid="{395547B5-539E-4DD9-9003-8F307F14AACA}"/>
+    <hyperlink ref="A185" r:id="rId62" display="mailto:cristhian.flores@clarosv" xr:uid="{50FF017D-5090-4952-927D-EB6CD55582E6}"/>
+    <hyperlink ref="A186" r:id="rId63" display="mailto:cristian.tobarc@clarosv" xr:uid="{9567E60D-A87D-4DBE-A748-F9B7D7246B2F}"/>
+    <hyperlink ref="A187" r:id="rId64" display="mailto:karen.perezn@clarosv" xr:uid="{1E5B4E15-9A63-488D-A14C-89726CD45C25}"/>
+    <hyperlink ref="A194" r:id="rId65" display="mailto:alexis.medina@clarosv" xr:uid="{C0F66076-DDB5-408B-BC93-292E6D8A2498}"/>
+    <hyperlink ref="A195" r:id="rId66" display="mailto:ashleys.martinez@clarosv" xr:uid="{38D98F96-656D-449A-8F68-2448B31C09E5}"/>
+    <hyperlink ref="A196" r:id="rId67" display="mailto:edwin.arivas@clarosv" xr:uid="{47A96BFB-4F3C-4DD4-878C-0549310EEF72}"/>
+    <hyperlink ref="A197" r:id="rId68" display="mailto:elizabeth.moran@clarosv" xr:uid="{6E105E05-AAFD-46D4-92E3-3A0E61A7647F}"/>
+    <hyperlink ref="A198" r:id="rId69" display="mailto:gladys.perez@clarosv" xr:uid="{44140AEE-A765-4597-8246-BFE03120ACA5}"/>
+    <hyperlink ref="A199" r:id="rId70" display="mailto:karenm.floresm@clarosv" xr:uid="{DAC39EC9-533C-43C4-B764-59E94F6808E2}"/>
+    <hyperlink ref="A200" r:id="rId71" display="mailto:kathya.aguilar@clarosv" xr:uid="{B5DB1047-010D-48F1-9883-A97BF3FFF03F}"/>
+    <hyperlink ref="A201" r:id="rId72" display="mailto:maria.moranc@clarosv" xr:uid="{58191D11-F579-43FB-A03C-D01954508253}"/>
+    <hyperlink ref="A205" r:id="rId73" display="mailto:raquel.montoya@clarosv" xr:uid="{B82FDB85-BA16-4DC3-B9DB-AFF1560441EF}"/>
+    <hyperlink ref="A221" r:id="rId74" display="mailto:claudiag.escobar@clarosv" xr:uid="{B51B0972-4DEE-45F2-B3F7-14A3434EC200}"/>
+    <hyperlink ref="A253" r:id="rId75" display="mailto:benjamin.jovel@clarosv" xr:uid="{B5F983B4-E597-4035-9EC1-420EA2A259B6}"/>
+    <hyperlink ref="A254" r:id="rId76" display="mailto:carlos.dmolina@clarosv" xr:uid="{93A10529-BB8E-488E-B137-CEC5C07DB4CC}"/>
+    <hyperlink ref="A257" r:id="rId77" display="mailto:douglas.molina@clarosv" xr:uid="{E909812A-6338-40CE-A270-313FFB255B6D}"/>
+    <hyperlink ref="A258" r:id="rId78" display="mailto:eduardoa.moran@clarosv" xr:uid="{891C5C54-3319-4AA8-AE41-7543491E0A91}"/>
+    <hyperlink ref="A268" r:id="rId79" display="mailto:oscar.rgomez@clarosv" xr:uid="{A06B33D7-2C70-4008-BC35-65CE3C86433F}"/>
+    <hyperlink ref="A269" r:id="rId80" display="mailto:oscare.cruz@clarosv" xr:uid="{3FBFABCF-1AB6-41C9-A9E5-381625A1F7EA}"/>
+    <hyperlink ref="A271" r:id="rId81" display="mailto:yaneth.ramos@clarosv" xr:uid="{DFE9F734-980A-42A1-87AA-7CB2C5FC164C}"/>
+    <hyperlink ref="A283" r:id="rId82" display="mailto:danielag.pena@clarosv" xr:uid="{39B78638-EE7C-48FC-A5F6-545630E19505}"/>
+    <hyperlink ref="A301" r:id="rId83" display="mailto:maira.gil@clarosv" xr:uid="{12DC3821-28E3-400F-87B1-7E1310DF381F}"/>
+    <hyperlink ref="A302" r:id="rId84" display="mailto:marjorie.guardado@clarosv" xr:uid="{7B447531-334B-488F-86C8-4276BAC1700A}"/>
+    <hyperlink ref="A340" r:id="rId85" display="mailto:jorgem.serrano@clarosv" xr:uid="{15994CDD-FE5D-427C-9C46-08F3917E870C}"/>
+    <hyperlink ref="A348" r:id="rId86" display="mailto:iveth.cuadra@clarosv" xr:uid="{6A12E169-975F-4ED5-8E9C-A3788B71A5B8}"/>
+    <hyperlink ref="A353" r:id="rId87" display="mailto:carlosd.tobar@clarosv" xr:uid="{40A92B11-8705-4CEB-9E05-A0ABB72B9327}"/>
+    <hyperlink ref="A354" r:id="rId88" display="mailto:hazela.ramirez@clarosv" xr:uid="{3388EC17-1B78-43EF-B73E-E261E6ECD8AE}"/>
+    <hyperlink ref="A356" r:id="rId89" display="mailto:jonathan.ahernandez@clarosv" xr:uid="{3E346811-A27A-46C4-AF7E-D425A2492D45}"/>
+    <hyperlink ref="A358" r:id="rId90" display="mailto:katherine.reynosa@clarosv" xr:uid="{CDB9A6CB-98BE-4900-930E-FCD8A4BBDF24}"/>
+    <hyperlink ref="A399" r:id="rId91" display="mailto:marielos.hernandez@clarosv" xr:uid="{B107CD83-836A-4D88-9BC7-7260FBC1DCBE}"/>
+    <hyperlink ref="A411" r:id="rId92" display="mailto:byron.marroquin@clarosv" xr:uid="{6DFBE911-EED6-44B7-96EA-29F27C6D74A0}"/>
+    <hyperlink ref="A412" r:id="rId93" display="mailto:cesar.elias@clarosv" xr:uid="{8A161163-FA28-4735-BEBA-5285F4BBCFA6}"/>
+    <hyperlink ref="A413" r:id="rId94" display="mailto:christian.mendoza@clarosv" xr:uid="{8EA282F4-FEB6-4969-AE7B-E49EA226FED7}"/>
+    <hyperlink ref="A414" r:id="rId95" display="mailto:javier.ruiz@clarosv" xr:uid="{B11B2C4C-E374-4E70-A5CB-80B962CEBE36}"/>
+    <hyperlink ref="A415" r:id="rId96" display="mailto:jennifer.landaverde@clarosv" xr:uid="{7035AD51-7ABE-4230-8FC3-5DFCE247E532}"/>
+    <hyperlink ref="A416" r:id="rId97" display="mailto:miriam.martinez@clarosv" xr:uid="{ADB2BBC3-6360-4FE3-B9F8-E7354216810D}"/>
+    <hyperlink ref="A417" r:id="rId98" display="mailto:rebeca.caballero@clarosv" xr:uid="{2AB61442-3295-4018-906D-447B84BB21F2}"/>
+    <hyperlink ref="A418" r:id="rId99" display="mailto:vladimir.estradav@clarosv" xr:uid="{5B5C8D09-13CD-4765-BE2E-D5D998E1F936}"/>
+    <hyperlink ref="A424" r:id="rId100" display="mailto:melendezm.juan@clarosv" xr:uid="{625B9BB5-D290-4B5A-A1F7-5763648BD11A}"/>
+    <hyperlink ref="A425" r:id="rId101" display="mailto:rivera_marvin@clarosv" xr:uid="{194F4F2D-0CB4-4011-AEC5-29896AD3495D}"/>
+    <hyperlink ref="A426" r:id="rId102" display="mailto:rafaela.figueroa@clarosv" xr:uid="{E71E76CA-6DEE-4619-83DF-2B35E9388784}"/>
+    <hyperlink ref="A428" r:id="rId103" display="mailto:gabriela.ocruz@clarosv" xr:uid="{027E49DB-1ACB-4724-B085-0D28711E6893}"/>
+    <hyperlink ref="A430" r:id="rId104" display="mailto:katherine.bolainez@clarosv" xr:uid="{C89E974A-DADF-4440-94F6-EFEE74112687}"/>
+    <hyperlink ref="A432" r:id="rId105" display="mailto:pineda.gabriela@clarosv" xr:uid="{07FDA044-7B05-4C3D-9E47-2542B3D2561F}"/>
+    <hyperlink ref="A433" r:id="rId106" display="mailto:veronica.campos@clarosv" xr:uid="{343B7D78-463B-4B89-AEB4-E3B063AF5E9F}"/>
+    <hyperlink ref="A436" r:id="rId107" display="mailto:alexander.orellanap@clarosv" xr:uid="{D6752EF5-D246-484C-A11D-8E5C7D4D5ACC}"/>
+    <hyperlink ref="A441" r:id="rId108" display="mailto:antonio.ponce@clarosv" xr:uid="{93AF8D17-48A5-46CD-B515-641EE0EEAD12}"/>
+    <hyperlink ref="A443" r:id="rId109" display="mailto:blanca.avelarm@clarosv" xr:uid="{E22EC095-562E-4634-A71A-4ACDEDF9FCA0}"/>
+    <hyperlink ref="A444" r:id="rId110" display="mailto:brenda.turcios@clarosv" xr:uid="{294B8C64-D9D2-4D67-854A-9C6B9DFEAD51}"/>
+    <hyperlink ref="A445" r:id="rId111" display="mailto:daniel.hernandezs@clarosv" xr:uid="{1E873271-FD7F-48EC-AA76-FB35E1C17953}"/>
+    <hyperlink ref="A448" r:id="rId112" display="mailto:ezequiel.lopez@clarosv" xr:uid="{66A93EFE-6997-47E3-818A-393FAB094376}"/>
+    <hyperlink ref="A449" r:id="rId113" display="mailto:jessica.valencia@clarosv" xr:uid="{4C16D6E8-CFBE-49F1-A5C7-921AD69BBB5D}"/>
+    <hyperlink ref="A451" r:id="rId114" display="mailto:josem.ayala@clarosv" xr:uid="{4C695458-A616-48EB-90B2-EB3992DB5A12}"/>
+    <hyperlink ref="A454" r:id="rId115" display="mailto:kathya.guerrero@clarosv" xr:uid="{34288623-BC37-42BC-81F0-5EAD19BAFC50}"/>
+    <hyperlink ref="A456" r:id="rId116" display="mailto:mario.jovel@clarosv" xr:uid="{97BE0798-0F17-42C6-B480-A6857BBFD6EC}"/>
+    <hyperlink ref="A457" r:id="rId117" display="mailto:op12@clarosv" xr:uid="{2D146628-ADE9-4D1A-A01E-E8BDE4749093}"/>
+    <hyperlink ref="A458" r:id="rId118" display="mailto:orellana.luism@clarosv" xr:uid="{1EFF2710-C90A-472B-805A-70E54F3A5BE1}"/>
+    <hyperlink ref="A459" r:id="rId119" display="mailto:orellana.olgam@clarosv" xr:uid="{CF880D09-12DB-484D-948E-9555FEEE8A18}"/>
+    <hyperlink ref="A460" r:id="rId120" display="mailto:oscar.sarceno@clarosv" xr:uid="{DE5C1224-04D0-4D73-9070-7175D1B24E94}"/>
+    <hyperlink ref="A462" r:id="rId121" display="mailto:soniae.mendez@clarosv" xr:uid="{AA781D29-2EDA-4918-BA24-BCA337F27052}"/>
+    <hyperlink ref="A464" r:id="rId122" display="mailto:susana.valiente@clarosv" xr:uid="{6E47C99B-9E9D-4815-96C3-23F80D957B8A}"/>
+    <hyperlink ref="A465" r:id="rId123" display="mailto:wendys.mejia@clarosv" xr:uid="{9B3537C7-48AE-4476-AF6D-12D5F0B8E51B}"/>
+    <hyperlink ref="A466" r:id="rId124" display="mailto:xiomara.mejia@clarosv" xr:uid="{5820C231-4325-4D5D-A572-17C5EBDE6E92}"/>
+    <hyperlink ref="A467" r:id="rId125" display="mailto:alejandran.blancom@clarosv" xr:uid="{5E8C26D2-6002-4513-BF79-6C83F272EE36}"/>
+    <hyperlink ref="A470" r:id="rId126" display="mailto:henry.romero@clarosv" xr:uid="{8CC5FD2E-91C6-4950-BAAE-10D34A1D785C}"/>
+    <hyperlink ref="A472" r:id="rId127" display="mailto:ambara.maradiaga@clarosv" xr:uid="{7D910468-4461-41D6-81FC-891527E1FB1C}"/>
+    <hyperlink ref="A476" r:id="rId128" display="mailto:gabrielaa.amarin@clarosv" xr:uid="{1654ED00-F195-4AF5-96F1-E94BE15D4A48}"/>
+    <hyperlink ref="A478" r:id="rId129" display="mailto:luis.orellana@clarosv" xr:uid="{8802603E-AD2B-4394-87D0-E78027BACD22}"/>
+    <hyperlink ref="A479" r:id="rId130" display="mailto:william.murcia@clarosv" xr:uid="{765D23F0-B11C-45B2-8F1E-E2BB9C290F80}"/>
+    <hyperlink ref="A630" r:id="rId131" display="mailto:nasser.zablash@clarosv" xr:uid="{117BBC8E-5881-4745-ADA1-DEE69A3C5AD9}"/>
+    <hyperlink ref="A645" r:id="rId132" display="mailto:erika.pmartinez2@clarosv" xr:uid="{FD2CA4DE-A4ED-4248-A708-BF8B9EE69705}"/>
+    <hyperlink ref="A650" r:id="rId133" display="mailto:adriana.raudag@clarosv" xr:uid="{EB7F1F1F-497A-4EE8-8D1C-C45341BF34AB}"/>
+    <hyperlink ref="A651" r:id="rId134" display="mailto:alejandram.flores@clarosv" xr:uid="{1BD17DFF-DCD3-479D-8301-164363A5B5C1}"/>
+    <hyperlink ref="A657" r:id="rId135" display="mailto:angel.monterrosag@clarosv" xr:uid="{FE56A8D1-0897-4208-A815-FD8E169572E9}"/>
+    <hyperlink ref="A658" r:id="rId136" display="mailto:angel.reyesh@clarosv" xr:uid="{2BCBA43E-008D-4358-8E9F-6020C69541EF}"/>
+    <hyperlink ref="A661" r:id="rId137" display="mailto:belen.avedano@clarosv" xr:uid="{4563044C-A511-4E7A-A8F9-7360BFC0CB07}"/>
+    <hyperlink ref="A667" r:id="rId138" display="mailto:carlos.eflores@clarosv" xr:uid="{71459048-E447-4523-8294-56548B1FEE2A}"/>
+    <hyperlink ref="A668" r:id="rId139" display="mailto:carlos.mguzman@clarosv" xr:uid="{6DC1B9EE-5370-4495-8522-D5E0CA074168}"/>
+    <hyperlink ref="A673" r:id="rId140" display="mailto:clara.lzavaleta@clarosv" xr:uid="{C21DA197-7958-4C28-9A72-DEFCCEB41101}"/>
+    <hyperlink ref="A674" r:id="rId141" display="mailto:claudia.perez@clarosv" xr:uid="{7AAD2A24-F2C9-4B7E-9035-E3F00ABF4C83}"/>
+    <hyperlink ref="A677" r:id="rId142" display="mailto:daniel.moran@clarosv" xr:uid="{7AE039F8-9118-4F0A-915E-E640CC03FEC0}"/>
+    <hyperlink ref="A680" r:id="rId143" display="mailto:davida.hernandezm@clarosv" xr:uid="{2352E120-D433-46E8-AAF3-9DFF71F850A3}"/>
+    <hyperlink ref="A682" r:id="rId144" display="mailto:derek.caballero@clarosv" xr:uid="{366CADC0-AFB9-40B1-8081-902D6B96530E}"/>
+    <hyperlink ref="A689" r:id="rId145" display="mailto:edwin.madrid@clarosv" xr:uid="{6184725E-7FD4-49FC-849A-C4844470E0D5}"/>
+    <hyperlink ref="A691" r:id="rId146" display="mailto:emilio.martineza@clarosv" xr:uid="{473E6B01-2B01-42DF-888A-10EAE9FC025B}"/>
+    <hyperlink ref="A692" r:id="rId147" display="mailto:estefany.mendezg@clarosv" xr:uid="{37AC905E-50DE-4B3D-871C-767EB544B103}"/>
+    <hyperlink ref="A697" r:id="rId148" display="mailto:gilma.barillas@clarosv" xr:uid="{745525ED-3615-4F26-9BA0-D3C9A593517F}"/>
+    <hyperlink ref="A703" r:id="rId149" display="mailto:henry.matute@clarosv" xr:uid="{EC3C076C-6FDF-4FA6-B078-677687D03898}"/>
+    <hyperlink ref="A705" r:id="rId150" display="mailto:iris.graciasz@clarosv" xr:uid="{F2459AA9-DAB1-4A38-A69D-BDC253658A3B}"/>
+    <hyperlink ref="A706" r:id="rId151" display="mailto:izamar.perezm@clarosv" xr:uid="{864D7BAC-B420-45C7-9C7E-61DE814F267B}"/>
+    <hyperlink ref="A707" r:id="rId152" display="mailto:jackelyn.guevarap@clarosv" xr:uid="{E681EC1E-8331-4CAE-B2BE-0A46E9D2EBEE}"/>
+    <hyperlink ref="A710" r:id="rId153" display="mailto:jasmin.branr@clarosv" xr:uid="{1CA41415-6697-42F3-97A1-5252E2ABA387}"/>
+    <hyperlink ref="A711" r:id="rId154" display="mailto:joaquin.lizamam@clarosv" xr:uid="{E45E2C62-58CF-47B0-A9A8-0AD07FEC194E}"/>
+    <hyperlink ref="A714" r:id="rId155" display="mailto:jose.ayalam@clarosv" xr:uid="{B2395695-0AA9-4324-BE7D-930F997A9B8A}"/>
+    <hyperlink ref="A724" r:id="rId156" display="mailto:juan.amartinez@clarosv" xr:uid="{102E2B02-41B8-411C-BC29-43DED9502E70}"/>
+    <hyperlink ref="A729" r:id="rId157" display="mailto:karlav.hernandez@clarosv" xr:uid="{60AE0E94-599C-4C70-B474-1D3AB4B6108A}"/>
+    <hyperlink ref="A735" r:id="rId158" display="mailto:kevin.contrerass@clarosv" xr:uid="{251A8BA0-D484-4D00-95B3-EBCF7323DFFA}"/>
+    <hyperlink ref="A737" r:id="rId159" display="mailto:kevin.menjivarh@clarosv" xr:uid="{30E73D08-9CAA-4427-965A-D35853E7B7F0}"/>
+    <hyperlink ref="A739" r:id="rId160" display="mailto:linda.rivasg@clarosv" xr:uid="{32C15B2F-06C1-4382-87E8-A9338736A73D}"/>
+    <hyperlink ref="A741" r:id="rId161" display="mailto:maria.alfaro@clarosv" xr:uid="{19012DD4-50F8-427C-AA3A-C491B899F511}"/>
+    <hyperlink ref="A750" r:id="rId162" display="mailto:marjorie.ortiza@clarosv" xr:uid="{09EAFBD7-94B5-4B44-8B5E-5EA6E903DD40}"/>
+    <hyperlink ref="A752" r:id="rId163" display="mailto:marlong.garcia@clarosv" xr:uid="{4753CBA1-5046-4011-B3D7-591E242C5B6B}"/>
+    <hyperlink ref="A762" r:id="rId164" display="mailto:nelsonv.rivera@clarosv" xr:uid="{F7299F62-299C-409E-A0A1-7F3754BF2927}"/>
+    <hyperlink ref="A764" r:id="rId165" display="mailto:oscars.bonilla@clarosv" xr:uid="{6A122FF2-85A5-4FD5-BFD8-4A125B892A9C}"/>
+    <hyperlink ref="A770" r:id="rId166" display="mailto:ricardo.pleitezh@clarosv" xr:uid="{585BBE98-929E-4253-B5FC-97D3B7577CF1}"/>
+    <hyperlink ref="A772" r:id="rId167" display="mailto:rodrigoa.martinez@clarosv" xr:uid="{856B05C4-D072-4077-B003-E839C0F2F121}"/>
+    <hyperlink ref="A773" r:id="rId168" display="mailto:rosaura.garcia@clarosv" xr:uid="{E4F426C8-F143-45E7-8C22-D3987563D876}"/>
+    <hyperlink ref="A780" r:id="rId169" display="mailto:vladimiran.margueiz@clarosv" xr:uid="{870410E4-F585-488F-80FA-3C3A3B508449}"/>
+    <hyperlink ref="A783" r:id="rId170" display="mailto:zuleyma.mendozar@clarosv" xr:uid="{48384CD0-7D9D-4D17-9446-9B4A9085B34A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId171"/>
@@ -26775,21 +26775,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -26927,31 +26912,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26967,4 +26943,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="113_{6C874331-FAA1-4795-96B8-7F7BC6A3A28C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{68F4562D-9057-4DAD-B46F-8E9D1E53F9C7}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="113_{CBC580B8-4B7D-42D6-9662-2F1803F12FC1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D7C56E82-1247-4CDB-8A8E-1669BC7D167E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6092" uniqueCount="1665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5991" uniqueCount="1665">
   <si>
     <t>Operador</t>
   </si>
@@ -23149,9 +23149,7 @@
       <c r="A649" s="19" t="s">
         <v>571</v>
       </c>
-      <c r="B649" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B649" s="7"/>
       <c r="C649" s="7" t="s">
         <v>572</v>
       </c>
@@ -23174,9 +23172,7 @@
       <c r="A650" s="28" t="s">
         <v>1292</v>
       </c>
-      <c r="B650" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B650" s="5"/>
       <c r="C650" s="5" t="s">
         <v>1293</v>
       </c>
@@ -23249,9 +23245,7 @@
       <c r="A653" s="19" t="s">
         <v>1626</v>
       </c>
-      <c r="B653" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B653" s="7"/>
       <c r="C653" s="7" t="s">
         <v>1627</v>
       </c>
@@ -23274,9 +23268,7 @@
       <c r="A654" s="24" t="s">
         <v>609</v>
       </c>
-      <c r="B654" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B654" s="5"/>
       <c r="C654" s="5" t="s">
         <v>610</v>
       </c>
@@ -23301,9 +23293,7 @@
       <c r="A655" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="B655" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B655" s="7"/>
       <c r="C655" s="7" t="s">
         <v>1286</v>
       </c>
@@ -23351,9 +23341,7 @@
       <c r="A657" s="25" t="s">
         <v>606</v>
       </c>
-      <c r="B657" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B657" s="7"/>
       <c r="C657" s="7" t="s">
         <v>607</v>
       </c>
@@ -23376,9 +23364,7 @@
       <c r="A658" s="28" t="s">
         <v>1281</v>
       </c>
-      <c r="B658" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B658" s="5"/>
       <c r="C658" s="5" t="s">
         <v>1282</v>
       </c>
@@ -23401,9 +23387,7 @@
       <c r="A659" s="19" t="s">
         <v>1279</v>
       </c>
-      <c r="B659" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B659" s="7"/>
       <c r="C659" s="7" t="s">
         <v>1280</v>
       </c>
@@ -23451,9 +23435,7 @@
       <c r="A661" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="B661" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B661" s="7"/>
       <c r="C661" s="7" t="s">
         <v>190</v>
       </c>
@@ -23476,9 +23458,7 @@
       <c r="A662" s="24" t="s">
         <v>1630</v>
       </c>
-      <c r="B662" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B662" s="5"/>
       <c r="C662" s="5" t="s">
         <v>1631</v>
       </c>
@@ -23503,9 +23483,7 @@
       <c r="A663" s="19" t="s">
         <v>544</v>
       </c>
-      <c r="B663" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B663" s="7"/>
       <c r="C663" s="7" t="s">
         <v>545</v>
       </c>
@@ -23528,9 +23506,7 @@
       <c r="A664" s="24" t="s">
         <v>1272</v>
       </c>
-      <c r="B664" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B664" s="5"/>
       <c r="C664" s="5" t="s">
         <v>1273</v>
       </c>
@@ -23603,9 +23579,7 @@
       <c r="A667" s="25" t="s">
         <v>741</v>
       </c>
-      <c r="B667" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B667" s="7"/>
       <c r="C667" s="7" t="s">
         <v>742</v>
       </c>
@@ -23628,9 +23602,7 @@
       <c r="A668" s="28" t="s">
         <v>569</v>
       </c>
-      <c r="B668" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B668" s="5"/>
       <c r="C668" s="5" t="s">
         <v>570</v>
       </c>
@@ -23653,9 +23625,7 @@
       <c r="A669" s="19" t="s">
         <v>1262</v>
       </c>
-      <c r="B669" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B669" s="7"/>
       <c r="C669" s="7" t="s">
         <v>1263</v>
       </c>
@@ -23678,9 +23648,7 @@
       <c r="A670" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="B670" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B670" s="5"/>
       <c r="C670" s="5" t="s">
         <v>568</v>
       </c>
@@ -23728,9 +23696,7 @@
       <c r="A672" s="24" t="s">
         <v>1256</v>
       </c>
-      <c r="B672" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B672" s="5"/>
       <c r="C672" s="5" t="s">
         <v>1257</v>
       </c>
@@ -23753,9 +23719,7 @@
       <c r="A673" s="25" t="s">
         <v>1254</v>
       </c>
-      <c r="B673" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B673" s="7"/>
       <c r="C673" s="7" t="s">
         <v>1255</v>
       </c>
@@ -23780,9 +23744,7 @@
       <c r="A674" s="28" t="s">
         <v>1252</v>
       </c>
-      <c r="B674" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B674" s="5"/>
       <c r="C674" s="5" t="s">
         <v>1253</v>
       </c>
@@ -23805,9 +23767,7 @@
       <c r="A675" s="19" t="s">
         <v>1248</v>
       </c>
-      <c r="B675" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B675" s="7"/>
       <c r="C675" s="7" t="s">
         <v>1249</v>
       </c>
@@ -23855,9 +23815,7 @@
       <c r="A677" s="25" t="s">
         <v>542</v>
       </c>
-      <c r="B677" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B677" s="7"/>
       <c r="C677" s="7" t="s">
         <v>543</v>
       </c>
@@ -23880,9 +23838,7 @@
       <c r="A678" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="B678" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B678" s="5"/>
       <c r="C678" s="5" t="s">
         <v>541</v>
       </c>
@@ -23930,9 +23886,7 @@
       <c r="A680" s="28" t="s">
         <v>1242</v>
       </c>
-      <c r="B680" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B680" s="5"/>
       <c r="C680" s="5" t="s">
         <v>1243</v>
       </c>
@@ -23957,9 +23911,7 @@
       <c r="A681" s="19" t="s">
         <v>1240</v>
       </c>
-      <c r="B681" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B681" s="7"/>
       <c r="C681" s="7" t="s">
         <v>1241</v>
       </c>
@@ -23982,9 +23934,7 @@
       <c r="A682" s="28" t="s">
         <v>596</v>
       </c>
-      <c r="B682" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B682" s="5"/>
       <c r="C682" s="5" t="s">
         <v>597</v>
       </c>
@@ -24007,9 +23957,7 @@
       <c r="A683" s="19" t="s">
         <v>1238</v>
       </c>
-      <c r="B683" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B683" s="7"/>
       <c r="C683" s="7" t="s">
         <v>1239</v>
       </c>
@@ -24032,9 +23980,7 @@
       <c r="A684" s="24" t="s">
         <v>1236</v>
       </c>
-      <c r="B684" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B684" s="5"/>
       <c r="C684" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24057,9 +24003,7 @@
       <c r="A685" s="19" t="s">
         <v>1232</v>
       </c>
-      <c r="B685" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B685" s="7"/>
       <c r="C685" s="7" t="s">
         <v>1233</v>
       </c>
@@ -24082,9 +24026,7 @@
       <c r="A686" s="24" t="s">
         <v>1228</v>
       </c>
-      <c r="B686" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B686" s="5"/>
       <c r="C686" s="5" t="s">
         <v>1229</v>
       </c>
@@ -24159,9 +24101,7 @@
       <c r="A689" s="25" t="s">
         <v>734</v>
       </c>
-      <c r="B689" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B689" s="7"/>
       <c r="C689" s="7" t="s">
         <v>735</v>
       </c>
@@ -24184,9 +24124,7 @@
       <c r="A690" s="24" t="s">
         <v>1220</v>
       </c>
-      <c r="B690" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B690" s="5"/>
       <c r="C690" s="5" t="s">
         <v>1221</v>
       </c>
@@ -24209,9 +24147,7 @@
       <c r="A691" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B691" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B691" s="7"/>
       <c r="C691" s="7" t="s">
         <v>1219</v>
       </c>
@@ -24236,9 +24172,7 @@
       <c r="A692" s="28" t="s">
         <v>536</v>
       </c>
-      <c r="B692" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B692" s="5"/>
       <c r="C692" s="5" t="s">
         <v>537</v>
       </c>
@@ -24261,9 +24195,7 @@
       <c r="A693" s="19" t="s">
         <v>1217</v>
       </c>
-      <c r="B693" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B693" s="7"/>
       <c r="C693" s="7" t="s">
         <v>1218</v>
       </c>
@@ -24311,9 +24243,7 @@
       <c r="A695" s="19" t="s">
         <v>1213</v>
       </c>
-      <c r="B695" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B695" s="7"/>
       <c r="C695" s="7" t="s">
         <v>1214</v>
       </c>
@@ -24338,9 +24268,7 @@
       <c r="A696" s="24" t="s">
         <v>1211</v>
       </c>
-      <c r="B696" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B696" s="5"/>
       <c r="C696" s="5" t="s">
         <v>1212</v>
       </c>
@@ -24363,9 +24291,7 @@
       <c r="A697" s="25" t="s">
         <v>565</v>
       </c>
-      <c r="B697" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B697" s="7"/>
       <c r="C697" s="7" t="s">
         <v>566</v>
       </c>
@@ -24463,9 +24389,7 @@
       <c r="A701" s="19" t="s">
         <v>534</v>
       </c>
-      <c r="B701" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B701" s="7"/>
       <c r="C701" s="7" t="s">
         <v>535</v>
       </c>
@@ -24490,9 +24414,7 @@
       <c r="A702" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="B702" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B702" s="5"/>
       <c r="C702" s="5" t="s">
         <v>589</v>
       </c>
@@ -24515,9 +24437,7 @@
       <c r="A703" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B703" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B703" s="7"/>
       <c r="C703" s="7" t="s">
         <v>182</v>
       </c>
@@ -24540,9 +24460,7 @@
       <c r="A704" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B704" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B704" s="5"/>
       <c r="C704" s="5" t="s">
         <v>532</v>
       </c>
@@ -24565,9 +24483,7 @@
       <c r="A705" s="25" t="s">
         <v>1207</v>
       </c>
-      <c r="B705" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B705" s="7"/>
       <c r="C705" s="7" t="s">
         <v>1208</v>
       </c>
@@ -24592,9 +24508,7 @@
       <c r="A706" s="28" t="s">
         <v>1205</v>
       </c>
-      <c r="B706" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B706" s="5"/>
       <c r="C706" s="5" t="s">
         <v>1206</v>
       </c>
@@ -24617,9 +24531,7 @@
       <c r="A707" s="25" t="s">
         <v>1203</v>
       </c>
-      <c r="B707" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B707" s="7"/>
       <c r="C707" s="7" t="s">
         <v>1204</v>
       </c>
@@ -24667,9 +24579,7 @@
       <c r="A709" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B709" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B709" s="7"/>
       <c r="C709" s="12" t="s">
         <v>530</v>
       </c>
@@ -24692,9 +24602,7 @@
       <c r="A710" s="28" t="s">
         <v>1199</v>
       </c>
-      <c r="B710" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B710" s="5"/>
       <c r="C710" s="5" t="s">
         <v>1200</v>
       </c>
@@ -24719,9 +24627,7 @@
       <c r="A711" s="25" t="s">
         <v>1197</v>
       </c>
-      <c r="B711" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B711" s="7"/>
       <c r="C711" s="7" t="s">
         <v>1198</v>
       </c>
@@ -24769,9 +24675,7 @@
       <c r="A713" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B713" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B713" s="7"/>
       <c r="C713" s="7" t="s">
         <v>177</v>
       </c>
@@ -24796,9 +24700,7 @@
       <c r="A714" s="28" t="s">
         <v>1191</v>
       </c>
-      <c r="B714" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B714" s="5"/>
       <c r="C714" s="5" t="s">
         <v>1192</v>
       </c>
@@ -24821,9 +24723,7 @@
       <c r="A715" s="19" t="s">
         <v>1189</v>
       </c>
-      <c r="B715" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B715" s="7"/>
       <c r="C715" s="7" t="s">
         <v>1190</v>
       </c>
@@ -24846,9 +24746,7 @@
       <c r="A716" s="24" t="s">
         <v>585</v>
       </c>
-      <c r="B716" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B716" s="5"/>
       <c r="C716" s="5" t="s">
         <v>586</v>
       </c>
@@ -24871,9 +24769,7 @@
       <c r="A717" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B717" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B717" s="7"/>
       <c r="C717" s="7" t="s">
         <v>171</v>
       </c>
@@ -24948,9 +24844,7 @@
       <c r="A720" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="B720" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B720" s="5"/>
       <c r="C720" s="13" t="s">
         <v>564</v>
       </c>
@@ -24973,9 +24867,7 @@
       <c r="A721" s="19" t="s">
         <v>1183</v>
       </c>
-      <c r="B721" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B721" s="7"/>
       <c r="C721" s="7" t="s">
         <v>1184</v>
       </c>
@@ -24998,9 +24890,7 @@
       <c r="A722" s="24" t="s">
         <v>1181</v>
       </c>
-      <c r="B722" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B722" s="5"/>
       <c r="C722" s="5" t="s">
         <v>1182</v>
       </c>
@@ -25048,9 +24938,7 @@
       <c r="A724" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="B724" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B724" s="5"/>
       <c r="C724" s="5" t="s">
         <v>168</v>
       </c>
@@ -25098,9 +24986,7 @@
       <c r="A726" s="24" t="s">
         <v>1632</v>
       </c>
-      <c r="B726" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B726" s="5"/>
       <c r="C726" s="5" t="s">
         <v>1633</v>
       </c>
@@ -25148,9 +25034,7 @@
       <c r="A728" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="B728" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B728" s="5"/>
       <c r="C728" s="5" t="s">
         <v>528</v>
       </c>
@@ -25175,9 +25059,7 @@
       <c r="A729" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="B729" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B729" s="7"/>
       <c r="C729" s="7" t="s">
         <v>723</v>
       </c>
@@ -25200,9 +25082,7 @@
       <c r="A730" s="24" t="s">
         <v>524</v>
       </c>
-      <c r="B730" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B730" s="5"/>
       <c r="C730" s="5" t="s">
         <v>525</v>
       </c>
@@ -25227,9 +25107,7 @@
       <c r="A731" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="B731" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B731" s="7"/>
       <c r="C731" s="7" t="s">
         <v>523</v>
       </c>
@@ -25254,9 +25132,7 @@
       <c r="A732" s="24" t="s">
         <v>1169</v>
       </c>
-      <c r="B732" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B732" s="5"/>
       <c r="C732" s="5" t="s">
         <v>1170</v>
       </c>
@@ -25308,9 +25184,7 @@
       <c r="A734" s="24" t="s">
         <v>1165</v>
       </c>
-      <c r="B734" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B734" s="5"/>
       <c r="C734" s="5" t="s">
         <v>1166</v>
       </c>
@@ -25333,9 +25207,7 @@
       <c r="A735" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="B735" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B735" s="7"/>
       <c r="C735" s="7" t="s">
         <v>166</v>
       </c>
@@ -25358,9 +25230,7 @@
       <c r="A736" s="24" t="s">
         <v>518</v>
       </c>
-      <c r="B736" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B736" s="5"/>
       <c r="C736" s="5" t="s">
         <v>519</v>
       </c>
@@ -25383,9 +25253,7 @@
       <c r="A737" s="25" t="s">
         <v>1163</v>
       </c>
-      <c r="B737" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B737" s="7"/>
       <c r="C737" s="7" t="s">
         <v>1164</v>
       </c>
@@ -25433,9 +25301,7 @@
       <c r="A739" s="25" t="s">
         <v>1159</v>
       </c>
-      <c r="B739" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B739" s="7"/>
       <c r="C739" s="7" t="s">
         <v>1160</v>
       </c>
@@ -25458,9 +25324,7 @@
       <c r="A740" s="24" t="s">
         <v>1157</v>
       </c>
-      <c r="B740" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B740" s="5"/>
       <c r="C740" s="5" t="s">
         <v>1158</v>
       </c>
@@ -25483,9 +25347,7 @@
       <c r="A741" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="B741" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B741" s="7"/>
       <c r="C741" s="7" t="s">
         <v>160</v>
       </c>
@@ -25533,9 +25395,7 @@
       <c r="A743" s="19" t="s">
         <v>1153</v>
       </c>
-      <c r="B743" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B743" s="7"/>
       <c r="C743" s="7" t="s">
         <v>1154</v>
       </c>
@@ -25558,9 +25418,7 @@
       <c r="A744" s="24" t="s">
         <v>561</v>
       </c>
-      <c r="B744" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B744" s="5"/>
       <c r="C744" s="13" t="s">
         <v>562</v>
       </c>
@@ -25583,9 +25441,7 @@
       <c r="A745" s="19" t="s">
         <v>1151</v>
       </c>
-      <c r="B745" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B745" s="7"/>
       <c r="C745" s="7" t="s">
         <v>1152</v>
       </c>
@@ -25608,9 +25464,7 @@
       <c r="A746" s="31" t="s">
         <v>516</v>
       </c>
-      <c r="B746" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B746" s="5"/>
       <c r="C746" s="13" t="s">
         <v>517</v>
       </c>
@@ -25633,9 +25487,7 @@
       <c r="A747" s="19" t="s">
         <v>514</v>
       </c>
-      <c r="B747" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B747" s="7"/>
       <c r="C747" s="12" t="s">
         <v>515</v>
       </c>
@@ -25658,9 +25510,7 @@
       <c r="A748" s="24" t="s">
         <v>512</v>
       </c>
-      <c r="B748" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B748" s="5"/>
       <c r="C748" s="5" t="s">
         <v>513</v>
       </c>
@@ -25683,9 +25533,7 @@
       <c r="A749" s="19" t="s">
         <v>1147</v>
       </c>
-      <c r="B749" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B749" s="7"/>
       <c r="C749" s="7" t="s">
         <v>1148</v>
       </c>
@@ -25708,9 +25556,7 @@
       <c r="A750" s="28" t="s">
         <v>1145</v>
       </c>
-      <c r="B750" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B750" s="5"/>
       <c r="C750" s="5" t="s">
         <v>1146</v>
       </c>
@@ -25735,9 +25581,7 @@
       <c r="A751" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B751" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B751" s="7"/>
       <c r="C751" s="7" t="s">
         <v>1144</v>
       </c>
@@ -25762,9 +25606,7 @@
       <c r="A752" s="28" t="s">
         <v>718</v>
       </c>
-      <c r="B752" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B752" s="5"/>
       <c r="C752" s="5" t="s">
         <v>719</v>
       </c>
@@ -25787,9 +25629,7 @@
       <c r="A753" s="19" t="s">
         <v>1634</v>
       </c>
-      <c r="B753" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B753" s="7"/>
       <c r="C753" s="7" t="s">
         <v>1635</v>
       </c>
@@ -25812,9 +25652,7 @@
       <c r="A754" s="24" t="s">
         <v>1141</v>
       </c>
-      <c r="B754" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B754" s="5"/>
       <c r="C754" s="5" t="s">
         <v>1142</v>
       </c>
@@ -25887,9 +25725,7 @@
       <c r="A757" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B757" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B757" s="7"/>
       <c r="C757" s="7" t="s">
         <v>510</v>
       </c>
@@ -25941,9 +25777,7 @@
       <c r="A759" s="19" t="s">
         <v>1134</v>
       </c>
-      <c r="B759" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B759" s="7"/>
       <c r="C759" s="7" t="s">
         <v>311</v>
       </c>
@@ -25966,9 +25800,7 @@
       <c r="A760" s="24" t="s">
         <v>1132</v>
       </c>
-      <c r="B760" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B760" s="5"/>
       <c r="C760" s="5" t="s">
         <v>1133</v>
       </c>
@@ -26016,9 +25848,7 @@
       <c r="A762" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="B762" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B762" s="5"/>
       <c r="C762" s="5" t="s">
         <v>155</v>
       </c>
@@ -26068,9 +25898,7 @@
       <c r="A764" s="28" t="s">
         <v>714</v>
       </c>
-      <c r="B764" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B764" s="5"/>
       <c r="C764" s="5" t="s">
         <v>715</v>
       </c>
@@ -26093,9 +25921,7 @@
       <c r="A765" s="19" t="s">
         <v>504</v>
       </c>
-      <c r="B765" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B765" s="7"/>
       <c r="C765" s="7" t="s">
         <v>505</v>
       </c>
@@ -26118,9 +25944,7 @@
       <c r="A766" s="24" t="s">
         <v>1628</v>
       </c>
-      <c r="B766" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B766" s="5"/>
       <c r="C766" s="5" t="s">
         <v>1629</v>
       </c>
@@ -26143,9 +25967,7 @@
       <c r="A767" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B767" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B767" s="7"/>
       <c r="C767" s="7" t="s">
         <v>1121</v>
       </c>
@@ -26168,9 +25990,7 @@
       <c r="A768" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="B768" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B768" s="5"/>
       <c r="C768" s="5" t="s">
         <v>501</v>
       </c>
@@ -26220,9 +26040,7 @@
       <c r="A770" s="28" t="s">
         <v>1117</v>
       </c>
-      <c r="B770" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B770" s="5"/>
       <c r="C770" s="5" t="s">
         <v>1118</v>
       </c>
@@ -26270,9 +26088,7 @@
       <c r="A772" s="28" t="s">
         <v>1661</v>
       </c>
-      <c r="B772" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B772" s="5"/>
       <c r="C772" s="5" t="s">
         <v>712</v>
       </c>
@@ -26295,9 +26111,7 @@
       <c r="A773" s="25" t="s">
         <v>1113</v>
       </c>
-      <c r="B773" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B773" s="7"/>
       <c r="C773" s="7" t="s">
         <v>1114</v>
       </c>
@@ -26320,9 +26134,7 @@
       <c r="A774" s="24" t="s">
         <v>1111</v>
       </c>
-      <c r="B774" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B774" s="5"/>
       <c r="C774" s="5" t="s">
         <v>1112</v>
       </c>
@@ -26345,9 +26157,7 @@
       <c r="A775" s="19" t="s">
         <v>1107</v>
       </c>
-      <c r="B775" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B775" s="7"/>
       <c r="C775" s="7" t="s">
         <v>1108</v>
       </c>
@@ -26395,9 +26205,7 @@
       <c r="A777" s="19" t="s">
         <v>1103</v>
       </c>
-      <c r="B777" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B777" s="7"/>
       <c r="C777" s="7" t="s">
         <v>1104</v>
       </c>
@@ -26420,9 +26228,7 @@
       <c r="A778" s="24" t="s">
         <v>1101</v>
       </c>
-      <c r="B778" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B778" s="5"/>
       <c r="C778" s="5" t="s">
         <v>1102</v>
       </c>
@@ -26445,9 +26251,7 @@
       <c r="A779" s="19" t="s">
         <v>1099</v>
       </c>
-      <c r="B779" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="B779" s="7"/>
       <c r="C779" s="7" t="s">
         <v>1100</v>
       </c>
@@ -26470,9 +26274,7 @@
       <c r="A780" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B780" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B780" s="5"/>
       <c r="C780" s="5" t="s">
         <v>147</v>
       </c>
@@ -26520,9 +26322,7 @@
       <c r="A782" s="24" t="s">
         <v>1093</v>
       </c>
-      <c r="B782" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="B782" s="5"/>
       <c r="C782" s="5" t="s">
         <v>1094</v>
       </c>
@@ -26545,9 +26345,7 @@
       <c r="A783" s="62" t="s">
         <v>1091</v>
       </c>
-      <c r="B783" s="63" t="s">
-        <v>93</v>
-      </c>
+      <c r="B783" s="63"/>
       <c r="C783" s="63" t="s">
         <v>1092</v>
       </c>
@@ -26595,176 +26393,176 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1" display="mailto:angelg.mejia@clarosv" xr:uid="{8927B62C-5642-4E37-8541-133F553046D7}"/>
-    <hyperlink ref="A17" r:id="rId2" display="mailto:camila.pena@clarosv" xr:uid="{427A8986-CAAE-4302-B1D6-E64545EDE782}"/>
-    <hyperlink ref="A19" r:id="rId3" display="mailto:carmen.turcios@clarosv" xr:uid="{3537DBED-0563-404F-B7A5-644D6EEE1371}"/>
-    <hyperlink ref="A21" r:id="rId4" display="mailto:christian.garciag@clarosv" xr:uid="{B83C06A9-D3D7-4432-BF6C-2BA493B90738}"/>
-    <hyperlink ref="A22" r:id="rId5" display="mailto:cindy.albanes@clarosv" xr:uid="{D17673EA-64B0-4585-AE4A-C6874EEF1742}"/>
-    <hyperlink ref="A24" r:id="rId6" display="mailto:daniel.daguilar@clarosv" xr:uid="{EE7223F1-273D-4CB1-9873-A2984B0B34C6}"/>
-    <hyperlink ref="A25" r:id="rId7" display="mailto:daniela.cerritos@clarosv" xr:uid="{7623D078-08BA-4928-8F82-306F38D4640F}"/>
-    <hyperlink ref="A27" r:id="rId8" display="mailto:daniela.olivares@clarosv" xr:uid="{15DA68CA-4615-4594-815B-35E8C54510CD}"/>
-    <hyperlink ref="A28" r:id="rId9" display="mailto:debbie.castilloc@clarosv" xr:uid="{FC5FF5B0-A22A-4995-A83C-54B499E27D17}"/>
-    <hyperlink ref="A29" r:id="rId10" display="mailto:duran.rolando@clarosv" xr:uid="{2BDC31C9-5DC3-46B9-ABDC-A1F572F1197E}"/>
-    <hyperlink ref="A30" r:id="rId11" display="mailto:edwin.grijalvah@clarosv" xr:uid="{1096786F-0FB9-4E6C-AB6E-5F9C04B13CE3}"/>
-    <hyperlink ref="A33" r:id="rId12" display="mailto:ernesto.alopez@clarosv" xr:uid="{7857A685-A41D-4B3C-977F-58D66FD6C31E}"/>
-    <hyperlink ref="A35" r:id="rId13" display="mailto:geisel.rosales@clarosv" xr:uid="{87B51C6F-DBF5-46D7-AEB3-F2B046AF7057}"/>
-    <hyperlink ref="A36" r:id="rId14" display="mailto:gracia.bonilla@clarosv" xr:uid="{24848229-B1FA-404D-B061-4654859E913F}"/>
-    <hyperlink ref="A37" r:id="rId15" display="mailto:harold.diaz@clarosv" xr:uid="{CE9F5B01-4E89-471C-9E91-8515FD149E48}"/>
-    <hyperlink ref="A40" r:id="rId16" display="mailto:irving.alvarez@clarosv" xr:uid="{8F8993B7-0615-4784-9D91-76E0C5AFD13F}"/>
-    <hyperlink ref="A44" r:id="rId17" display="mailto:josue.diazp@clarosv" xr:uid="{DFC691B2-1A85-45AB-B184-78E92B354B06}"/>
-    <hyperlink ref="A45" r:id="rId18" display="mailto:juanm.ortiz@clarosv" xr:uid="{43A4CB1D-1DC3-4D15-A5A0-F2DEF41BAFE6}"/>
-    <hyperlink ref="A46" r:id="rId19" display="mailto:julissa.cardona@clarosv" xr:uid="{0565D657-6F7F-440F-8B8D-3621607437E6}"/>
-    <hyperlink ref="A48" r:id="rId20" display="mailto:karen.chacon@clarosv" xr:uid="{69BFAC36-D7C8-4F10-8650-D58CD495E39A}"/>
-    <hyperlink ref="A49" r:id="rId21" display="mailto:katherine.calderonh@clarosv" xr:uid="{04027D98-2FD1-422D-B3AC-50596EED6FEF}"/>
-    <hyperlink ref="A50" r:id="rId22" display="mailto:kathya.molina@clarosv" xr:uid="{4BDF195F-8781-40D6-AC0D-1D86994F309E}"/>
-    <hyperlink ref="A51" r:id="rId23" display="mailto:kevin.navarro@clarosv" xr:uid="{33358D5D-FBF1-4DD1-9CDE-5B6F520FF37C}"/>
-    <hyperlink ref="A52" r:id="rId24" display="mailto:kevin.serranob@clarosv" xr:uid="{EAAE655C-F54B-4A17-AE82-9B29EC2BBB61}"/>
-    <hyperlink ref="A53" r:id="rId25" display="mailto:laura.ortizf@clarosv" xr:uid="{D1CF79E3-492D-49F7-A9E9-B9C4601211AC}"/>
-    <hyperlink ref="A54" r:id="rId26" display="mailto:lesly.romerog@clarosv" xr:uid="{43967FF8-4C3F-4C06-A283-1BB03F84E4CF}"/>
-    <hyperlink ref="A57" r:id="rId27" display="mailto:maria.quintanilla@clarosv" xr:uid="{0FC18BB8-1B5B-4F4D-9187-AAC1023298F9}"/>
-    <hyperlink ref="A59" r:id="rId28" display="mailto:marisela.santos@clarosv" xr:uid="{884C24A2-C749-4C32-AFF1-6DA87960B086}"/>
-    <hyperlink ref="A60" r:id="rId29" display="mailto:marlon.rivera@clarosv" xr:uid="{7455E035-8386-47A6-8246-CB06B0898DF5}"/>
-    <hyperlink ref="A62" r:id="rId30" display="mailto:miguel.arevalo@clarosv" xr:uid="{3C3DFE2B-EC71-48ED-925B-6507A6977741}"/>
-    <hyperlink ref="A63" r:id="rId31" display="mailto:milenal.ceron@clarosv" xr:uid="{11062A1E-4A84-48E5-9559-06B0BBD62B1D}"/>
-    <hyperlink ref="A64" r:id="rId32" display="mailto:mireya.guirola@clarosv" xr:uid="{E7FAD5E8-74AD-41B9-81BC-CA2FD3BB13CE}"/>
-    <hyperlink ref="A65" r:id="rId33" display="mailto:mynoru.garcia@clarosv" xr:uid="{06200DEE-9C92-4E77-B13A-979494C41307}"/>
-    <hyperlink ref="A66" r:id="rId34" display="mailto:nestor.maldonador@clarosv" xr:uid="{3CDC70A9-2FD4-4E53-8F77-14951E24FC5C}"/>
-    <hyperlink ref="A67" r:id="rId35" display="mailto:noe.castillo@clarosv" xr:uid="{E6B60FBF-447C-43A7-948A-3E74E7C2CE04}"/>
-    <hyperlink ref="A69" r:id="rId36" display="mailto:patricia.miranda@clarosv" xr:uid="{896737ED-9E38-46AB-803C-D80480C45260}"/>
-    <hyperlink ref="A72" r:id="rId37" display="mailto:rolandoa.pineda@clarosv" xr:uid="{B9C295A8-2F5A-4538-87F3-F305F8202346}"/>
-    <hyperlink ref="A73" r:id="rId38" display="mailto:roxana.valencia@clarosv" xr:uid="{05F8240B-4059-47D9-A8EA-4920C31C2CFE}"/>
-    <hyperlink ref="A74" r:id="rId39" display="mailto:samuel.duran@clarosv" xr:uid="{A2D04108-7D1E-4B77-A522-5421F461754E}"/>
-    <hyperlink ref="A77" r:id="rId40" display="mailto:tommy.ramos@clarosv" xr:uid="{51D78540-5A04-41E6-9E28-0A6CCFE81291}"/>
-    <hyperlink ref="A81" r:id="rId41" display="mailto:wilfredo.floresm@clarosv" xr:uid="{6A17F062-DDAC-4872-AA43-E63A61FD6F3C}"/>
-    <hyperlink ref="A86" r:id="rId42" display="mailto:alexandrap.melchor@clarosv" xr:uid="{B501769D-2E45-4257-84B3-561E70A3AB4D}"/>
-    <hyperlink ref="A88" r:id="rId43" display="mailto:andreab.reyes@clarosv" xr:uid="{8B00CFB4-5547-4695-8C39-248E6D75A778}"/>
-    <hyperlink ref="A89" r:id="rId44" display="mailto:aquino.wilbert@clarosv" xr:uid="{AB22CDDA-5206-4AFF-9CC4-5CBED734770C}"/>
-    <hyperlink ref="A92" r:id="rId45" display="mailto:bessy.olivia@clarosv" xr:uid="{E6E725B9-BD7A-4288-B667-82177A893DBF}"/>
-    <hyperlink ref="A99" r:id="rId46" display="mailto:carlosa.flores@clarosv" xr:uid="{3DA6DB91-27EF-4FD7-848A-029A740D501B}"/>
-    <hyperlink ref="A101" r:id="rId47" display="mailto:carlosh.villalta@clarosv" xr:uid="{0724D293-639B-4C21-896D-E04208B0C1DA}"/>
-    <hyperlink ref="A104" r:id="rId48" display="mailto:clara.vasquez@clarosv" xr:uid="{34AB3787-4850-4DE4-86A6-E1E1CD0161FC}"/>
-    <hyperlink ref="A113" r:id="rId49" display="mailto:estefanyy.fabian@clarosv" xr:uid="{58AA704E-C9AF-4B19-B209-94A8B1216E9C}"/>
-    <hyperlink ref="A135" r:id="rId50" display="mailto:josej.zelaya@clarosv" xr:uid="{9B680BD9-E0D3-4AF0-B0A9-8345D66252BD}"/>
-    <hyperlink ref="A150" r:id="rId51" display="mailto:luiss.aguirre@clarosv" xr:uid="{9FDCF2C4-54A6-4D09-B41E-E92E2B333092}"/>
-    <hyperlink ref="A158" r:id="rId52" display="mailto:michelle.perez@clarosv" xr:uid="{E42B43B8-5B4A-41EB-BEFC-5356A3348809}"/>
-    <hyperlink ref="A159" r:id="rId53" display="mailto:milton.barraza@clarosv" xr:uid="{C2B36D1D-B054-45C1-95DE-1DAD93F2C8A1}"/>
-    <hyperlink ref="A162" r:id="rId54" display="mailto:op16@clarosv" xr:uid="{AA1BE4FF-3B0D-4704-BF10-BB8F7551CF94}"/>
-    <hyperlink ref="A163" r:id="rId55" display="mailto:op17@clarosv" xr:uid="{DDC86C26-F7CD-4F20-A4EA-567BFFDE1290}"/>
-    <hyperlink ref="A164" r:id="rId56" display="mailto:op18@clarosv" xr:uid="{7C92FFC1-8B67-4A58-83BD-ED6ACE94A11D}"/>
-    <hyperlink ref="A173" r:id="rId57" display="mailto:sandray.chicas@clarosv" xr:uid="{814B7622-C9AE-4933-9F66-A0D182DA9A6D}"/>
-    <hyperlink ref="A175" r:id="rId58" display="mailto:solano.vanessa@clarosv" xr:uid="{12BAE7B6-292C-4B01-9AE5-D6758D9D740F}"/>
-    <hyperlink ref="A182" r:id="rId59" display="mailto:camila.diaz@clarosv" xr:uid="{7F89BB7B-AB24-45C2-82E2-1DF2E2183CF9}"/>
-    <hyperlink ref="A183" r:id="rId60" display="mailto:carlos.hernandezr@clarosv" xr:uid="{902F2DC5-250F-4FB9-9F64-21268FF524BF}"/>
-    <hyperlink ref="A184" r:id="rId61" display="mailto:christian.rodriguezm@clarosv" xr:uid="{395547B5-539E-4DD9-9003-8F307F14AACA}"/>
-    <hyperlink ref="A185" r:id="rId62" display="mailto:cristhian.flores@clarosv" xr:uid="{50FF017D-5090-4952-927D-EB6CD55582E6}"/>
-    <hyperlink ref="A186" r:id="rId63" display="mailto:cristian.tobarc@clarosv" xr:uid="{9567E60D-A87D-4DBE-A748-F9B7D7246B2F}"/>
-    <hyperlink ref="A187" r:id="rId64" display="mailto:karen.perezn@clarosv" xr:uid="{1E5B4E15-9A63-488D-A14C-89726CD45C25}"/>
-    <hyperlink ref="A194" r:id="rId65" display="mailto:alexis.medina@clarosv" xr:uid="{C0F66076-DDB5-408B-BC93-292E6D8A2498}"/>
-    <hyperlink ref="A195" r:id="rId66" display="mailto:ashleys.martinez@clarosv" xr:uid="{38D98F96-656D-449A-8F68-2448B31C09E5}"/>
-    <hyperlink ref="A196" r:id="rId67" display="mailto:edwin.arivas@clarosv" xr:uid="{47A96BFB-4F3C-4DD4-878C-0549310EEF72}"/>
-    <hyperlink ref="A197" r:id="rId68" display="mailto:elizabeth.moran@clarosv" xr:uid="{6E105E05-AAFD-46D4-92E3-3A0E61A7647F}"/>
-    <hyperlink ref="A198" r:id="rId69" display="mailto:gladys.perez@clarosv" xr:uid="{44140AEE-A765-4597-8246-BFE03120ACA5}"/>
-    <hyperlink ref="A199" r:id="rId70" display="mailto:karenm.floresm@clarosv" xr:uid="{DAC39EC9-533C-43C4-B764-59E94F6808E2}"/>
-    <hyperlink ref="A200" r:id="rId71" display="mailto:kathya.aguilar@clarosv" xr:uid="{B5DB1047-010D-48F1-9883-A97BF3FFF03F}"/>
-    <hyperlink ref="A201" r:id="rId72" display="mailto:maria.moranc@clarosv" xr:uid="{58191D11-F579-43FB-A03C-D01954508253}"/>
-    <hyperlink ref="A205" r:id="rId73" display="mailto:raquel.montoya@clarosv" xr:uid="{B82FDB85-BA16-4DC3-B9DB-AFF1560441EF}"/>
-    <hyperlink ref="A221" r:id="rId74" display="mailto:claudiag.escobar@clarosv" xr:uid="{B51B0972-4DEE-45F2-B3F7-14A3434EC200}"/>
-    <hyperlink ref="A253" r:id="rId75" display="mailto:benjamin.jovel@clarosv" xr:uid="{B5F983B4-E597-4035-9EC1-420EA2A259B6}"/>
-    <hyperlink ref="A254" r:id="rId76" display="mailto:carlos.dmolina@clarosv" xr:uid="{93A10529-BB8E-488E-B137-CEC5C07DB4CC}"/>
-    <hyperlink ref="A257" r:id="rId77" display="mailto:douglas.molina@clarosv" xr:uid="{E909812A-6338-40CE-A270-313FFB255B6D}"/>
-    <hyperlink ref="A258" r:id="rId78" display="mailto:eduardoa.moran@clarosv" xr:uid="{891C5C54-3319-4AA8-AE41-7543491E0A91}"/>
-    <hyperlink ref="A268" r:id="rId79" display="mailto:oscar.rgomez@clarosv" xr:uid="{A06B33D7-2C70-4008-BC35-65CE3C86433F}"/>
-    <hyperlink ref="A269" r:id="rId80" display="mailto:oscare.cruz@clarosv" xr:uid="{3FBFABCF-1AB6-41C9-A9E5-381625A1F7EA}"/>
-    <hyperlink ref="A271" r:id="rId81" display="mailto:yaneth.ramos@clarosv" xr:uid="{DFE9F734-980A-42A1-87AA-7CB2C5FC164C}"/>
-    <hyperlink ref="A283" r:id="rId82" display="mailto:danielag.pena@clarosv" xr:uid="{39B78638-EE7C-48FC-A5F6-545630E19505}"/>
-    <hyperlink ref="A301" r:id="rId83" display="mailto:maira.gil@clarosv" xr:uid="{12DC3821-28E3-400F-87B1-7E1310DF381F}"/>
-    <hyperlink ref="A302" r:id="rId84" display="mailto:marjorie.guardado@clarosv" xr:uid="{7B447531-334B-488F-86C8-4276BAC1700A}"/>
-    <hyperlink ref="A340" r:id="rId85" display="mailto:jorgem.serrano@clarosv" xr:uid="{15994CDD-FE5D-427C-9C46-08F3917E870C}"/>
-    <hyperlink ref="A348" r:id="rId86" display="mailto:iveth.cuadra@clarosv" xr:uid="{6A12E169-975F-4ED5-8E9C-A3788B71A5B8}"/>
-    <hyperlink ref="A353" r:id="rId87" display="mailto:carlosd.tobar@clarosv" xr:uid="{40A92B11-8705-4CEB-9E05-A0ABB72B9327}"/>
-    <hyperlink ref="A354" r:id="rId88" display="mailto:hazela.ramirez@clarosv" xr:uid="{3388EC17-1B78-43EF-B73E-E261E6ECD8AE}"/>
-    <hyperlink ref="A356" r:id="rId89" display="mailto:jonathan.ahernandez@clarosv" xr:uid="{3E346811-A27A-46C4-AF7E-D425A2492D45}"/>
-    <hyperlink ref="A358" r:id="rId90" display="mailto:katherine.reynosa@clarosv" xr:uid="{CDB9A6CB-98BE-4900-930E-FCD8A4BBDF24}"/>
-    <hyperlink ref="A399" r:id="rId91" display="mailto:marielos.hernandez@clarosv" xr:uid="{B107CD83-836A-4D88-9BC7-7260FBC1DCBE}"/>
-    <hyperlink ref="A411" r:id="rId92" display="mailto:byron.marroquin@clarosv" xr:uid="{6DFBE911-EED6-44B7-96EA-29F27C6D74A0}"/>
-    <hyperlink ref="A412" r:id="rId93" display="mailto:cesar.elias@clarosv" xr:uid="{8A161163-FA28-4735-BEBA-5285F4BBCFA6}"/>
-    <hyperlink ref="A413" r:id="rId94" display="mailto:christian.mendoza@clarosv" xr:uid="{8EA282F4-FEB6-4969-AE7B-E49EA226FED7}"/>
-    <hyperlink ref="A414" r:id="rId95" display="mailto:javier.ruiz@clarosv" xr:uid="{B11B2C4C-E374-4E70-A5CB-80B962CEBE36}"/>
-    <hyperlink ref="A415" r:id="rId96" display="mailto:jennifer.landaverde@clarosv" xr:uid="{7035AD51-7ABE-4230-8FC3-5DFCE247E532}"/>
-    <hyperlink ref="A416" r:id="rId97" display="mailto:miriam.martinez@clarosv" xr:uid="{ADB2BBC3-6360-4FE3-B9F8-E7354216810D}"/>
-    <hyperlink ref="A417" r:id="rId98" display="mailto:rebeca.caballero@clarosv" xr:uid="{2AB61442-3295-4018-906D-447B84BB21F2}"/>
-    <hyperlink ref="A418" r:id="rId99" display="mailto:vladimir.estradav@clarosv" xr:uid="{5B5C8D09-13CD-4765-BE2E-D5D998E1F936}"/>
-    <hyperlink ref="A424" r:id="rId100" display="mailto:melendezm.juan@clarosv" xr:uid="{625B9BB5-D290-4B5A-A1F7-5763648BD11A}"/>
-    <hyperlink ref="A425" r:id="rId101" display="mailto:rivera_marvin@clarosv" xr:uid="{194F4F2D-0CB4-4011-AEC5-29896AD3495D}"/>
-    <hyperlink ref="A426" r:id="rId102" display="mailto:rafaela.figueroa@clarosv" xr:uid="{E71E76CA-6DEE-4619-83DF-2B35E9388784}"/>
-    <hyperlink ref="A428" r:id="rId103" display="mailto:gabriela.ocruz@clarosv" xr:uid="{027E49DB-1ACB-4724-B085-0D28711E6893}"/>
-    <hyperlink ref="A430" r:id="rId104" display="mailto:katherine.bolainez@clarosv" xr:uid="{C89E974A-DADF-4440-94F6-EFEE74112687}"/>
-    <hyperlink ref="A432" r:id="rId105" display="mailto:pineda.gabriela@clarosv" xr:uid="{07FDA044-7B05-4C3D-9E47-2542B3D2561F}"/>
-    <hyperlink ref="A433" r:id="rId106" display="mailto:veronica.campos@clarosv" xr:uid="{343B7D78-463B-4B89-AEB4-E3B063AF5E9F}"/>
-    <hyperlink ref="A436" r:id="rId107" display="mailto:alexander.orellanap@clarosv" xr:uid="{D6752EF5-D246-484C-A11D-8E5C7D4D5ACC}"/>
-    <hyperlink ref="A441" r:id="rId108" display="mailto:antonio.ponce@clarosv" xr:uid="{93AF8D17-48A5-46CD-B515-641EE0EEAD12}"/>
-    <hyperlink ref="A443" r:id="rId109" display="mailto:blanca.avelarm@clarosv" xr:uid="{E22EC095-562E-4634-A71A-4ACDEDF9FCA0}"/>
-    <hyperlink ref="A444" r:id="rId110" display="mailto:brenda.turcios@clarosv" xr:uid="{294B8C64-D9D2-4D67-854A-9C6B9DFEAD51}"/>
-    <hyperlink ref="A445" r:id="rId111" display="mailto:daniel.hernandezs@clarosv" xr:uid="{1E873271-FD7F-48EC-AA76-FB35E1C17953}"/>
-    <hyperlink ref="A448" r:id="rId112" display="mailto:ezequiel.lopez@clarosv" xr:uid="{66A93EFE-6997-47E3-818A-393FAB094376}"/>
-    <hyperlink ref="A449" r:id="rId113" display="mailto:jessica.valencia@clarosv" xr:uid="{4C16D6E8-CFBE-49F1-A5C7-921AD69BBB5D}"/>
-    <hyperlink ref="A451" r:id="rId114" display="mailto:josem.ayala@clarosv" xr:uid="{4C695458-A616-48EB-90B2-EB3992DB5A12}"/>
-    <hyperlink ref="A454" r:id="rId115" display="mailto:kathya.guerrero@clarosv" xr:uid="{34288623-BC37-42BC-81F0-5EAD19BAFC50}"/>
-    <hyperlink ref="A456" r:id="rId116" display="mailto:mario.jovel@clarosv" xr:uid="{97BE0798-0F17-42C6-B480-A6857BBFD6EC}"/>
-    <hyperlink ref="A457" r:id="rId117" display="mailto:op12@clarosv" xr:uid="{2D146628-ADE9-4D1A-A01E-E8BDE4749093}"/>
-    <hyperlink ref="A458" r:id="rId118" display="mailto:orellana.luism@clarosv" xr:uid="{1EFF2710-C90A-472B-805A-70E54F3A5BE1}"/>
-    <hyperlink ref="A459" r:id="rId119" display="mailto:orellana.olgam@clarosv" xr:uid="{CF880D09-12DB-484D-948E-9555FEEE8A18}"/>
-    <hyperlink ref="A460" r:id="rId120" display="mailto:oscar.sarceno@clarosv" xr:uid="{DE5C1224-04D0-4D73-9070-7175D1B24E94}"/>
-    <hyperlink ref="A462" r:id="rId121" display="mailto:soniae.mendez@clarosv" xr:uid="{AA781D29-2EDA-4918-BA24-BCA337F27052}"/>
-    <hyperlink ref="A464" r:id="rId122" display="mailto:susana.valiente@clarosv" xr:uid="{6E47C99B-9E9D-4815-96C3-23F80D957B8A}"/>
-    <hyperlink ref="A465" r:id="rId123" display="mailto:wendys.mejia@clarosv" xr:uid="{9B3537C7-48AE-4476-AF6D-12D5F0B8E51B}"/>
-    <hyperlink ref="A466" r:id="rId124" display="mailto:xiomara.mejia@clarosv" xr:uid="{5820C231-4325-4D5D-A572-17C5EBDE6E92}"/>
-    <hyperlink ref="A467" r:id="rId125" display="mailto:alejandran.blancom@clarosv" xr:uid="{5E8C26D2-6002-4513-BF79-6C83F272EE36}"/>
-    <hyperlink ref="A470" r:id="rId126" display="mailto:henry.romero@clarosv" xr:uid="{8CC5FD2E-91C6-4950-BAAE-10D34A1D785C}"/>
-    <hyperlink ref="A472" r:id="rId127" display="mailto:ambara.maradiaga@clarosv" xr:uid="{7D910468-4461-41D6-81FC-891527E1FB1C}"/>
-    <hyperlink ref="A476" r:id="rId128" display="mailto:gabrielaa.amarin@clarosv" xr:uid="{1654ED00-F195-4AF5-96F1-E94BE15D4A48}"/>
-    <hyperlink ref="A478" r:id="rId129" display="mailto:luis.orellana@clarosv" xr:uid="{8802603E-AD2B-4394-87D0-E78027BACD22}"/>
-    <hyperlink ref="A479" r:id="rId130" display="mailto:william.murcia@clarosv" xr:uid="{765D23F0-B11C-45B2-8F1E-E2BB9C290F80}"/>
-    <hyperlink ref="A630" r:id="rId131" display="mailto:nasser.zablash@clarosv" xr:uid="{117BBC8E-5881-4745-ADA1-DEE69A3C5AD9}"/>
-    <hyperlink ref="A645" r:id="rId132" display="mailto:erika.pmartinez2@clarosv" xr:uid="{FD2CA4DE-A4ED-4248-A708-BF8B9EE69705}"/>
-    <hyperlink ref="A650" r:id="rId133" display="mailto:adriana.raudag@clarosv" xr:uid="{EB7F1F1F-497A-4EE8-8D1C-C45341BF34AB}"/>
-    <hyperlink ref="A651" r:id="rId134" display="mailto:alejandram.flores@clarosv" xr:uid="{1BD17DFF-DCD3-479D-8301-164363A5B5C1}"/>
-    <hyperlink ref="A657" r:id="rId135" display="mailto:angel.monterrosag@clarosv" xr:uid="{FE56A8D1-0897-4208-A815-FD8E169572E9}"/>
-    <hyperlink ref="A658" r:id="rId136" display="mailto:angel.reyesh@clarosv" xr:uid="{2BCBA43E-008D-4358-8E9F-6020C69541EF}"/>
-    <hyperlink ref="A661" r:id="rId137" display="mailto:belen.avedano@clarosv" xr:uid="{4563044C-A511-4E7A-A8F9-7360BFC0CB07}"/>
-    <hyperlink ref="A667" r:id="rId138" display="mailto:carlos.eflores@clarosv" xr:uid="{71459048-E447-4523-8294-56548B1FEE2A}"/>
-    <hyperlink ref="A668" r:id="rId139" display="mailto:carlos.mguzman@clarosv" xr:uid="{6DC1B9EE-5370-4495-8522-D5E0CA074168}"/>
-    <hyperlink ref="A673" r:id="rId140" display="mailto:clara.lzavaleta@clarosv" xr:uid="{C21DA197-7958-4C28-9A72-DEFCCEB41101}"/>
-    <hyperlink ref="A674" r:id="rId141" display="mailto:claudia.perez@clarosv" xr:uid="{7AAD2A24-F2C9-4B7E-9035-E3F00ABF4C83}"/>
-    <hyperlink ref="A677" r:id="rId142" display="mailto:daniel.moran@clarosv" xr:uid="{7AE039F8-9118-4F0A-915E-E640CC03FEC0}"/>
-    <hyperlink ref="A680" r:id="rId143" display="mailto:davida.hernandezm@clarosv" xr:uid="{2352E120-D433-46E8-AAF3-9DFF71F850A3}"/>
-    <hyperlink ref="A682" r:id="rId144" display="mailto:derek.caballero@clarosv" xr:uid="{366CADC0-AFB9-40B1-8081-902D6B96530E}"/>
-    <hyperlink ref="A689" r:id="rId145" display="mailto:edwin.madrid@clarosv" xr:uid="{6184725E-7FD4-49FC-849A-C4844470E0D5}"/>
-    <hyperlink ref="A691" r:id="rId146" display="mailto:emilio.martineza@clarosv" xr:uid="{473E6B01-2B01-42DF-888A-10EAE9FC025B}"/>
-    <hyperlink ref="A692" r:id="rId147" display="mailto:estefany.mendezg@clarosv" xr:uid="{37AC905E-50DE-4B3D-871C-767EB544B103}"/>
-    <hyperlink ref="A697" r:id="rId148" display="mailto:gilma.barillas@clarosv" xr:uid="{745525ED-3615-4F26-9BA0-D3C9A593517F}"/>
-    <hyperlink ref="A703" r:id="rId149" display="mailto:henry.matute@clarosv" xr:uid="{EC3C076C-6FDF-4FA6-B078-677687D03898}"/>
-    <hyperlink ref="A705" r:id="rId150" display="mailto:iris.graciasz@clarosv" xr:uid="{F2459AA9-DAB1-4A38-A69D-BDC253658A3B}"/>
-    <hyperlink ref="A706" r:id="rId151" display="mailto:izamar.perezm@clarosv" xr:uid="{864D7BAC-B420-45C7-9C7E-61DE814F267B}"/>
-    <hyperlink ref="A707" r:id="rId152" display="mailto:jackelyn.guevarap@clarosv" xr:uid="{E681EC1E-8331-4CAE-B2BE-0A46E9D2EBEE}"/>
-    <hyperlink ref="A710" r:id="rId153" display="mailto:jasmin.branr@clarosv" xr:uid="{1CA41415-6697-42F3-97A1-5252E2ABA387}"/>
-    <hyperlink ref="A711" r:id="rId154" display="mailto:joaquin.lizamam@clarosv" xr:uid="{E45E2C62-58CF-47B0-A9A8-0AD07FEC194E}"/>
-    <hyperlink ref="A714" r:id="rId155" display="mailto:jose.ayalam@clarosv" xr:uid="{B2395695-0AA9-4324-BE7D-930F997A9B8A}"/>
-    <hyperlink ref="A724" r:id="rId156" display="mailto:juan.amartinez@clarosv" xr:uid="{102E2B02-41B8-411C-BC29-43DED9502E70}"/>
-    <hyperlink ref="A729" r:id="rId157" display="mailto:karlav.hernandez@clarosv" xr:uid="{60AE0E94-599C-4C70-B474-1D3AB4B6108A}"/>
-    <hyperlink ref="A735" r:id="rId158" display="mailto:kevin.contrerass@clarosv" xr:uid="{251A8BA0-D484-4D00-95B3-EBCF7323DFFA}"/>
-    <hyperlink ref="A737" r:id="rId159" display="mailto:kevin.menjivarh@clarosv" xr:uid="{30E73D08-9CAA-4427-965A-D35853E7B7F0}"/>
-    <hyperlink ref="A739" r:id="rId160" display="mailto:linda.rivasg@clarosv" xr:uid="{32C15B2F-06C1-4382-87E8-A9338736A73D}"/>
-    <hyperlink ref="A741" r:id="rId161" display="mailto:maria.alfaro@clarosv" xr:uid="{19012DD4-50F8-427C-AA3A-C491B899F511}"/>
-    <hyperlink ref="A750" r:id="rId162" display="mailto:marjorie.ortiza@clarosv" xr:uid="{09EAFBD7-94B5-4B44-8B5E-5EA6E903DD40}"/>
-    <hyperlink ref="A752" r:id="rId163" display="mailto:marlong.garcia@clarosv" xr:uid="{4753CBA1-5046-4011-B3D7-591E242C5B6B}"/>
-    <hyperlink ref="A762" r:id="rId164" display="mailto:nelsonv.rivera@clarosv" xr:uid="{F7299F62-299C-409E-A0A1-7F3754BF2927}"/>
-    <hyperlink ref="A764" r:id="rId165" display="mailto:oscars.bonilla@clarosv" xr:uid="{6A122FF2-85A5-4FD5-BFD8-4A125B892A9C}"/>
-    <hyperlink ref="A770" r:id="rId166" display="mailto:ricardo.pleitezh@clarosv" xr:uid="{585BBE98-929E-4253-B5FC-97D3B7577CF1}"/>
-    <hyperlink ref="A772" r:id="rId167" display="mailto:rodrigoa.martinez@clarosv" xr:uid="{856B05C4-D072-4077-B003-E839C0F2F121}"/>
-    <hyperlink ref="A773" r:id="rId168" display="mailto:rosaura.garcia@clarosv" xr:uid="{E4F426C8-F143-45E7-8C22-D3987563D876}"/>
-    <hyperlink ref="A780" r:id="rId169" display="mailto:vladimiran.margueiz@clarosv" xr:uid="{870410E4-F585-488F-80FA-3C3A3B508449}"/>
-    <hyperlink ref="A783" r:id="rId170" display="mailto:zuleyma.mendozar@clarosv" xr:uid="{48384CD0-7D9D-4D17-9446-9B4A9085B34A}"/>
+    <hyperlink ref="A15" r:id="rId1" display="mailto:angelg.mejia@clarosv" xr:uid="{7D213CF8-3837-4347-A99E-FEFB6C2ACD46}"/>
+    <hyperlink ref="A17" r:id="rId2" display="mailto:camila.pena@clarosv" xr:uid="{D064A136-D4F6-49FF-888B-6537F20A86D8}"/>
+    <hyperlink ref="A19" r:id="rId3" display="mailto:carmen.turcios@clarosv" xr:uid="{77E377DD-00F4-469B-AA66-078C10BB742A}"/>
+    <hyperlink ref="A21" r:id="rId4" display="mailto:christian.garciag@clarosv" xr:uid="{57D465FE-892E-4D03-B6ED-A8D7A69E0948}"/>
+    <hyperlink ref="A22" r:id="rId5" display="mailto:cindy.albanes@clarosv" xr:uid="{81D63D4F-0DDC-4DDD-9874-2941746332AF}"/>
+    <hyperlink ref="A24" r:id="rId6" display="mailto:daniel.daguilar@clarosv" xr:uid="{39B71FFE-A060-48E8-9C6A-1FE6C42C78B2}"/>
+    <hyperlink ref="A25" r:id="rId7" display="mailto:daniela.cerritos@clarosv" xr:uid="{2DCC1293-483A-4599-A084-39919B0EDD06}"/>
+    <hyperlink ref="A27" r:id="rId8" display="mailto:daniela.olivares@clarosv" xr:uid="{1A438B41-52A0-493D-AC0C-F612FAD93DDB}"/>
+    <hyperlink ref="A28" r:id="rId9" display="mailto:debbie.castilloc@clarosv" xr:uid="{C524D330-6ECF-4A14-96EE-504D158FC58C}"/>
+    <hyperlink ref="A29" r:id="rId10" display="mailto:duran.rolando@clarosv" xr:uid="{F529E9F7-E3C2-47B4-8494-AC321421A4A0}"/>
+    <hyperlink ref="A30" r:id="rId11" display="mailto:edwin.grijalvah@clarosv" xr:uid="{A42B2974-7F67-4CC8-9DB9-D5E2BAF96ED7}"/>
+    <hyperlink ref="A33" r:id="rId12" display="mailto:ernesto.alopez@clarosv" xr:uid="{A94B9C15-3302-43B4-BB6E-68C471123459}"/>
+    <hyperlink ref="A35" r:id="rId13" display="mailto:geisel.rosales@clarosv" xr:uid="{137A3B27-A172-4D94-A46B-3F91F5707405}"/>
+    <hyperlink ref="A36" r:id="rId14" display="mailto:gracia.bonilla@clarosv" xr:uid="{DA420BC4-807E-4D22-A1DA-F55A6EE71BB6}"/>
+    <hyperlink ref="A37" r:id="rId15" display="mailto:harold.diaz@clarosv" xr:uid="{5069B5A0-0A87-4EC5-91C0-5778E1AB9DE7}"/>
+    <hyperlink ref="A40" r:id="rId16" display="mailto:irving.alvarez@clarosv" xr:uid="{4A7967B9-4739-4E8D-B8DA-265682C5637C}"/>
+    <hyperlink ref="A44" r:id="rId17" display="mailto:josue.diazp@clarosv" xr:uid="{4B495593-563F-4251-B572-2702D54D5319}"/>
+    <hyperlink ref="A45" r:id="rId18" display="mailto:juanm.ortiz@clarosv" xr:uid="{4137E582-C4AB-42FC-8DD6-137B22EFCD4E}"/>
+    <hyperlink ref="A46" r:id="rId19" display="mailto:julissa.cardona@clarosv" xr:uid="{D72A3348-4400-44B8-852B-09A970910BFA}"/>
+    <hyperlink ref="A48" r:id="rId20" display="mailto:karen.chacon@clarosv" xr:uid="{8BD00F1F-7B05-4186-A442-B1B267BFC60A}"/>
+    <hyperlink ref="A49" r:id="rId21" display="mailto:katherine.calderonh@clarosv" xr:uid="{AF64294D-98B8-4A88-A248-A664C9D43F58}"/>
+    <hyperlink ref="A50" r:id="rId22" display="mailto:kathya.molina@clarosv" xr:uid="{9C67999A-1EE6-4573-94FB-CB533E366BB5}"/>
+    <hyperlink ref="A51" r:id="rId23" display="mailto:kevin.navarro@clarosv" xr:uid="{64CF963E-9BBD-4C05-8F4E-FA8832F5125F}"/>
+    <hyperlink ref="A52" r:id="rId24" display="mailto:kevin.serranob@clarosv" xr:uid="{09D77386-B0AB-4C25-B801-D8543D6A0717}"/>
+    <hyperlink ref="A53" r:id="rId25" display="mailto:laura.ortizf@clarosv" xr:uid="{55226BF5-ACE0-41FF-A561-2D8B143EC5FE}"/>
+    <hyperlink ref="A54" r:id="rId26" display="mailto:lesly.romerog@clarosv" xr:uid="{4A553064-9497-43A3-8513-DE411735D991}"/>
+    <hyperlink ref="A57" r:id="rId27" display="mailto:maria.quintanilla@clarosv" xr:uid="{1984D151-629A-40C6-A8A2-D3ABFFD298AB}"/>
+    <hyperlink ref="A59" r:id="rId28" display="mailto:marisela.santos@clarosv" xr:uid="{EA8DDCE8-0672-4FBE-BB18-2CE6625CA739}"/>
+    <hyperlink ref="A60" r:id="rId29" display="mailto:marlon.rivera@clarosv" xr:uid="{41F48BC0-01C9-4E1F-9F14-D2865FFA25BB}"/>
+    <hyperlink ref="A62" r:id="rId30" display="mailto:miguel.arevalo@clarosv" xr:uid="{54874E1B-D94E-429D-971D-B6C00A3292C3}"/>
+    <hyperlink ref="A63" r:id="rId31" display="mailto:milenal.ceron@clarosv" xr:uid="{13CC645D-AE57-4676-AA82-425D8A1FC62C}"/>
+    <hyperlink ref="A64" r:id="rId32" display="mailto:mireya.guirola@clarosv" xr:uid="{083A10DD-B8DC-43F9-8B83-85C699B8DAE2}"/>
+    <hyperlink ref="A65" r:id="rId33" display="mailto:mynoru.garcia@clarosv" xr:uid="{633A245F-3F83-4A04-96EF-9F1854AFDCE6}"/>
+    <hyperlink ref="A66" r:id="rId34" display="mailto:nestor.maldonador@clarosv" xr:uid="{0E1DD1E3-A797-4807-8015-A44A085C0106}"/>
+    <hyperlink ref="A67" r:id="rId35" display="mailto:noe.castillo@clarosv" xr:uid="{A3FC3BE2-1E80-4C7A-A4AC-FE2D8B866D37}"/>
+    <hyperlink ref="A69" r:id="rId36" display="mailto:patricia.miranda@clarosv" xr:uid="{3DECB82F-EE67-457C-BA0C-CD27E9AFFEC2}"/>
+    <hyperlink ref="A72" r:id="rId37" display="mailto:rolandoa.pineda@clarosv" xr:uid="{905CA0E0-2A21-42B0-8F46-4CC30936991D}"/>
+    <hyperlink ref="A73" r:id="rId38" display="mailto:roxana.valencia@clarosv" xr:uid="{77D45367-0EA6-4C46-97A1-C4B9A500067B}"/>
+    <hyperlink ref="A74" r:id="rId39" display="mailto:samuel.duran@clarosv" xr:uid="{37222ED0-9701-4BEF-89AF-D6C77E70C6D7}"/>
+    <hyperlink ref="A77" r:id="rId40" display="mailto:tommy.ramos@clarosv" xr:uid="{9E2FDD1A-3984-43C2-B18F-581BA2DD335C}"/>
+    <hyperlink ref="A81" r:id="rId41" display="mailto:wilfredo.floresm@clarosv" xr:uid="{DAE65DF6-EF11-4F8A-AE94-4E6E541A186A}"/>
+    <hyperlink ref="A86" r:id="rId42" display="mailto:alexandrap.melchor@clarosv" xr:uid="{483E4BB8-132B-4547-BFDE-CBF39DD0C4B7}"/>
+    <hyperlink ref="A88" r:id="rId43" display="mailto:andreab.reyes@clarosv" xr:uid="{8B653577-4D26-44C1-B225-253F77C2FF49}"/>
+    <hyperlink ref="A89" r:id="rId44" display="mailto:aquino.wilbert@clarosv" xr:uid="{C6F3813F-F347-4B73-BC73-74A31B1DE056}"/>
+    <hyperlink ref="A92" r:id="rId45" display="mailto:bessy.olivia@clarosv" xr:uid="{CA69B319-C951-4951-8AED-87E0D5442603}"/>
+    <hyperlink ref="A99" r:id="rId46" display="mailto:carlosa.flores@clarosv" xr:uid="{959DB834-6889-4B25-89C6-C9940D8C3BD9}"/>
+    <hyperlink ref="A101" r:id="rId47" display="mailto:carlosh.villalta@clarosv" xr:uid="{2F21F743-859E-4EF0-92E6-F1B285110FD2}"/>
+    <hyperlink ref="A104" r:id="rId48" display="mailto:clara.vasquez@clarosv" xr:uid="{01D8869C-540C-4458-9DCE-ADC065BDC480}"/>
+    <hyperlink ref="A113" r:id="rId49" display="mailto:estefanyy.fabian@clarosv" xr:uid="{882E26E8-C0C2-49E5-91A1-D3E7540426BB}"/>
+    <hyperlink ref="A135" r:id="rId50" display="mailto:josej.zelaya@clarosv" xr:uid="{37E8EA03-9A7C-4A1E-A2F1-7AE61690FEEC}"/>
+    <hyperlink ref="A150" r:id="rId51" display="mailto:luiss.aguirre@clarosv" xr:uid="{643938AF-ECE4-4029-BF9A-26AB3256FDD7}"/>
+    <hyperlink ref="A158" r:id="rId52" display="mailto:michelle.perez@clarosv" xr:uid="{40BB548C-3741-4F97-A64D-07B5713D35C3}"/>
+    <hyperlink ref="A159" r:id="rId53" display="mailto:milton.barraza@clarosv" xr:uid="{40FF5D96-93D3-4980-ABC0-02B0B4D48BB7}"/>
+    <hyperlink ref="A162" r:id="rId54" display="mailto:op16@clarosv" xr:uid="{53C94299-AF45-4747-8AFF-182BFE3F5D27}"/>
+    <hyperlink ref="A163" r:id="rId55" display="mailto:op17@clarosv" xr:uid="{ACD107BD-9BD2-4681-860C-3138E33C125D}"/>
+    <hyperlink ref="A164" r:id="rId56" display="mailto:op18@clarosv" xr:uid="{224F05E9-7DFA-4E4A-B45C-FAFC6E0A2AC1}"/>
+    <hyperlink ref="A173" r:id="rId57" display="mailto:sandray.chicas@clarosv" xr:uid="{76A12D90-4041-4974-B0C0-C405A847F257}"/>
+    <hyperlink ref="A175" r:id="rId58" display="mailto:solano.vanessa@clarosv" xr:uid="{1CEEC611-DD46-4AC8-AED1-A2AFD06E5664}"/>
+    <hyperlink ref="A182" r:id="rId59" display="mailto:camila.diaz@clarosv" xr:uid="{6BB76DD9-BC37-45B1-98FE-8AA565BD0A1E}"/>
+    <hyperlink ref="A183" r:id="rId60" display="mailto:carlos.hernandezr@clarosv" xr:uid="{3F7E7E7A-DB5F-4D0D-9F3F-82F0223170C4}"/>
+    <hyperlink ref="A184" r:id="rId61" display="mailto:christian.rodriguezm@clarosv" xr:uid="{1799E286-73CB-4D09-80DA-1386A9C352A8}"/>
+    <hyperlink ref="A185" r:id="rId62" display="mailto:cristhian.flores@clarosv" xr:uid="{AFA1E63C-8DE9-4D43-B6BA-50EEE65402EE}"/>
+    <hyperlink ref="A186" r:id="rId63" display="mailto:cristian.tobarc@clarosv" xr:uid="{5D949D77-D156-424F-8A6D-5E3FE144FA14}"/>
+    <hyperlink ref="A187" r:id="rId64" display="mailto:karen.perezn@clarosv" xr:uid="{31FDF136-2147-41BB-9F18-64EBEF96325B}"/>
+    <hyperlink ref="A194" r:id="rId65" display="mailto:alexis.medina@clarosv" xr:uid="{0300A937-5F77-439B-8759-A8136D50CE0E}"/>
+    <hyperlink ref="A195" r:id="rId66" display="mailto:ashleys.martinez@clarosv" xr:uid="{682BB87B-4071-402D-8896-80F54B59C2F0}"/>
+    <hyperlink ref="A196" r:id="rId67" display="mailto:edwin.arivas@clarosv" xr:uid="{EB9B1562-31B2-495A-B811-EDC224C5A933}"/>
+    <hyperlink ref="A197" r:id="rId68" display="mailto:elizabeth.moran@clarosv" xr:uid="{29B02255-A0FF-4403-A08B-D7295F6283CE}"/>
+    <hyperlink ref="A198" r:id="rId69" display="mailto:gladys.perez@clarosv" xr:uid="{C701981F-D9D1-478A-B573-EBEE8CACD86A}"/>
+    <hyperlink ref="A199" r:id="rId70" display="mailto:karenm.floresm@clarosv" xr:uid="{B64805E6-2A1F-4D53-946F-707A55623F4F}"/>
+    <hyperlink ref="A200" r:id="rId71" display="mailto:kathya.aguilar@clarosv" xr:uid="{B48CF211-6906-434C-8BF2-26AA99FCE3A8}"/>
+    <hyperlink ref="A201" r:id="rId72" display="mailto:maria.moranc@clarosv" xr:uid="{CD36E6BC-DB98-4F61-9F45-8B6CE347E4D1}"/>
+    <hyperlink ref="A205" r:id="rId73" display="mailto:raquel.montoya@clarosv" xr:uid="{7ACF9004-6B04-44D9-889F-4DA4CF3009EA}"/>
+    <hyperlink ref="A221" r:id="rId74" display="mailto:claudiag.escobar@clarosv" xr:uid="{5A875731-7F0A-49E2-AD40-CB8B74754A55}"/>
+    <hyperlink ref="A253" r:id="rId75" display="mailto:benjamin.jovel@clarosv" xr:uid="{20AE0693-54E0-4344-BF80-9C69ABD4254D}"/>
+    <hyperlink ref="A254" r:id="rId76" display="mailto:carlos.dmolina@clarosv" xr:uid="{BF9AF06E-93EC-4E38-AAFE-EEBBCB6CF01E}"/>
+    <hyperlink ref="A257" r:id="rId77" display="mailto:douglas.molina@clarosv" xr:uid="{8C189F76-58AA-4ECE-A4FA-EC05975D2BDC}"/>
+    <hyperlink ref="A258" r:id="rId78" display="mailto:eduardoa.moran@clarosv" xr:uid="{AFFCF424-AA94-4041-990E-70DBDE93D203}"/>
+    <hyperlink ref="A268" r:id="rId79" display="mailto:oscar.rgomez@clarosv" xr:uid="{EA60BBC9-D9B3-4F76-975D-09806A5A60CC}"/>
+    <hyperlink ref="A269" r:id="rId80" display="mailto:oscare.cruz@clarosv" xr:uid="{F82A87D2-15C1-4303-AC6A-466D1EB271D7}"/>
+    <hyperlink ref="A271" r:id="rId81" display="mailto:yaneth.ramos@clarosv" xr:uid="{13773716-52FF-48B1-A220-38F5829611A9}"/>
+    <hyperlink ref="A283" r:id="rId82" display="mailto:danielag.pena@clarosv" xr:uid="{50F2EE6A-88C6-4BCC-9771-B198816E2E8E}"/>
+    <hyperlink ref="A301" r:id="rId83" display="mailto:maira.gil@clarosv" xr:uid="{8E8EA5C1-D80E-4774-BED7-A56429494C29}"/>
+    <hyperlink ref="A302" r:id="rId84" display="mailto:marjorie.guardado@clarosv" xr:uid="{4E83DC30-3579-4F3B-A988-B2369CB644C4}"/>
+    <hyperlink ref="A340" r:id="rId85" display="mailto:jorgem.serrano@clarosv" xr:uid="{88988BEF-E1C2-4AEF-8FA5-B38E83E8351E}"/>
+    <hyperlink ref="A348" r:id="rId86" display="mailto:iveth.cuadra@clarosv" xr:uid="{FB5B68C4-F1DC-487C-BA75-4BC52A72C352}"/>
+    <hyperlink ref="A353" r:id="rId87" display="mailto:carlosd.tobar@clarosv" xr:uid="{E6FFD0C9-10BE-4853-927E-039E60795502}"/>
+    <hyperlink ref="A354" r:id="rId88" display="mailto:hazela.ramirez@clarosv" xr:uid="{89A117C1-BBC9-4E33-9E7F-EDB0D41AE018}"/>
+    <hyperlink ref="A356" r:id="rId89" display="mailto:jonathan.ahernandez@clarosv" xr:uid="{E2916E02-2E8B-4101-92F8-0635024C66DF}"/>
+    <hyperlink ref="A358" r:id="rId90" display="mailto:katherine.reynosa@clarosv" xr:uid="{35787882-D9AC-4105-AF3A-0F686DD7676A}"/>
+    <hyperlink ref="A399" r:id="rId91" display="mailto:marielos.hernandez@clarosv" xr:uid="{11A8E50F-9D8F-484F-A3CB-EB15C8AD2A1A}"/>
+    <hyperlink ref="A411" r:id="rId92" display="mailto:byron.marroquin@clarosv" xr:uid="{AEA1DCED-6D0D-4805-95B1-B365E34A683F}"/>
+    <hyperlink ref="A412" r:id="rId93" display="mailto:cesar.elias@clarosv" xr:uid="{133449B1-AC87-46FF-B55D-159967334F4B}"/>
+    <hyperlink ref="A413" r:id="rId94" display="mailto:christian.mendoza@clarosv" xr:uid="{31BA296A-6447-455B-B9C4-5D5EC34B6E36}"/>
+    <hyperlink ref="A414" r:id="rId95" display="mailto:javier.ruiz@clarosv" xr:uid="{ED50CB10-1C59-4124-AC2C-597939E135AF}"/>
+    <hyperlink ref="A415" r:id="rId96" display="mailto:jennifer.landaverde@clarosv" xr:uid="{207D9C4C-E548-4D8B-896A-4B6841FE5609}"/>
+    <hyperlink ref="A416" r:id="rId97" display="mailto:miriam.martinez@clarosv" xr:uid="{C078A715-8559-4BB7-A291-7854D7940F48}"/>
+    <hyperlink ref="A417" r:id="rId98" display="mailto:rebeca.caballero@clarosv" xr:uid="{3F2E6573-76F5-41C7-B4D3-E8726A9D5A9D}"/>
+    <hyperlink ref="A418" r:id="rId99" display="mailto:vladimir.estradav@clarosv" xr:uid="{4A35FDD5-4722-4F2C-B830-E996FC1A3D82}"/>
+    <hyperlink ref="A424" r:id="rId100" display="mailto:melendezm.juan@clarosv" xr:uid="{80869B72-8B94-49A8-AC0D-371E945DAF30}"/>
+    <hyperlink ref="A425" r:id="rId101" display="mailto:rivera_marvin@clarosv" xr:uid="{5D2B8AED-6576-4190-96A2-63FB96532C14}"/>
+    <hyperlink ref="A426" r:id="rId102" display="mailto:rafaela.figueroa@clarosv" xr:uid="{8D6D13AD-6A97-4679-B044-13B88E2C2904}"/>
+    <hyperlink ref="A428" r:id="rId103" display="mailto:gabriela.ocruz@clarosv" xr:uid="{3BD9BE02-EC7A-4819-AE26-6B6B7ACE32BD}"/>
+    <hyperlink ref="A430" r:id="rId104" display="mailto:katherine.bolainez@clarosv" xr:uid="{20BB68AF-34A6-446C-B403-92111AF8B2FA}"/>
+    <hyperlink ref="A432" r:id="rId105" display="mailto:pineda.gabriela@clarosv" xr:uid="{8C508C40-41BA-4829-9861-D04EF964A3F7}"/>
+    <hyperlink ref="A433" r:id="rId106" display="mailto:veronica.campos@clarosv" xr:uid="{EBF817CC-0E91-4A32-A3D2-C92C2E68ECA9}"/>
+    <hyperlink ref="A436" r:id="rId107" display="mailto:alexander.orellanap@clarosv" xr:uid="{EE7EA8F0-7AB8-40A7-86D5-E6985C8A4F61}"/>
+    <hyperlink ref="A441" r:id="rId108" display="mailto:antonio.ponce@clarosv" xr:uid="{B4BF837A-3A5F-4BB0-B9AB-D63C16B28E33}"/>
+    <hyperlink ref="A443" r:id="rId109" display="mailto:blanca.avelarm@clarosv" xr:uid="{6D299A80-EE5D-4E84-A0D9-38C2549348FC}"/>
+    <hyperlink ref="A444" r:id="rId110" display="mailto:brenda.turcios@clarosv" xr:uid="{D208D137-11E7-4307-994D-E17C470A82C0}"/>
+    <hyperlink ref="A445" r:id="rId111" display="mailto:daniel.hernandezs@clarosv" xr:uid="{09BD9021-36D2-4671-BC9D-93207DFE3038}"/>
+    <hyperlink ref="A448" r:id="rId112" display="mailto:ezequiel.lopez@clarosv" xr:uid="{EF1C2AE4-3DDA-43A3-9214-C54366B02A6D}"/>
+    <hyperlink ref="A449" r:id="rId113" display="mailto:jessica.valencia@clarosv" xr:uid="{EB5C6330-2F90-478F-9477-B21C29788220}"/>
+    <hyperlink ref="A451" r:id="rId114" display="mailto:josem.ayala@clarosv" xr:uid="{057A2E00-48FA-4F95-B5E4-E2DC4C8ADAE8}"/>
+    <hyperlink ref="A454" r:id="rId115" display="mailto:kathya.guerrero@clarosv" xr:uid="{5FCF8C35-B260-4173-A7AA-65A09C3C139F}"/>
+    <hyperlink ref="A456" r:id="rId116" display="mailto:mario.jovel@clarosv" xr:uid="{1996E1F5-9274-4AAB-9FBD-A238EF38AE08}"/>
+    <hyperlink ref="A457" r:id="rId117" display="mailto:op12@clarosv" xr:uid="{66452100-E4F7-40BD-8435-FFCC6B78C4B8}"/>
+    <hyperlink ref="A458" r:id="rId118" display="mailto:orellana.luism@clarosv" xr:uid="{2B9408D7-B020-4DBA-915E-D711C069D49F}"/>
+    <hyperlink ref="A459" r:id="rId119" display="mailto:orellana.olgam@clarosv" xr:uid="{7871F0B7-0031-44B8-8B48-12CC582919F2}"/>
+    <hyperlink ref="A460" r:id="rId120" display="mailto:oscar.sarceno@clarosv" xr:uid="{324294E3-EE00-4496-8004-81F884476EEC}"/>
+    <hyperlink ref="A462" r:id="rId121" display="mailto:soniae.mendez@clarosv" xr:uid="{DAD8F132-296B-42D8-ABE4-81D7A6067153}"/>
+    <hyperlink ref="A464" r:id="rId122" display="mailto:susana.valiente@clarosv" xr:uid="{4B32C878-47F7-466A-849D-ED78456F479F}"/>
+    <hyperlink ref="A465" r:id="rId123" display="mailto:wendys.mejia@clarosv" xr:uid="{BEAAC67D-29B5-4B93-984B-78689A62C98A}"/>
+    <hyperlink ref="A466" r:id="rId124" display="mailto:xiomara.mejia@clarosv" xr:uid="{C3A935A2-FC70-4EE0-90EB-01823F38553A}"/>
+    <hyperlink ref="A467" r:id="rId125" display="mailto:alejandran.blancom@clarosv" xr:uid="{E8FAAADA-0FA6-45B0-9FEE-921A2FBA759D}"/>
+    <hyperlink ref="A470" r:id="rId126" display="mailto:henry.romero@clarosv" xr:uid="{E406B3FD-E527-43B6-8A92-9CA29A144987}"/>
+    <hyperlink ref="A472" r:id="rId127" display="mailto:ambara.maradiaga@clarosv" xr:uid="{E7240EA0-50CF-4224-A2F4-218F07F60327}"/>
+    <hyperlink ref="A476" r:id="rId128" display="mailto:gabrielaa.amarin@clarosv" xr:uid="{3A3787F2-EE2A-42BC-B5CB-271006E9CC6E}"/>
+    <hyperlink ref="A478" r:id="rId129" display="mailto:luis.orellana@clarosv" xr:uid="{E1EBE570-45C0-4F83-B687-67F705C782C3}"/>
+    <hyperlink ref="A479" r:id="rId130" display="mailto:william.murcia@clarosv" xr:uid="{7150636D-C64D-4553-9EFD-E4E9585FB601}"/>
+    <hyperlink ref="A630" r:id="rId131" display="mailto:nasser.zablash@clarosv" xr:uid="{3E0B34EE-569D-4017-83EB-0E62CB788BF8}"/>
+    <hyperlink ref="A645" r:id="rId132" display="mailto:erika.pmartinez2@clarosv" xr:uid="{0BEB8B27-1BCD-4288-9333-550DA87ABCEE}"/>
+    <hyperlink ref="A650" r:id="rId133" display="mailto:adriana.raudag@clarosv" xr:uid="{1D0C101B-F487-47C9-9A0C-D287E175DB06}"/>
+    <hyperlink ref="A651" r:id="rId134" display="mailto:alejandram.flores@clarosv" xr:uid="{E339536E-6BC0-4BA7-963C-899DFB99D2A4}"/>
+    <hyperlink ref="A657" r:id="rId135" display="mailto:angel.monterrosag@clarosv" xr:uid="{4ACB8EDA-5539-4039-A471-C72B27D3C796}"/>
+    <hyperlink ref="A658" r:id="rId136" display="mailto:angel.reyesh@clarosv" xr:uid="{5581B781-9439-4932-956B-E3BD04BA0130}"/>
+    <hyperlink ref="A661" r:id="rId137" display="mailto:belen.avedano@clarosv" xr:uid="{1F947D6F-162A-4B1A-AE6D-0C8C075361F6}"/>
+    <hyperlink ref="A667" r:id="rId138" display="mailto:carlos.eflores@clarosv" xr:uid="{B47B3285-BC36-4AF1-B70A-5302BE5B4EC3}"/>
+    <hyperlink ref="A668" r:id="rId139" display="mailto:carlos.mguzman@clarosv" xr:uid="{02A43E60-080A-4D27-BA38-D664A4F6E205}"/>
+    <hyperlink ref="A673" r:id="rId140" display="mailto:clara.lzavaleta@clarosv" xr:uid="{1911B146-5D0B-4626-8206-99AE836D39EC}"/>
+    <hyperlink ref="A674" r:id="rId141" display="mailto:claudia.perez@clarosv" xr:uid="{005A705B-F949-455C-8D48-6296B983838B}"/>
+    <hyperlink ref="A677" r:id="rId142" display="mailto:daniel.moran@clarosv" xr:uid="{2C2F1D67-BA70-443A-86CE-E1AD0EBCCB7F}"/>
+    <hyperlink ref="A680" r:id="rId143" display="mailto:davida.hernandezm@clarosv" xr:uid="{4F6459D7-7103-4E4C-9F90-F2A0729F0643}"/>
+    <hyperlink ref="A682" r:id="rId144" display="mailto:derek.caballero@clarosv" xr:uid="{1F1D2492-CA7F-4C43-987C-6A58C820B305}"/>
+    <hyperlink ref="A689" r:id="rId145" display="mailto:edwin.madrid@clarosv" xr:uid="{B5F9D174-4F14-44D8-8A8B-D413F93AA322}"/>
+    <hyperlink ref="A691" r:id="rId146" display="mailto:emilio.martineza@clarosv" xr:uid="{F1FD2D00-D1A8-4E4E-AD4F-C69A908F8374}"/>
+    <hyperlink ref="A692" r:id="rId147" display="mailto:estefany.mendezg@clarosv" xr:uid="{90F96D5D-8657-46AE-8CC1-F4C744C7037B}"/>
+    <hyperlink ref="A697" r:id="rId148" display="mailto:gilma.barillas@clarosv" xr:uid="{8E1C92C3-342B-436B-928C-976D5D5274C3}"/>
+    <hyperlink ref="A703" r:id="rId149" display="mailto:henry.matute@clarosv" xr:uid="{6274B48D-1A4A-458B-B0F4-FF83DD35853A}"/>
+    <hyperlink ref="A705" r:id="rId150" display="mailto:iris.graciasz@clarosv" xr:uid="{10C64533-08AE-4FD3-A4E8-E6E441E5F579}"/>
+    <hyperlink ref="A706" r:id="rId151" display="mailto:izamar.perezm@clarosv" xr:uid="{A78EE24E-CBE0-46AF-86A3-CD908AF56B78}"/>
+    <hyperlink ref="A707" r:id="rId152" display="mailto:jackelyn.guevarap@clarosv" xr:uid="{663561E2-4841-4D02-82A5-7C24AEEAE50A}"/>
+    <hyperlink ref="A710" r:id="rId153" display="mailto:jasmin.branr@clarosv" xr:uid="{74700D6B-9742-4FA5-8372-77F2F52F59AF}"/>
+    <hyperlink ref="A711" r:id="rId154" display="mailto:joaquin.lizamam@clarosv" xr:uid="{24ABC48A-DD1F-4AD3-BDAE-172CEC43D038}"/>
+    <hyperlink ref="A714" r:id="rId155" display="mailto:jose.ayalam@clarosv" xr:uid="{3DBBFEF7-9E80-4A5F-9715-4DF93A3295A0}"/>
+    <hyperlink ref="A724" r:id="rId156" display="mailto:juan.amartinez@clarosv" xr:uid="{C11D87A6-917D-48A3-96F1-538F5FD0CB34}"/>
+    <hyperlink ref="A729" r:id="rId157" display="mailto:karlav.hernandez@clarosv" xr:uid="{C272E8B8-006A-4234-98D4-C5853293AADA}"/>
+    <hyperlink ref="A735" r:id="rId158" display="mailto:kevin.contrerass@clarosv" xr:uid="{45B22699-883E-4ADD-A7AF-2D66AB7E1264}"/>
+    <hyperlink ref="A737" r:id="rId159" display="mailto:kevin.menjivarh@clarosv" xr:uid="{885E64D2-90D4-40EF-9E61-1F78CA85D801}"/>
+    <hyperlink ref="A739" r:id="rId160" display="mailto:linda.rivasg@clarosv" xr:uid="{6F5059F8-F9C5-4AEC-BC98-6397BB0903E7}"/>
+    <hyperlink ref="A741" r:id="rId161" display="mailto:maria.alfaro@clarosv" xr:uid="{D5D9965D-FD4A-4697-828C-1BB16FE12661}"/>
+    <hyperlink ref="A750" r:id="rId162" display="mailto:marjorie.ortiza@clarosv" xr:uid="{D3909B8B-0E43-40C5-AF10-A03407A0D746}"/>
+    <hyperlink ref="A752" r:id="rId163" display="mailto:marlong.garcia@clarosv" xr:uid="{25569C92-C438-4EFB-9735-EF0A954532F7}"/>
+    <hyperlink ref="A762" r:id="rId164" display="mailto:nelsonv.rivera@clarosv" xr:uid="{FA1996F2-25D8-47F4-902B-85C5559F6605}"/>
+    <hyperlink ref="A764" r:id="rId165" display="mailto:oscars.bonilla@clarosv" xr:uid="{9D03B1CA-487F-43BB-9E56-48250C129C38}"/>
+    <hyperlink ref="A770" r:id="rId166" display="mailto:ricardo.pleitezh@clarosv" xr:uid="{26B00D4C-E82A-44F5-A3C4-9BCE5D6757AD}"/>
+    <hyperlink ref="A772" r:id="rId167" display="mailto:rodrigoa.martinez@clarosv" xr:uid="{1F2B4717-7BC4-4284-A04F-911BF318A3F9}"/>
+    <hyperlink ref="A773" r:id="rId168" display="mailto:rosaura.garcia@clarosv" xr:uid="{DD12E24C-5E89-4FB4-A82C-D24F4F8D8490}"/>
+    <hyperlink ref="A780" r:id="rId169" display="mailto:vladimiran.margueiz@clarosv" xr:uid="{F1BB5546-E748-48D4-BDC5-E85A85194AA5}"/>
+    <hyperlink ref="A783" r:id="rId170" display="mailto:zuleyma.mendozar@clarosv" xr:uid="{EB9C4EAB-3F60-4336-A68A-8A3D708E2C1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId171"/>
@@ -26775,6 +26573,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -26912,22 +26725,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26943,28 +26765,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>